--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EA24B3-80AF-4643-801F-835E19C39310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96624AEB-03D9-0048-97D5-3F2458116D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7838" uniqueCount="1159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7952" uniqueCount="1175">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3513,6 +3513,54 @@
   </si>
   <si>
     <t>01:32:09</t>
+  </si>
+  <si>
+    <t>01:08:21</t>
+  </si>
+  <si>
+    <t>01:09:53</t>
+  </si>
+  <si>
+    <t>01:08:37</t>
+  </si>
+  <si>
+    <t>01:06:50</t>
+  </si>
+  <si>
+    <t>01:09:23</t>
+  </si>
+  <si>
+    <t>01:07:50</t>
+  </si>
+  <si>
+    <t>01:47:11</t>
+  </si>
+  <si>
+    <t>01:46:35</t>
+  </si>
+  <si>
+    <t>00:37:43</t>
+  </si>
+  <si>
+    <t>01:47:45</t>
+  </si>
+  <si>
+    <t>01:07:16</t>
+  </si>
+  <si>
+    <t>00:12:08</t>
+  </si>
+  <si>
+    <t>00:36:15</t>
+  </si>
+  <si>
+    <t>00:05:16</t>
+  </si>
+  <si>
+    <t>01:33:16</t>
+  </si>
+  <si>
+    <t>N3 J14 VS Alès</t>
   </si>
 </sst>
 </file>
@@ -3916,7 +3964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1387"/>
+  <dimension ref="A1:V1406"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -96744,6 +96792,1298 @@
         <v>2</v>
       </c>
     </row>
+    <row r="1388" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1388" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1388" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1388" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1388" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1388" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1388" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H1388">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="I1388">
+        <v>0.13</v>
+      </c>
+      <c r="J1388">
+        <v>4.25</v>
+      </c>
+      <c r="K1388">
+        <v>0.12</v>
+      </c>
+      <c r="L1388">
+        <v>0.02</v>
+      </c>
+      <c r="M1388">
+        <v>0</v>
+      </c>
+      <c r="N1388">
+        <v>0</v>
+      </c>
+      <c r="O1388">
+        <v>0</v>
+      </c>
+      <c r="P1388">
+        <v>3.87</v>
+      </c>
+      <c r="Q1388">
+        <v>21.89</v>
+      </c>
+      <c r="R1388">
+        <v>5.07</v>
+      </c>
+      <c r="S1388">
+        <v>19</v>
+      </c>
+      <c r="T1388">
+        <v>4</v>
+      </c>
+      <c r="U1388">
+        <v>18</v>
+      </c>
+      <c r="V1388">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1389" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1389" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1389" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1389" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1389" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1389" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H1389">
+        <v>4.97</v>
+      </c>
+      <c r="I1389">
+        <v>0.37</v>
+      </c>
+      <c r="J1389">
+        <v>4.57</v>
+      </c>
+      <c r="K1389">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L1389">
+        <v>0.08</v>
+      </c>
+      <c r="M1389">
+        <v>0.02</v>
+      </c>
+      <c r="N1389">
+        <v>0</v>
+      </c>
+      <c r="O1389">
+        <v>5</v>
+      </c>
+      <c r="P1389">
+        <v>3.89</v>
+      </c>
+      <c r="Q1389">
+        <v>26.42</v>
+      </c>
+      <c r="R1389">
+        <v>6.78</v>
+      </c>
+      <c r="S1389">
+        <v>77</v>
+      </c>
+      <c r="T1389">
+        <v>23</v>
+      </c>
+      <c r="U1389">
+        <v>40</v>
+      </c>
+      <c r="V1389">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1390" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1390" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1390" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1390" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1390" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1390" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H1390">
+        <v>5.46</v>
+      </c>
+      <c r="I1390">
+        <v>0.2</v>
+      </c>
+      <c r="J1390">
+        <v>5.25</v>
+      </c>
+      <c r="K1390">
+        <v>0.18</v>
+      </c>
+      <c r="L1390">
+        <v>0.02</v>
+      </c>
+      <c r="M1390">
+        <v>0</v>
+      </c>
+      <c r="N1390">
+        <v>0</v>
+      </c>
+      <c r="O1390">
+        <v>0</v>
+      </c>
+      <c r="P1390">
+        <v>4.7</v>
+      </c>
+      <c r="Q1390">
+        <v>23.12</v>
+      </c>
+      <c r="R1390">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="S1390">
+        <v>30</v>
+      </c>
+      <c r="T1390">
+        <v>8</v>
+      </c>
+      <c r="U1390">
+        <v>22</v>
+      </c>
+      <c r="V1390">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1391" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1391" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1391" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1391" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1391" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1391" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H1391">
+        <v>4.28</v>
+      </c>
+      <c r="I1391">
+        <v>0.08</v>
+      </c>
+      <c r="J1391">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="K1391">
+        <v>0.09</v>
+      </c>
+      <c r="L1391">
+        <v>0</v>
+      </c>
+      <c r="M1391">
+        <v>0</v>
+      </c>
+      <c r="N1391">
+        <v>0</v>
+      </c>
+      <c r="O1391">
+        <v>0</v>
+      </c>
+      <c r="P1391">
+        <v>3.34</v>
+      </c>
+      <c r="Q1391">
+        <v>21.59</v>
+      </c>
+      <c r="R1391">
+        <v>5.08</v>
+      </c>
+      <c r="S1391">
+        <v>14</v>
+      </c>
+      <c r="T1391">
+        <v>5</v>
+      </c>
+      <c r="U1391">
+        <v>10</v>
+      </c>
+      <c r="V1391">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1392" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1392" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1392" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1392" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1392" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1392" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H1392">
+        <v>5.15</v>
+      </c>
+      <c r="I1392">
+        <v>0.35</v>
+      </c>
+      <c r="J1392">
+        <v>4.79</v>
+      </c>
+      <c r="K1392">
+        <v>0.25</v>
+      </c>
+      <c r="L1392">
+        <v>0.11</v>
+      </c>
+      <c r="M1392">
+        <v>0</v>
+      </c>
+      <c r="N1392">
+        <v>0</v>
+      </c>
+      <c r="O1392">
+        <v>0</v>
+      </c>
+      <c r="P1392">
+        <v>4.43</v>
+      </c>
+      <c r="Q1392">
+        <v>24.58</v>
+      </c>
+      <c r="R1392">
+        <v>4.66</v>
+      </c>
+      <c r="S1392">
+        <v>28</v>
+      </c>
+      <c r="T1392">
+        <v>7</v>
+      </c>
+      <c r="U1392">
+        <v>20</v>
+      </c>
+      <c r="V1392">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1393" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1393" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1393" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1393" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1393" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1393" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H1393">
+        <v>5.36</v>
+      </c>
+      <c r="I1393">
+        <v>0.34</v>
+      </c>
+      <c r="J1393">
+        <v>5.01</v>
+      </c>
+      <c r="K1393">
+        <v>0.33</v>
+      </c>
+      <c r="L1393">
+        <v>0.01</v>
+      </c>
+      <c r="M1393">
+        <v>0</v>
+      </c>
+      <c r="N1393">
+        <v>0</v>
+      </c>
+      <c r="O1393">
+        <v>0</v>
+      </c>
+      <c r="P1393">
+        <v>4.67</v>
+      </c>
+      <c r="Q1393">
+        <v>21.51</v>
+      </c>
+      <c r="R1393">
+        <v>4.5</v>
+      </c>
+      <c r="S1393">
+        <v>38</v>
+      </c>
+      <c r="T1393">
+        <v>8</v>
+      </c>
+      <c r="U1393">
+        <v>25</v>
+      </c>
+      <c r="V1393">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1394" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1394" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1394" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1394" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1394" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1394" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H1394">
+        <v>12.24</v>
+      </c>
+      <c r="I1394">
+        <v>2.12</v>
+      </c>
+      <c r="J1394">
+        <v>10.1</v>
+      </c>
+      <c r="K1394">
+        <v>1.42</v>
+      </c>
+      <c r="L1394">
+        <v>0.63</v>
+      </c>
+      <c r="M1394">
+        <v>0.09</v>
+      </c>
+      <c r="N1394">
+        <v>0</v>
+      </c>
+      <c r="O1394">
+        <v>8</v>
+      </c>
+      <c r="P1394">
+        <v>6.65</v>
+      </c>
+      <c r="Q1394">
+        <v>29.35</v>
+      </c>
+      <c r="R1394">
+        <v>4.74</v>
+      </c>
+      <c r="S1394">
+        <v>42</v>
+      </c>
+      <c r="T1394">
+        <v>11</v>
+      </c>
+      <c r="U1394">
+        <v>30</v>
+      </c>
+      <c r="V1394">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1395" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1395" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1395" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1395" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1395" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1395" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H1395">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="I1395">
+        <v>1.23</v>
+      </c>
+      <c r="J1395">
+        <v>8.81</v>
+      </c>
+      <c r="K1395">
+        <v>0.88</v>
+      </c>
+      <c r="L1395">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M1395">
+        <v>0.08</v>
+      </c>
+      <c r="N1395">
+        <v>0</v>
+      </c>
+      <c r="O1395">
+        <v>5</v>
+      </c>
+      <c r="P1395">
+        <v>5.55</v>
+      </c>
+      <c r="Q1395">
+        <v>29.42</v>
+      </c>
+      <c r="R1395">
+        <v>4.37</v>
+      </c>
+      <c r="S1395">
+        <v>17</v>
+      </c>
+      <c r="T1395">
+        <v>3</v>
+      </c>
+      <c r="U1395">
+        <v>22</v>
+      </c>
+      <c r="V1395">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1396" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1396" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1396" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1396" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1396" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1396" t="s">
+        <v>809</v>
+      </c>
+      <c r="H1396">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="I1396">
+        <v>1.47</v>
+      </c>
+      <c r="J1396">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="K1396">
+        <v>1.07</v>
+      </c>
+      <c r="L1396">
+        <v>0.35</v>
+      </c>
+      <c r="M1396">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N1396">
+        <v>0.01</v>
+      </c>
+      <c r="O1396">
+        <v>4</v>
+      </c>
+      <c r="P1396">
+        <v>5.92</v>
+      </c>
+      <c r="Q1396">
+        <v>31.23</v>
+      </c>
+      <c r="R1396">
+        <v>5</v>
+      </c>
+      <c r="S1396">
+        <v>42</v>
+      </c>
+      <c r="T1396">
+        <v>9</v>
+      </c>
+      <c r="U1396">
+        <v>37</v>
+      </c>
+      <c r="V1396">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1397" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1397" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1397" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1397" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1397" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1397" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H1397">
+        <v>12.24</v>
+      </c>
+      <c r="I1397">
+        <v>2.25</v>
+      </c>
+      <c r="J1397">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="K1397">
+        <v>1.38</v>
+      </c>
+      <c r="L1397">
+        <v>0.74</v>
+      </c>
+      <c r="M1397">
+        <v>0.15</v>
+      </c>
+      <c r="N1397">
+        <v>0</v>
+      </c>
+      <c r="O1397">
+        <v>13</v>
+      </c>
+      <c r="P1397">
+        <v>6.81</v>
+      </c>
+      <c r="Q1397">
+        <v>29.13</v>
+      </c>
+      <c r="R1397">
+        <v>4.49</v>
+      </c>
+      <c r="S1397">
+        <v>41</v>
+      </c>
+      <c r="T1397">
+        <v>7</v>
+      </c>
+      <c r="U1397">
+        <v>46</v>
+      </c>
+      <c r="V1397">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1398" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1398" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1398" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1398" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1398" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1398" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H1398">
+        <v>4.51</v>
+      </c>
+      <c r="I1398">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="J1398">
+        <v>3.41</v>
+      </c>
+      <c r="K1398">
+        <v>0.66</v>
+      </c>
+      <c r="L1398">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M1398">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N1398">
+        <v>0.02</v>
+      </c>
+      <c r="O1398">
+        <v>7</v>
+      </c>
+      <c r="P1398">
+        <v>7.15</v>
+      </c>
+      <c r="Q1398">
+        <v>30.91</v>
+      </c>
+      <c r="R1398">
+        <v>4.49</v>
+      </c>
+      <c r="S1398">
+        <v>24</v>
+      </c>
+      <c r="T1398">
+        <v>4</v>
+      </c>
+      <c r="U1398">
+        <v>11</v>
+      </c>
+      <c r="V1398">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1399" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1399" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1399" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1399" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1399" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1399" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H1399">
+        <v>13.33</v>
+      </c>
+      <c r="I1399">
+        <v>3.37</v>
+      </c>
+      <c r="J1399">
+        <v>9.92</v>
+      </c>
+      <c r="K1399">
+        <v>2.34</v>
+      </c>
+      <c r="L1399">
+        <v>0.96</v>
+      </c>
+      <c r="M1399">
+        <v>0.1</v>
+      </c>
+      <c r="N1399">
+        <v>0</v>
+      </c>
+      <c r="O1399">
+        <v>9</v>
+      </c>
+      <c r="P1399">
+        <v>7.3</v>
+      </c>
+      <c r="Q1399">
+        <v>29.52</v>
+      </c>
+      <c r="R1399">
+        <v>4.51</v>
+      </c>
+      <c r="S1399">
+        <v>66</v>
+      </c>
+      <c r="T1399">
+        <v>8</v>
+      </c>
+      <c r="U1399">
+        <v>58</v>
+      </c>
+      <c r="V1399">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1400" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1400" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1400" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1400" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1400" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1400" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H1400">
+        <v>8.07</v>
+      </c>
+      <c r="I1400">
+        <v>1.92</v>
+      </c>
+      <c r="J1400">
+        <v>6.13</v>
+      </c>
+      <c r="K1400">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L1400">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M1400">
+        <v>0.2</v>
+      </c>
+      <c r="N1400">
+        <v>0.02</v>
+      </c>
+      <c r="O1400">
+        <v>16</v>
+      </c>
+      <c r="P1400">
+        <v>7.15</v>
+      </c>
+      <c r="Q1400">
+        <v>31.06</v>
+      </c>
+      <c r="R1400">
+        <v>4.42</v>
+      </c>
+      <c r="S1400">
+        <v>29</v>
+      </c>
+      <c r="T1400">
+        <v>6</v>
+      </c>
+      <c r="U1400">
+        <v>44</v>
+      </c>
+      <c r="V1400">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1401" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1401" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1401" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1401" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1401" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1401" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H1401">
+        <v>1.08</v>
+      </c>
+      <c r="I1401">
+        <v>0.18</v>
+      </c>
+      <c r="J1401">
+        <v>0.9</v>
+      </c>
+      <c r="K1401">
+        <v>0.11</v>
+      </c>
+      <c r="L1401">
+        <v>0.05</v>
+      </c>
+      <c r="M1401">
+        <v>0.02</v>
+      </c>
+      <c r="N1401">
+        <v>0</v>
+      </c>
+      <c r="O1401">
+        <v>3</v>
+      </c>
+      <c r="P1401">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="Q1401">
+        <v>26.7</v>
+      </c>
+      <c r="R1401">
+        <v>4</v>
+      </c>
+      <c r="S1401">
+        <v>6</v>
+      </c>
+      <c r="T1401">
+        <v>0</v>
+      </c>
+      <c r="U1401">
+        <v>1</v>
+      </c>
+      <c r="V1401">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1402" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1402" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1402" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1402" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1402" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1402" t="s">
+        <v>1171</v>
+      </c>
+      <c r="H1402">
+        <v>3.82</v>
+      </c>
+      <c r="I1402">
+        <v>0.59</v>
+      </c>
+      <c r="J1402">
+        <v>3.23</v>
+      </c>
+      <c r="K1402">
+        <v>0.45</v>
+      </c>
+      <c r="L1402">
+        <v>0.12</v>
+      </c>
+      <c r="M1402">
+        <v>0.03</v>
+      </c>
+      <c r="N1402">
+        <v>0</v>
+      </c>
+      <c r="O1402">
+        <v>3</v>
+      </c>
+      <c r="P1402">
+        <v>6.26</v>
+      </c>
+      <c r="Q1402">
+        <v>28.64</v>
+      </c>
+      <c r="R1402">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S1402">
+        <v>8</v>
+      </c>
+      <c r="T1402">
+        <v>1</v>
+      </c>
+      <c r="U1402">
+        <v>9</v>
+      </c>
+      <c r="V1402">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1403" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1403" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1403" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1403" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1403" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1403" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H1403">
+        <v>0.52</v>
+      </c>
+      <c r="I1403">
+        <v>0.1</v>
+      </c>
+      <c r="J1403">
+        <v>0.42</v>
+      </c>
+      <c r="K1403">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L1403">
+        <v>0.04</v>
+      </c>
+      <c r="M1403">
+        <v>0</v>
+      </c>
+      <c r="N1403">
+        <v>0</v>
+      </c>
+      <c r="O1403">
+        <v>0</v>
+      </c>
+      <c r="P1403">
+        <v>5.84</v>
+      </c>
+      <c r="Q1403">
+        <v>22.04</v>
+      </c>
+      <c r="R1403">
+        <v>5.27</v>
+      </c>
+      <c r="S1403">
+        <v>3</v>
+      </c>
+      <c r="T1403">
+        <v>2</v>
+      </c>
+      <c r="U1403">
+        <v>3</v>
+      </c>
+      <c r="V1403">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1404" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1404" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1404" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1404" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1404" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1404" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H1404">
+        <v>10</v>
+      </c>
+      <c r="I1404">
+        <v>1.99</v>
+      </c>
+      <c r="J1404">
+        <v>7.99</v>
+      </c>
+      <c r="K1404">
+        <v>1.36</v>
+      </c>
+      <c r="L1404">
+        <v>0.51</v>
+      </c>
+      <c r="M1404">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N1404">
+        <v>0</v>
+      </c>
+      <c r="O1404">
+        <v>12</v>
+      </c>
+      <c r="P1404">
+        <v>6.37</v>
+      </c>
+      <c r="Q1404">
+        <v>29.9</v>
+      </c>
+      <c r="R1404">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="S1404">
+        <v>46</v>
+      </c>
+      <c r="T1404">
+        <v>9</v>
+      </c>
+      <c r="U1404">
+        <v>30</v>
+      </c>
+      <c r="V1404">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1405" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1405" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1405" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1405" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1405" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1405" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H1405">
+        <v>13.22</v>
+      </c>
+      <c r="I1405">
+        <v>3.18</v>
+      </c>
+      <c r="J1405">
+        <v>10.01</v>
+      </c>
+      <c r="K1405">
+        <v>2.4</v>
+      </c>
+      <c r="L1405">
+        <v>0.68</v>
+      </c>
+      <c r="M1405">
+        <v>0.13</v>
+      </c>
+      <c r="N1405">
+        <v>0</v>
+      </c>
+      <c r="O1405">
+        <v>8</v>
+      </c>
+      <c r="P1405">
+        <v>7.6</v>
+      </c>
+      <c r="Q1405">
+        <v>27.52</v>
+      </c>
+      <c r="R1405">
+        <v>4.03</v>
+      </c>
+      <c r="S1405">
+        <v>38</v>
+      </c>
+      <c r="T1405">
+        <v>2</v>
+      </c>
+      <c r="U1405">
+        <v>48</v>
+      </c>
+      <c r="V1405">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1406" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1406" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1406" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1406" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1406" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1406" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H1406">
+        <v>7.05</v>
+      </c>
+      <c r="I1406">
+        <v>1.04</v>
+      </c>
+      <c r="J1406">
+        <v>6</v>
+      </c>
+      <c r="K1406">
+        <v>0.73</v>
+      </c>
+      <c r="L1406">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M1406">
+        <v>0.04</v>
+      </c>
+      <c r="N1406">
+        <v>0</v>
+      </c>
+      <c r="O1406">
+        <v>4</v>
+      </c>
+      <c r="P1406">
+        <v>6.26</v>
+      </c>
+      <c r="Q1406">
+        <v>27.34</v>
+      </c>
+      <c r="R1406">
+        <v>4.32</v>
+      </c>
+      <c r="S1406">
+        <v>18</v>
+      </c>
+      <c r="T1406">
+        <v>4</v>
+      </c>
+      <c r="U1406">
+        <v>20</v>
+      </c>
+      <c r="V1406">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96624AEB-03D9-0048-97D5-3F2458116D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481400E5-5D54-AA41-9AD4-63E660021264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7952" uniqueCount="1175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8096" uniqueCount="1194">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3561,6 +3561,63 @@
   </si>
   <si>
     <t>N3 J14 VS Alès</t>
+  </si>
+  <si>
+    <t>01:37:44</t>
+  </si>
+  <si>
+    <t>01:39:41</t>
+  </si>
+  <si>
+    <t>01:38:35</t>
+  </si>
+  <si>
+    <t>01:36:23</t>
+  </si>
+  <si>
+    <t>01:40:32</t>
+  </si>
+  <si>
+    <t>01:07:14</t>
+  </si>
+  <si>
+    <t>01:37:12</t>
+  </si>
+  <si>
+    <t>01:41:37</t>
+  </si>
+  <si>
+    <t>01:50:45</t>
+  </si>
+  <si>
+    <t>01:49:19</t>
+  </si>
+  <si>
+    <t>01:49:18</t>
+  </si>
+  <si>
+    <t>01:48:52</t>
+  </si>
+  <si>
+    <t>01:38:40</t>
+  </si>
+  <si>
+    <t>01:50:54</t>
+  </si>
+  <si>
+    <t>01:50:02</t>
+  </si>
+  <si>
+    <t>01:14:56</t>
+  </si>
+  <si>
+    <t>01:47:10</t>
+  </si>
+  <si>
+    <t>01:49:02</t>
+  </si>
+  <si>
+    <t>01:50:01</t>
   </si>
 </sst>
 </file>
@@ -3964,7 +4021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1406"/>
+  <dimension ref="A1:V1430"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -98084,6 +98141,1638 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1407" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1407" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1407" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1407" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1407" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1407" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1407" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H1407">
+        <v>6.89</v>
+      </c>
+      <c r="I1407">
+        <v>0.06</v>
+      </c>
+      <c r="J1407">
+        <v>6.84</v>
+      </c>
+      <c r="K1407">
+        <v>0.06</v>
+      </c>
+      <c r="L1407">
+        <v>0</v>
+      </c>
+      <c r="M1407">
+        <v>0</v>
+      </c>
+      <c r="N1407">
+        <v>0</v>
+      </c>
+      <c r="O1407">
+        <v>0</v>
+      </c>
+      <c r="P1407">
+        <v>3.62</v>
+      </c>
+      <c r="Q1407">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="R1407">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="S1407">
+        <v>31</v>
+      </c>
+      <c r="T1407">
+        <v>2</v>
+      </c>
+      <c r="U1407">
+        <v>25</v>
+      </c>
+      <c r="V1407">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1408" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1408" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1408" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1408" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1408" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1408" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H1408">
+        <v>8.84</v>
+      </c>
+      <c r="I1408">
+        <v>0.33</v>
+      </c>
+      <c r="J1408">
+        <v>8.49</v>
+      </c>
+      <c r="K1408">
+        <v>0.32</v>
+      </c>
+      <c r="L1408">
+        <v>0.03</v>
+      </c>
+      <c r="M1408">
+        <v>0</v>
+      </c>
+      <c r="N1408">
+        <v>0</v>
+      </c>
+      <c r="O1408">
+        <v>0</v>
+      </c>
+      <c r="P1408">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="Q1408">
+        <v>23.79</v>
+      </c>
+      <c r="R1408">
+        <v>5.25</v>
+      </c>
+      <c r="S1408">
+        <v>93</v>
+      </c>
+      <c r="T1408">
+        <v>21</v>
+      </c>
+      <c r="U1408">
+        <v>71</v>
+      </c>
+      <c r="V1408">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1409" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1409" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1409" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1409" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1409" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1409" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H1409">
+        <v>7.74</v>
+      </c>
+      <c r="I1409">
+        <v>0.11</v>
+      </c>
+      <c r="J1409">
+        <v>7.62</v>
+      </c>
+      <c r="K1409">
+        <v>0.12</v>
+      </c>
+      <c r="L1409">
+        <v>0</v>
+      </c>
+      <c r="M1409">
+        <v>0</v>
+      </c>
+      <c r="N1409">
+        <v>0</v>
+      </c>
+      <c r="O1409">
+        <v>0</v>
+      </c>
+      <c r="P1409">
+        <v>4.66</v>
+      </c>
+      <c r="Q1409">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="R1409">
+        <v>3.81</v>
+      </c>
+      <c r="S1409">
+        <v>38</v>
+      </c>
+      <c r="T1409">
+        <v>0</v>
+      </c>
+      <c r="U1409">
+        <v>15</v>
+      </c>
+      <c r="V1409">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1410" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1410" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1410" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1410" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1410" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1410" t="s">
+        <v>315</v>
+      </c>
+      <c r="H1410">
+        <v>7.72</v>
+      </c>
+      <c r="I1410">
+        <v>0.25</v>
+      </c>
+      <c r="J1410">
+        <v>7.45</v>
+      </c>
+      <c r="K1410">
+        <v>0.25</v>
+      </c>
+      <c r="L1410">
+        <v>0.02</v>
+      </c>
+      <c r="M1410">
+        <v>0</v>
+      </c>
+      <c r="N1410">
+        <v>0</v>
+      </c>
+      <c r="O1410">
+        <v>0</v>
+      </c>
+      <c r="P1410">
+        <v>4.08</v>
+      </c>
+      <c r="Q1410">
+        <v>22.69</v>
+      </c>
+      <c r="R1410">
+        <v>5.75</v>
+      </c>
+      <c r="S1410">
+        <v>88</v>
+      </c>
+      <c r="T1410">
+        <v>32</v>
+      </c>
+      <c r="U1410">
+        <v>72</v>
+      </c>
+      <c r="V1410">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1411" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1411" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1411" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1411" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1411" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1411" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H1411">
+        <v>6.58</v>
+      </c>
+      <c r="I1411">
+        <v>0.19</v>
+      </c>
+      <c r="J1411">
+        <v>6.39</v>
+      </c>
+      <c r="K1411">
+        <v>0.18</v>
+      </c>
+      <c r="L1411">
+        <v>0.02</v>
+      </c>
+      <c r="M1411">
+        <v>0</v>
+      </c>
+      <c r="N1411">
+        <v>0</v>
+      </c>
+      <c r="O1411">
+        <v>0</v>
+      </c>
+      <c r="P1411">
+        <v>3.98</v>
+      </c>
+      <c r="Q1411">
+        <v>21.28</v>
+      </c>
+      <c r="R1411">
+        <v>4.45</v>
+      </c>
+      <c r="S1411">
+        <v>17</v>
+      </c>
+      <c r="T1411">
+        <v>1</v>
+      </c>
+      <c r="U1411">
+        <v>12</v>
+      </c>
+      <c r="V1411">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1412" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1412" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1412" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1412" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1412" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1412" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H1412">
+        <v>8.48</v>
+      </c>
+      <c r="I1412">
+        <v>0.26</v>
+      </c>
+      <c r="J1412">
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="K1412">
+        <v>0.22</v>
+      </c>
+      <c r="L1412">
+        <v>0.04</v>
+      </c>
+      <c r="M1412">
+        <v>0</v>
+      </c>
+      <c r="N1412">
+        <v>0</v>
+      </c>
+      <c r="O1412">
+        <v>0</v>
+      </c>
+      <c r="P1412">
+        <v>4.2</v>
+      </c>
+      <c r="Q1412">
+        <v>22.93</v>
+      </c>
+      <c r="R1412">
+        <v>4.91</v>
+      </c>
+      <c r="S1412">
+        <v>63</v>
+      </c>
+      <c r="T1412">
+        <v>12</v>
+      </c>
+      <c r="U1412">
+        <v>55</v>
+      </c>
+      <c r="V1412">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1413" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1413" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1413" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1413" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1413" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1413" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H1413">
+        <v>6.02</v>
+      </c>
+      <c r="I1413">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J1413">
+        <v>5.95</v>
+      </c>
+      <c r="K1413">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L1413">
+        <v>0</v>
+      </c>
+      <c r="M1413">
+        <v>0</v>
+      </c>
+      <c r="N1413">
+        <v>0</v>
+      </c>
+      <c r="O1413">
+        <v>0</v>
+      </c>
+      <c r="P1413">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="Q1413">
+        <v>20.329999999999998</v>
+      </c>
+      <c r="R1413">
+        <v>5.2</v>
+      </c>
+      <c r="S1413">
+        <v>27</v>
+      </c>
+      <c r="T1413">
+        <v>3</v>
+      </c>
+      <c r="U1413">
+        <v>21</v>
+      </c>
+      <c r="V1413">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1414" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1414" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1414" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1414" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1414" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1414" t="s">
+        <v>318</v>
+      </c>
+      <c r="H1414">
+        <v>7.02</v>
+      </c>
+      <c r="I1414">
+        <v>0.22</v>
+      </c>
+      <c r="J1414">
+        <v>6.79</v>
+      </c>
+      <c r="K1414">
+        <v>0.22</v>
+      </c>
+      <c r="L1414">
+        <v>0</v>
+      </c>
+      <c r="M1414">
+        <v>0</v>
+      </c>
+      <c r="N1414">
+        <v>0</v>
+      </c>
+      <c r="O1414">
+        <v>0</v>
+      </c>
+      <c r="P1414">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="Q1414">
+        <v>20.05</v>
+      </c>
+      <c r="R1414">
+        <v>4.87</v>
+      </c>
+      <c r="S1414">
+        <v>32</v>
+      </c>
+      <c r="T1414">
+        <v>6</v>
+      </c>
+      <c r="U1414">
+        <v>18</v>
+      </c>
+      <c r="V1414">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1415" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1415" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1415" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1415" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1415" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1415" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H1415">
+        <v>7.78</v>
+      </c>
+      <c r="I1415">
+        <v>0.32</v>
+      </c>
+      <c r="J1415">
+        <v>7.45</v>
+      </c>
+      <c r="K1415">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L1415">
+        <v>0.05</v>
+      </c>
+      <c r="M1415">
+        <v>0</v>
+      </c>
+      <c r="N1415">
+        <v>0</v>
+      </c>
+      <c r="O1415">
+        <v>0</v>
+      </c>
+      <c r="P1415">
+        <v>4.74</v>
+      </c>
+      <c r="Q1415">
+        <v>24.65</v>
+      </c>
+      <c r="R1415">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S1415">
+        <v>40</v>
+      </c>
+      <c r="T1415">
+        <v>4</v>
+      </c>
+      <c r="U1415">
+        <v>25</v>
+      </c>
+      <c r="V1415">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1416" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1416" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1416" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1416" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1416" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1416" t="s">
+        <v>404</v>
+      </c>
+      <c r="H1416">
+        <v>6.91</v>
+      </c>
+      <c r="I1416">
+        <v>0.2</v>
+      </c>
+      <c r="J1416">
+        <v>6.7</v>
+      </c>
+      <c r="K1416">
+        <v>0.19</v>
+      </c>
+      <c r="L1416">
+        <v>0.02</v>
+      </c>
+      <c r="M1416">
+        <v>0</v>
+      </c>
+      <c r="N1416">
+        <v>0</v>
+      </c>
+      <c r="O1416">
+        <v>0</v>
+      </c>
+      <c r="P1416">
+        <v>4.17</v>
+      </c>
+      <c r="Q1416">
+        <v>23.29</v>
+      </c>
+      <c r="R1416">
+        <v>5.2</v>
+      </c>
+      <c r="S1416">
+        <v>43</v>
+      </c>
+      <c r="T1416">
+        <v>16</v>
+      </c>
+      <c r="U1416">
+        <v>38</v>
+      </c>
+      <c r="V1416">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1417" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1417" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1417" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1417" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1417" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1417" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H1417">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="I1417">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J1417">
+        <v>8.08</v>
+      </c>
+      <c r="K1417">
+        <v>0.27</v>
+      </c>
+      <c r="L1417">
+        <v>0.03</v>
+      </c>
+      <c r="M1417">
+        <v>0</v>
+      </c>
+      <c r="N1417">
+        <v>0</v>
+      </c>
+      <c r="O1417">
+        <v>0</v>
+      </c>
+      <c r="P1417">
+        <v>4.87</v>
+      </c>
+      <c r="Q1417">
+        <v>22.4</v>
+      </c>
+      <c r="R1417">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="S1417">
+        <v>25</v>
+      </c>
+      <c r="T1417">
+        <v>2</v>
+      </c>
+      <c r="U1417">
+        <v>30</v>
+      </c>
+      <c r="V1417">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1418" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1418" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1418" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1418" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1418" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1418" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H1418">
+        <v>6.58</v>
+      </c>
+      <c r="I1418">
+        <v>0.48</v>
+      </c>
+      <c r="J1418">
+        <v>6.09</v>
+      </c>
+      <c r="K1418">
+        <v>0.41</v>
+      </c>
+      <c r="L1418">
+        <v>0.08</v>
+      </c>
+      <c r="M1418">
+        <v>0</v>
+      </c>
+      <c r="N1418">
+        <v>0</v>
+      </c>
+      <c r="O1418">
+        <v>0</v>
+      </c>
+      <c r="P1418">
+        <v>3.6</v>
+      </c>
+      <c r="Q1418">
+        <v>23.51</v>
+      </c>
+      <c r="R1418">
+        <v>4.79</v>
+      </c>
+      <c r="S1418">
+        <v>15</v>
+      </c>
+      <c r="T1418">
+        <v>2</v>
+      </c>
+      <c r="U1418">
+        <v>22</v>
+      </c>
+      <c r="V1418">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1419" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1419" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1419" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1419" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1419" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1419" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H1419">
+        <v>7.85</v>
+      </c>
+      <c r="I1419">
+        <v>0.54</v>
+      </c>
+      <c r="J1419">
+        <v>7.31</v>
+      </c>
+      <c r="K1419">
+        <v>0.5</v>
+      </c>
+      <c r="L1419">
+        <v>0.04</v>
+      </c>
+      <c r="M1419">
+        <v>0</v>
+      </c>
+      <c r="N1419">
+        <v>0</v>
+      </c>
+      <c r="O1419">
+        <v>1</v>
+      </c>
+      <c r="P1419">
+        <v>4.17</v>
+      </c>
+      <c r="Q1419">
+        <v>25.25</v>
+      </c>
+      <c r="R1419">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="S1419">
+        <v>28</v>
+      </c>
+      <c r="T1419">
+        <v>3</v>
+      </c>
+      <c r="U1419">
+        <v>18</v>
+      </c>
+      <c r="V1419">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1420" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1420" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1420" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1420" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1420" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1420" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1420" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H1420">
+        <v>6.31</v>
+      </c>
+      <c r="I1420">
+        <v>0.11</v>
+      </c>
+      <c r="J1420">
+        <v>6.19</v>
+      </c>
+      <c r="K1420">
+        <v>0.11</v>
+      </c>
+      <c r="L1420">
+        <v>0.01</v>
+      </c>
+      <c r="M1420">
+        <v>0</v>
+      </c>
+      <c r="N1420">
+        <v>0</v>
+      </c>
+      <c r="O1420">
+        <v>0</v>
+      </c>
+      <c r="P1420">
+        <v>2.85</v>
+      </c>
+      <c r="Q1420">
+        <v>21.86</v>
+      </c>
+      <c r="R1420">
+        <v>4.54</v>
+      </c>
+      <c r="S1420">
+        <v>17</v>
+      </c>
+      <c r="T1420">
+        <v>1</v>
+      </c>
+      <c r="U1420">
+        <v>16</v>
+      </c>
+      <c r="V1420">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1421" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1421" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1421" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1421" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1421" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1421" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1421" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H1421">
+        <v>7.56</v>
+      </c>
+      <c r="I1421">
+        <v>0.67</v>
+      </c>
+      <c r="J1421">
+        <v>6.86</v>
+      </c>
+      <c r="K1421">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L1421">
+        <v>0.13</v>
+      </c>
+      <c r="M1421">
+        <v>0.02</v>
+      </c>
+      <c r="N1421">
+        <v>0</v>
+      </c>
+      <c r="O1421">
+        <v>2</v>
+      </c>
+      <c r="P1421">
+        <v>3.64</v>
+      </c>
+      <c r="Q1421">
+        <v>27.19</v>
+      </c>
+      <c r="R1421">
+        <v>6.15</v>
+      </c>
+      <c r="S1421">
+        <v>91</v>
+      </c>
+      <c r="T1421">
+        <v>25</v>
+      </c>
+      <c r="U1421">
+        <v>99</v>
+      </c>
+      <c r="V1421">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1422" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1422" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1422" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1422" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1422" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1422" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1422" t="s">
+        <v>1186</v>
+      </c>
+      <c r="H1422">
+        <v>7.13</v>
+      </c>
+      <c r="I1422">
+        <v>0.65</v>
+      </c>
+      <c r="J1422">
+        <v>6.46</v>
+      </c>
+      <c r="K1422">
+        <v>0.47</v>
+      </c>
+      <c r="L1422">
+        <v>0.2</v>
+      </c>
+      <c r="M1422">
+        <v>0</v>
+      </c>
+      <c r="N1422">
+        <v>0</v>
+      </c>
+      <c r="O1422">
+        <v>0</v>
+      </c>
+      <c r="P1422">
+        <v>3.65</v>
+      </c>
+      <c r="Q1422">
+        <v>24.91</v>
+      </c>
+      <c r="R1422">
+        <v>5.17</v>
+      </c>
+      <c r="S1422">
+        <v>104</v>
+      </c>
+      <c r="T1422">
+        <v>29</v>
+      </c>
+      <c r="U1422">
+        <v>70</v>
+      </c>
+      <c r="V1422">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1423" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1423" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1423" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1423" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1423" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1423" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1423" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H1423">
+        <v>5.84</v>
+      </c>
+      <c r="I1423">
+        <v>0.51</v>
+      </c>
+      <c r="J1423">
+        <v>5.32</v>
+      </c>
+      <c r="K1423">
+        <v>0.3</v>
+      </c>
+      <c r="L1423">
+        <v>0.17</v>
+      </c>
+      <c r="M1423">
+        <v>0.06</v>
+      </c>
+      <c r="N1423">
+        <v>0</v>
+      </c>
+      <c r="O1423">
+        <v>5</v>
+      </c>
+      <c r="P1423">
+        <v>3.47</v>
+      </c>
+      <c r="Q1423">
+        <v>27.37</v>
+      </c>
+      <c r="R1423">
+        <v>4.62</v>
+      </c>
+      <c r="S1423">
+        <v>26</v>
+      </c>
+      <c r="T1423">
+        <v>12</v>
+      </c>
+      <c r="U1423">
+        <v>8</v>
+      </c>
+      <c r="V1423">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1424" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1424" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1424" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1424" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1424" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1424" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1424" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H1424">
+        <v>7.17</v>
+      </c>
+      <c r="I1424">
+        <v>0.38</v>
+      </c>
+      <c r="J1424">
+        <v>6.78</v>
+      </c>
+      <c r="K1424">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L1424">
+        <v>0.08</v>
+      </c>
+      <c r="M1424">
+        <v>0.02</v>
+      </c>
+      <c r="N1424">
+        <v>0</v>
+      </c>
+      <c r="O1424">
+        <v>2</v>
+      </c>
+      <c r="P1424">
+        <v>3.78</v>
+      </c>
+      <c r="Q1424">
+        <v>27.13</v>
+      </c>
+      <c r="R1424">
+        <v>3.8</v>
+      </c>
+      <c r="S1424">
+        <v>27</v>
+      </c>
+      <c r="T1424">
+        <v>0</v>
+      </c>
+      <c r="U1424">
+        <v>22</v>
+      </c>
+      <c r="V1424">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1425" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1425" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1425" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1425" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1425" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1425" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1425" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H1425">
+        <v>8.92</v>
+      </c>
+      <c r="I1425">
+        <v>0.92</v>
+      </c>
+      <c r="J1425">
+        <v>7.98</v>
+      </c>
+      <c r="K1425">
+        <v>0.8</v>
+      </c>
+      <c r="L1425">
+        <v>0.13</v>
+      </c>
+      <c r="M1425">
+        <v>0.01</v>
+      </c>
+      <c r="N1425">
+        <v>0</v>
+      </c>
+      <c r="O1425">
+        <v>1</v>
+      </c>
+      <c r="P1425">
+        <v>4.82</v>
+      </c>
+      <c r="Q1425">
+        <v>25.72</v>
+      </c>
+      <c r="R1425">
+        <v>4.32</v>
+      </c>
+      <c r="S1425">
+        <v>45</v>
+      </c>
+      <c r="T1425">
+        <v>2</v>
+      </c>
+      <c r="U1425">
+        <v>39</v>
+      </c>
+      <c r="V1425">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1426" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1426" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1426" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1426" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1426" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1426" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1426" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H1426">
+        <v>4.58</v>
+      </c>
+      <c r="I1426">
+        <v>0.21</v>
+      </c>
+      <c r="J1426">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="K1426">
+        <v>0.16</v>
+      </c>
+      <c r="L1426">
+        <v>0.05</v>
+      </c>
+      <c r="M1426">
+        <v>0.01</v>
+      </c>
+      <c r="N1426">
+        <v>0</v>
+      </c>
+      <c r="O1426">
+        <v>1</v>
+      </c>
+      <c r="P1426">
+        <v>3.04</v>
+      </c>
+      <c r="Q1426">
+        <v>27.88</v>
+      </c>
+      <c r="R1426">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="S1426">
+        <v>28</v>
+      </c>
+      <c r="T1426">
+        <v>10</v>
+      </c>
+      <c r="U1426">
+        <v>18</v>
+      </c>
+      <c r="V1426">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1427" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1427" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1427" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1427" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1427" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1427" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1427" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H1427">
+        <v>5.46</v>
+      </c>
+      <c r="I1427">
+        <v>0.16</v>
+      </c>
+      <c r="J1427">
+        <v>5.3</v>
+      </c>
+      <c r="K1427">
+        <v>0.12</v>
+      </c>
+      <c r="L1427">
+        <v>0.04</v>
+      </c>
+      <c r="M1427">
+        <v>0</v>
+      </c>
+      <c r="N1427">
+        <v>0</v>
+      </c>
+      <c r="O1427">
+        <v>1</v>
+      </c>
+      <c r="P1427">
+        <v>2.83</v>
+      </c>
+      <c r="Q1427">
+        <v>25</v>
+      </c>
+      <c r="R1427">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S1427">
+        <v>15</v>
+      </c>
+      <c r="T1427">
+        <v>1</v>
+      </c>
+      <c r="U1427">
+        <v>6</v>
+      </c>
+      <c r="V1427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1428" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1428" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1428" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1428" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1428" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1428" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1428" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H1428">
+        <v>5.85</v>
+      </c>
+      <c r="I1428">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J1428">
+        <v>5.29</v>
+      </c>
+      <c r="K1428">
+        <v>0.25</v>
+      </c>
+      <c r="L1428">
+        <v>0.18</v>
+      </c>
+      <c r="M1428">
+        <v>0.12</v>
+      </c>
+      <c r="N1428">
+        <v>0</v>
+      </c>
+      <c r="O1428">
+        <v>6</v>
+      </c>
+      <c r="P1428">
+        <v>3.15</v>
+      </c>
+      <c r="Q1428">
+        <v>30.12</v>
+      </c>
+      <c r="R1428">
+        <v>3.99</v>
+      </c>
+      <c r="S1428">
+        <v>24</v>
+      </c>
+      <c r="T1428">
+        <v>0</v>
+      </c>
+      <c r="U1428">
+        <v>20</v>
+      </c>
+      <c r="V1428">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1429" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1429" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1429" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1429" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1429" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1429" t="s">
+        <v>894</v>
+      </c>
+      <c r="H1429">
+        <v>6.85</v>
+      </c>
+      <c r="I1429">
+        <v>0.66</v>
+      </c>
+      <c r="J1429">
+        <v>6.18</v>
+      </c>
+      <c r="K1429">
+        <v>0.36</v>
+      </c>
+      <c r="L1429">
+        <v>0.21</v>
+      </c>
+      <c r="M1429">
+        <v>0.1</v>
+      </c>
+      <c r="N1429">
+        <v>0</v>
+      </c>
+      <c r="O1429">
+        <v>10</v>
+      </c>
+      <c r="P1429">
+        <v>3.43</v>
+      </c>
+      <c r="Q1429">
+        <v>29.37</v>
+      </c>
+      <c r="R1429">
+        <v>4.45</v>
+      </c>
+      <c r="S1429">
+        <v>34</v>
+      </c>
+      <c r="T1429">
+        <v>1</v>
+      </c>
+      <c r="U1429">
+        <v>27</v>
+      </c>
+      <c r="V1429">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1430" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1430" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C1430" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1430" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1430" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1430" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1430" t="s">
+        <v>1193</v>
+      </c>
+      <c r="H1430">
+        <v>8.27</v>
+      </c>
+      <c r="I1430">
+        <v>1.22</v>
+      </c>
+      <c r="J1430">
+        <v>7.04</v>
+      </c>
+      <c r="K1430">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L1430">
+        <v>0.47</v>
+      </c>
+      <c r="M1430">
+        <v>0.18</v>
+      </c>
+      <c r="N1430">
+        <v>0</v>
+      </c>
+      <c r="O1430">
+        <v>15</v>
+      </c>
+      <c r="P1430">
+        <v>4.46</v>
+      </c>
+      <c r="Q1430">
+        <v>27.92</v>
+      </c>
+      <c r="R1430">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="S1430">
+        <v>41</v>
+      </c>
+      <c r="T1430">
+        <v>8</v>
+      </c>
+      <c r="U1430">
+        <v>26</v>
+      </c>
+      <c r="V1430">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481400E5-5D54-AA41-9AD4-63E660021264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE95BE24-5295-7148-A12A-9DBACDB08227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8096" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8210" uniqueCount="1208">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3618,6 +3618,48 @@
   </si>
   <si>
     <t>01:50:01</t>
+  </si>
+  <si>
+    <t>01:14:35</t>
+  </si>
+  <si>
+    <t>01:14:27</t>
+  </si>
+  <si>
+    <t>01:15:09</t>
+  </si>
+  <si>
+    <t>01:02:06</t>
+  </si>
+  <si>
+    <t>01:40:36</t>
+  </si>
+  <si>
+    <t>01:15:54</t>
+  </si>
+  <si>
+    <t>01:12:15</t>
+  </si>
+  <si>
+    <t>01:38:09</t>
+  </si>
+  <si>
+    <t>00:27:15</t>
+  </si>
+  <si>
+    <t>01:11:23</t>
+  </si>
+  <si>
+    <t>00:47:18</t>
+  </si>
+  <si>
+    <t>00:26:46</t>
+  </si>
+  <si>
+    <t>00:49:16</t>
+  </si>
+  <si>
+    <t>N3 J18 VS Riviera</t>
   </si>
 </sst>
 </file>
@@ -4021,7 +4063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1430"/>
+  <dimension ref="A1:V1449"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -99773,6 +99815,1298 @@
         <v>6</v>
       </c>
     </row>
+    <row r="1431" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1431" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1431" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C1431" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1431" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1431" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1431" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1431" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H1431">
+        <v>5.97</v>
+      </c>
+      <c r="I1431">
+        <v>0.19</v>
+      </c>
+      <c r="J1431">
+        <v>5.77</v>
+      </c>
+      <c r="K1431">
+        <v>0.17</v>
+      </c>
+      <c r="L1431">
+        <v>0.03</v>
+      </c>
+      <c r="M1431">
+        <v>0</v>
+      </c>
+      <c r="N1431">
+        <v>0</v>
+      </c>
+      <c r="O1431">
+        <v>1</v>
+      </c>
+      <c r="P1431">
+        <v>4.29</v>
+      </c>
+      <c r="Q1431">
+        <v>27.01</v>
+      </c>
+      <c r="R1431">
+        <v>5.86</v>
+      </c>
+      <c r="S1431">
+        <v>47</v>
+      </c>
+      <c r="T1431">
+        <v>10</v>
+      </c>
+      <c r="U1431">
+        <v>25</v>
+      </c>
+      <c r="V1431">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1432" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1432" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C1432" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1432" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1432" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1432" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1432" t="s">
+        <v>937</v>
+      </c>
+      <c r="H1432">
+        <v>5.97</v>
+      </c>
+      <c r="I1432">
+        <v>0.24</v>
+      </c>
+      <c r="J1432">
+        <v>5.72</v>
+      </c>
+      <c r="K1432">
+        <v>0.22</v>
+      </c>
+      <c r="L1432">
+        <v>0.03</v>
+      </c>
+      <c r="M1432">
+        <v>0</v>
+      </c>
+      <c r="N1432">
+        <v>0</v>
+      </c>
+      <c r="O1432">
+        <v>0</v>
+      </c>
+      <c r="P1432">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q1432">
+        <v>22.42</v>
+      </c>
+      <c r="R1432">
+        <v>5.33</v>
+      </c>
+      <c r="S1432">
+        <v>67</v>
+      </c>
+      <c r="T1432">
+        <v>13</v>
+      </c>
+      <c r="U1432">
+        <v>54</v>
+      </c>
+      <c r="V1432">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1433" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1433" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C1433" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1433" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1433" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1433" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1433" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H1433">
+        <v>5.45</v>
+      </c>
+      <c r="I1433">
+        <v>0.23</v>
+      </c>
+      <c r="J1433">
+        <v>5.21</v>
+      </c>
+      <c r="K1433">
+        <v>0.18</v>
+      </c>
+      <c r="L1433">
+        <v>0.06</v>
+      </c>
+      <c r="M1433">
+        <v>0.01</v>
+      </c>
+      <c r="N1433">
+        <v>0</v>
+      </c>
+      <c r="O1433">
+        <v>1</v>
+      </c>
+      <c r="P1433">
+        <v>3.91</v>
+      </c>
+      <c r="Q1433">
+        <v>26.83</v>
+      </c>
+      <c r="R1433">
+        <v>4.62</v>
+      </c>
+      <c r="S1433">
+        <v>23</v>
+      </c>
+      <c r="T1433">
+        <v>2</v>
+      </c>
+      <c r="U1433">
+        <v>12</v>
+      </c>
+      <c r="V1433">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1434" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1434" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C1434" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1434" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1434" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1434" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1434" t="s">
+        <v>855</v>
+      </c>
+      <c r="H1434">
+        <v>6.15</v>
+      </c>
+      <c r="I1434">
+        <v>0.33</v>
+      </c>
+      <c r="J1434">
+        <v>5.81</v>
+      </c>
+      <c r="K1434">
+        <v>0.27</v>
+      </c>
+      <c r="L1434">
+        <v>0.06</v>
+      </c>
+      <c r="M1434">
+        <v>0.01</v>
+      </c>
+      <c r="N1434">
+        <v>0</v>
+      </c>
+      <c r="O1434">
+        <v>1</v>
+      </c>
+      <c r="P1434">
+        <v>4.83</v>
+      </c>
+      <c r="Q1434">
+        <v>26.12</v>
+      </c>
+      <c r="R1434">
+        <v>5.07</v>
+      </c>
+      <c r="S1434">
+        <v>17</v>
+      </c>
+      <c r="T1434">
+        <v>5</v>
+      </c>
+      <c r="U1434">
+        <v>7</v>
+      </c>
+      <c r="V1434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1435" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1435" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C1435" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1435" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1435" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1435" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1435" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H1435">
+        <v>6.22</v>
+      </c>
+      <c r="I1435">
+        <v>0.45</v>
+      </c>
+      <c r="J1435">
+        <v>5.76</v>
+      </c>
+      <c r="K1435">
+        <v>0.37</v>
+      </c>
+      <c r="L1435">
+        <v>0.09</v>
+      </c>
+      <c r="M1435">
+        <v>0</v>
+      </c>
+      <c r="N1435">
+        <v>0</v>
+      </c>
+      <c r="O1435">
+        <v>0</v>
+      </c>
+      <c r="P1435">
+        <v>4.92</v>
+      </c>
+      <c r="Q1435">
+        <v>23.95</v>
+      </c>
+      <c r="R1435">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S1435">
+        <v>31</v>
+      </c>
+      <c r="T1435">
+        <v>7</v>
+      </c>
+      <c r="U1435">
+        <v>17</v>
+      </c>
+      <c r="V1435">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1436" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1436" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C1436" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1436" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1436" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1436" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1436" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H1436">
+        <v>4.55</v>
+      </c>
+      <c r="I1436">
+        <v>0.22</v>
+      </c>
+      <c r="J1436">
+        <v>4.32</v>
+      </c>
+      <c r="K1436">
+        <v>0.18</v>
+      </c>
+      <c r="L1436">
+        <v>0.05</v>
+      </c>
+      <c r="M1436">
+        <v>0.01</v>
+      </c>
+      <c r="N1436">
+        <v>0</v>
+      </c>
+      <c r="O1436">
+        <v>3</v>
+      </c>
+      <c r="P1436">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="Q1436">
+        <v>26.28</v>
+      </c>
+      <c r="R1436">
+        <v>5.73</v>
+      </c>
+      <c r="S1436">
+        <v>64</v>
+      </c>
+      <c r="T1436">
+        <v>26</v>
+      </c>
+      <c r="U1436">
+        <v>35</v>
+      </c>
+      <c r="V1436">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1437" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1437" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1437" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1437" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1437" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1437" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1437" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H1437">
+        <v>10.28</v>
+      </c>
+      <c r="I1437">
+        <v>1.9</v>
+      </c>
+      <c r="J1437">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="K1437">
+        <v>1.26</v>
+      </c>
+      <c r="L1437">
+        <v>0.54</v>
+      </c>
+      <c r="M1437">
+        <v>0.11</v>
+      </c>
+      <c r="N1437">
+        <v>0</v>
+      </c>
+      <c r="O1437">
+        <v>8</v>
+      </c>
+      <c r="P1437">
+        <v>5.95</v>
+      </c>
+      <c r="Q1437">
+        <v>29.62</v>
+      </c>
+      <c r="R1437">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S1437">
+        <v>46</v>
+      </c>
+      <c r="T1437">
+        <v>5</v>
+      </c>
+      <c r="U1437">
+        <v>26</v>
+      </c>
+      <c r="V1437">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1438" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1438" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1438" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1438" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1438" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1438" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1438" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H1438">
+        <v>8.98</v>
+      </c>
+      <c r="I1438">
+        <v>1.92</v>
+      </c>
+      <c r="J1438">
+        <v>7.04</v>
+      </c>
+      <c r="K1438">
+        <v>1.44</v>
+      </c>
+      <c r="L1438">
+        <v>0.41</v>
+      </c>
+      <c r="M1438">
+        <v>0.09</v>
+      </c>
+      <c r="N1438">
+        <v>0</v>
+      </c>
+      <c r="O1438">
+        <v>7</v>
+      </c>
+      <c r="P1438">
+        <v>7</v>
+      </c>
+      <c r="Q1438">
+        <v>28.31</v>
+      </c>
+      <c r="R1438">
+        <v>4.57</v>
+      </c>
+      <c r="S1438">
+        <v>38</v>
+      </c>
+      <c r="T1438">
+        <v>2</v>
+      </c>
+      <c r="U1438">
+        <v>35</v>
+      </c>
+      <c r="V1438">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1439" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1439" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1439" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1439" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1439" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1439" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1439" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H1439">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="I1439">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="J1439">
+        <v>6.5</v>
+      </c>
+      <c r="K1439">
+        <v>1.42</v>
+      </c>
+      <c r="L1439">
+        <v>0.63</v>
+      </c>
+      <c r="M1439">
+        <v>0.15</v>
+      </c>
+      <c r="N1439">
+        <v>0</v>
+      </c>
+      <c r="O1439">
+        <v>6</v>
+      </c>
+      <c r="P1439">
+        <v>7.08</v>
+      </c>
+      <c r="Q1439">
+        <v>28.88</v>
+      </c>
+      <c r="R1439">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="S1439">
+        <v>51</v>
+      </c>
+      <c r="T1439">
+        <v>8</v>
+      </c>
+      <c r="U1439">
+        <v>28</v>
+      </c>
+      <c r="V1439">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1440" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1440" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1440" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1440" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1440" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1440" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1440" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H1440">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="I1440">
+        <v>1.55</v>
+      </c>
+      <c r="J1440">
+        <v>8.4</v>
+      </c>
+      <c r="K1440">
+        <v>1</v>
+      </c>
+      <c r="L1440">
+        <v>0.47</v>
+      </c>
+      <c r="M1440">
+        <v>0.09</v>
+      </c>
+      <c r="N1440">
+        <v>0</v>
+      </c>
+      <c r="O1440">
+        <v>8</v>
+      </c>
+      <c r="P1440">
+        <v>5.84</v>
+      </c>
+      <c r="Q1440">
+        <v>29.3</v>
+      </c>
+      <c r="R1440">
+        <v>4.47</v>
+      </c>
+      <c r="S1440">
+        <v>34</v>
+      </c>
+      <c r="T1440">
+        <v>2</v>
+      </c>
+      <c r="U1440">
+        <v>21</v>
+      </c>
+      <c r="V1440">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1441" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1441" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1441" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1441" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1441" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1441" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1441" t="s">
+        <v>1201</v>
+      </c>
+      <c r="H1441">
+        <v>10.58</v>
+      </c>
+      <c r="I1441">
+        <v>1.59</v>
+      </c>
+      <c r="J1441">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="K1441">
+        <v>1.2</v>
+      </c>
+      <c r="L1441">
+        <v>0.35</v>
+      </c>
+      <c r="M1441">
+        <v>0.06</v>
+      </c>
+      <c r="N1441">
+        <v>0</v>
+      </c>
+      <c r="O1441">
+        <v>5</v>
+      </c>
+      <c r="P1441">
+        <v>6.45</v>
+      </c>
+      <c r="Q1441">
+        <v>28.87</v>
+      </c>
+      <c r="R1441">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="S1441">
+        <v>30</v>
+      </c>
+      <c r="T1441">
+        <v>9</v>
+      </c>
+      <c r="U1441">
+        <v>30</v>
+      </c>
+      <c r="V1441">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1442" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1442" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1442" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1442" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1442" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1442" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1442" t="s">
+        <v>907</v>
+      </c>
+      <c r="H1442">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="I1442">
+        <v>1.94</v>
+      </c>
+      <c r="J1442">
+        <v>8.09</v>
+      </c>
+      <c r="K1442">
+        <v>1.2</v>
+      </c>
+      <c r="L1442">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M1442">
+        <v>0.18</v>
+      </c>
+      <c r="N1442">
+        <v>0</v>
+      </c>
+      <c r="O1442">
+        <v>13</v>
+      </c>
+      <c r="P1442">
+        <v>5.94</v>
+      </c>
+      <c r="Q1442">
+        <v>29.81</v>
+      </c>
+      <c r="R1442">
+        <v>4.79</v>
+      </c>
+      <c r="S1442">
+        <v>30</v>
+      </c>
+      <c r="T1442">
+        <v>13</v>
+      </c>
+      <c r="U1442">
+        <v>27</v>
+      </c>
+      <c r="V1442">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1443" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1443" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1443" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1443" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1443" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1443" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1443" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H1443">
+        <v>3.46</v>
+      </c>
+      <c r="I1443">
+        <v>0.97</v>
+      </c>
+      <c r="J1443">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="K1443">
+        <v>0.75</v>
+      </c>
+      <c r="L1443">
+        <v>0.2</v>
+      </c>
+      <c r="M1443">
+        <v>0.04</v>
+      </c>
+      <c r="N1443">
+        <v>0</v>
+      </c>
+      <c r="O1443">
+        <v>4</v>
+      </c>
+      <c r="P1443">
+        <v>7.58</v>
+      </c>
+      <c r="Q1443">
+        <v>28.02</v>
+      </c>
+      <c r="R1443">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="S1443">
+        <v>19</v>
+      </c>
+      <c r="T1443">
+        <v>1</v>
+      </c>
+      <c r="U1443">
+        <v>11</v>
+      </c>
+      <c r="V1443">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1444" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1444" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1444" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1444" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1444" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1444" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1444" t="s">
+        <v>623</v>
+      </c>
+      <c r="H1444">
+        <v>11.36</v>
+      </c>
+      <c r="I1444">
+        <v>1.89</v>
+      </c>
+      <c r="J1444">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="K1444">
+        <v>1.33</v>
+      </c>
+      <c r="L1444">
+        <v>0.52</v>
+      </c>
+      <c r="M1444">
+        <v>0.06</v>
+      </c>
+      <c r="N1444">
+        <v>0</v>
+      </c>
+      <c r="O1444">
+        <v>5</v>
+      </c>
+      <c r="P1444">
+        <v>6.63</v>
+      </c>
+      <c r="Q1444">
+        <v>27.51</v>
+      </c>
+      <c r="R1444">
+        <v>4.29</v>
+      </c>
+      <c r="S1444">
+        <v>34</v>
+      </c>
+      <c r="T1444">
+        <v>3</v>
+      </c>
+      <c r="U1444">
+        <v>35</v>
+      </c>
+      <c r="V1444">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1445" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1445" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1445" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1445" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1445" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1445" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1445" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H1445">
+        <v>7.4</v>
+      </c>
+      <c r="I1445">
+        <v>1.38</v>
+      </c>
+      <c r="J1445">
+        <v>5.99</v>
+      </c>
+      <c r="K1445">
+        <v>0.97</v>
+      </c>
+      <c r="L1445">
+        <v>0.34</v>
+      </c>
+      <c r="M1445">
+        <v>0.1</v>
+      </c>
+      <c r="N1445">
+        <v>0</v>
+      </c>
+      <c r="O1445">
+        <v>8</v>
+      </c>
+      <c r="P1445">
+        <v>6.1</v>
+      </c>
+      <c r="Q1445">
+        <v>28.65</v>
+      </c>
+      <c r="R1445">
+        <v>4.07</v>
+      </c>
+      <c r="S1445">
+        <v>26</v>
+      </c>
+      <c r="T1445">
+        <v>1</v>
+      </c>
+      <c r="U1445">
+        <v>21</v>
+      </c>
+      <c r="V1445">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1446" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1446" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1446" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1446" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1446" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1446" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1446" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H1446">
+        <v>5.56</v>
+      </c>
+      <c r="I1446">
+        <v>1.34</v>
+      </c>
+      <c r="J1446">
+        <v>4.2</v>
+      </c>
+      <c r="K1446">
+        <v>0.85</v>
+      </c>
+      <c r="L1446">
+        <v>0.38</v>
+      </c>
+      <c r="M1446">
+        <v>0.12</v>
+      </c>
+      <c r="N1446">
+        <v>0.01</v>
+      </c>
+      <c r="O1446">
+        <v>7</v>
+      </c>
+      <c r="P1446">
+        <v>7.05</v>
+      </c>
+      <c r="Q1446">
+        <v>30.2</v>
+      </c>
+      <c r="R1446">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S1446">
+        <v>36</v>
+      </c>
+      <c r="T1446">
+        <v>10</v>
+      </c>
+      <c r="U1446">
+        <v>18</v>
+      </c>
+      <c r="V1446">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1447" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1447" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1447" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1447" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1447" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1447" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1447" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H1447">
+        <v>2.84</v>
+      </c>
+      <c r="I1447">
+        <v>0.81</v>
+      </c>
+      <c r="J1447">
+        <v>2.02</v>
+      </c>
+      <c r="K1447">
+        <v>0.37</v>
+      </c>
+      <c r="L1447">
+        <v>0.25</v>
+      </c>
+      <c r="M1447">
+        <v>0.2</v>
+      </c>
+      <c r="N1447">
+        <v>0</v>
+      </c>
+      <c r="O1447">
+        <v>9</v>
+      </c>
+      <c r="P1447">
+        <v>6.34</v>
+      </c>
+      <c r="Q1447">
+        <v>29.48</v>
+      </c>
+      <c r="R1447">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="S1447">
+        <v>13</v>
+      </c>
+      <c r="T1447">
+        <v>3</v>
+      </c>
+      <c r="U1447">
+        <v>17</v>
+      </c>
+      <c r="V1447">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1448" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1448" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1448" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1448" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1448" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1448" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1448" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H1448">
+        <v>11.65</v>
+      </c>
+      <c r="I1448">
+        <v>2.46</v>
+      </c>
+      <c r="J1448">
+        <v>9.17</v>
+      </c>
+      <c r="K1448">
+        <v>1.67</v>
+      </c>
+      <c r="L1448">
+        <v>0.62</v>
+      </c>
+      <c r="M1448">
+        <v>0.18</v>
+      </c>
+      <c r="N1448">
+        <v>0.01</v>
+      </c>
+      <c r="O1448">
+        <v>14</v>
+      </c>
+      <c r="P1448">
+        <v>6.83</v>
+      </c>
+      <c r="Q1448">
+        <v>30.78</v>
+      </c>
+      <c r="R1448">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S1448">
+        <v>37</v>
+      </c>
+      <c r="T1448">
+        <v>8</v>
+      </c>
+      <c r="U1448">
+        <v>34</v>
+      </c>
+      <c r="V1448">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1449" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1449" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C1449" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1449" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1449" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1449" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1449" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H1449">
+        <v>5.91</v>
+      </c>
+      <c r="I1449">
+        <v>1.31</v>
+      </c>
+      <c r="J1449">
+        <v>4.59</v>
+      </c>
+      <c r="K1449">
+        <v>0.89</v>
+      </c>
+      <c r="L1449">
+        <v>0.3</v>
+      </c>
+      <c r="M1449">
+        <v>0.1</v>
+      </c>
+      <c r="N1449">
+        <v>0.03</v>
+      </c>
+      <c r="O1449">
+        <v>8</v>
+      </c>
+      <c r="P1449">
+        <v>6.75</v>
+      </c>
+      <c r="Q1449">
+        <v>31.32</v>
+      </c>
+      <c r="R1449">
+        <v>4.95</v>
+      </c>
+      <c r="S1449">
+        <v>29</v>
+      </c>
+      <c r="T1449">
+        <v>4</v>
+      </c>
+      <c r="U1449">
+        <v>24</v>
+      </c>
+      <c r="V1449">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE95BE24-5295-7148-A12A-9DBACDB08227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17767789-A423-5948-82A6-546AC6FE02C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8210" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8322" uniqueCount="1223">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3660,6 +3660,51 @@
   </si>
   <si>
     <t>N3 J18 VS Riviera</t>
+  </si>
+  <si>
+    <t>01:54:10</t>
+  </si>
+  <si>
+    <t>01:53:16</t>
+  </si>
+  <si>
+    <t>01:52:49</t>
+  </si>
+  <si>
+    <t>01:50:43</t>
+  </si>
+  <si>
+    <t>01:51:18</t>
+  </si>
+  <si>
+    <t>01:53:43</t>
+  </si>
+  <si>
+    <t>01:30:48</t>
+  </si>
+  <si>
+    <t>01:31:20</t>
+  </si>
+  <si>
+    <t>01:31:12</t>
+  </si>
+  <si>
+    <t>01:30:16</t>
+  </si>
+  <si>
+    <t>00:55:39</t>
+  </si>
+  <si>
+    <t>01:30:56</t>
+  </si>
+  <si>
+    <t>01:27:52</t>
+  </si>
+  <si>
+    <t>00:49:48</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
   </si>
 </sst>
 </file>
@@ -4063,7 +4108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1449"/>
+  <dimension ref="A1:V1470"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -101107,6 +101152,1392 @@
         <v>13</v>
       </c>
     </row>
+    <row r="1450" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1450" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1450" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C1450" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1450" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1450" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1450" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1450" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H1450">
+        <v>10.63</v>
+      </c>
+      <c r="I1450">
+        <v>1.51</v>
+      </c>
+      <c r="J1450">
+        <v>9.09</v>
+      </c>
+      <c r="K1450">
+        <v>1.21</v>
+      </c>
+      <c r="L1450">
+        <v>0.34</v>
+      </c>
+      <c r="M1450">
+        <v>0</v>
+      </c>
+      <c r="N1450">
+        <v>0</v>
+      </c>
+      <c r="O1450">
+        <v>0</v>
+      </c>
+      <c r="P1450">
+        <v>5.12</v>
+      </c>
+      <c r="Q1450">
+        <v>24.07</v>
+      </c>
+      <c r="R1450">
+        <v>5.31</v>
+      </c>
+      <c r="S1450">
+        <v>101</v>
+      </c>
+      <c r="T1450">
+        <v>31</v>
+      </c>
+      <c r="U1450">
+        <v>68</v>
+      </c>
+      <c r="V1450">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1451" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1451" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C1451" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1451" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1451" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1451" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1451" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1451">
+        <v>7.99</v>
+      </c>
+      <c r="I1451">
+        <v>0.96</v>
+      </c>
+      <c r="J1451">
+        <v>7.02</v>
+      </c>
+      <c r="K1451">
+        <v>0.85</v>
+      </c>
+      <c r="L1451">
+        <v>0.12</v>
+      </c>
+      <c r="M1451">
+        <v>0</v>
+      </c>
+      <c r="N1451">
+        <v>0</v>
+      </c>
+      <c r="O1451">
+        <v>0</v>
+      </c>
+      <c r="P1451">
+        <v>4.75</v>
+      </c>
+      <c r="Q1451">
+        <v>24.99</v>
+      </c>
+      <c r="R1451">
+        <v>4.83</v>
+      </c>
+      <c r="S1451">
+        <v>74</v>
+      </c>
+      <c r="T1451">
+        <v>15</v>
+      </c>
+      <c r="U1451">
+        <v>55</v>
+      </c>
+      <c r="V1451">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1452" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1452" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C1452" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1452" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1452" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1452" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1452" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1452">
+        <v>11.22</v>
+      </c>
+      <c r="I1452">
+        <v>1.66</v>
+      </c>
+      <c r="J1452">
+        <v>9.52</v>
+      </c>
+      <c r="K1452">
+        <v>1.33</v>
+      </c>
+      <c r="L1452">
+        <v>0.37</v>
+      </c>
+      <c r="M1452">
+        <v>0</v>
+      </c>
+      <c r="N1452">
+        <v>0</v>
+      </c>
+      <c r="O1452">
+        <v>0</v>
+      </c>
+      <c r="P1452">
+        <v>5.59</v>
+      </c>
+      <c r="Q1452">
+        <v>24.68</v>
+      </c>
+      <c r="R1452">
+        <v>6</v>
+      </c>
+      <c r="S1452">
+        <v>103</v>
+      </c>
+      <c r="T1452">
+        <v>39</v>
+      </c>
+      <c r="U1452">
+        <v>66</v>
+      </c>
+      <c r="V1452">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1453" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1453" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C1453" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1453" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1453" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1453" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1453" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H1453">
+        <v>8.33</v>
+      </c>
+      <c r="I1453">
+        <v>0.84</v>
+      </c>
+      <c r="J1453">
+        <v>7.46</v>
+      </c>
+      <c r="K1453">
+        <v>0.65</v>
+      </c>
+      <c r="L1453">
+        <v>0.21</v>
+      </c>
+      <c r="M1453">
+        <v>0</v>
+      </c>
+      <c r="N1453">
+        <v>0</v>
+      </c>
+      <c r="O1453">
+        <v>0</v>
+      </c>
+      <c r="P1453">
+        <v>3.83</v>
+      </c>
+      <c r="Q1453">
+        <v>24.97</v>
+      </c>
+      <c r="R1453">
+        <v>5.01</v>
+      </c>
+      <c r="S1453">
+        <v>60</v>
+      </c>
+      <c r="T1453">
+        <v>22</v>
+      </c>
+      <c r="U1453">
+        <v>51</v>
+      </c>
+      <c r="V1453">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1454" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1454" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C1454" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1454" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1454" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1454" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1454" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H1454">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="I1454">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="J1454">
+        <v>8.41</v>
+      </c>
+      <c r="K1454">
+        <v>1.05</v>
+      </c>
+      <c r="L1454">
+        <v>0.08</v>
+      </c>
+      <c r="M1454">
+        <v>0</v>
+      </c>
+      <c r="N1454">
+        <v>0</v>
+      </c>
+      <c r="O1454">
+        <v>0</v>
+      </c>
+      <c r="P1454">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Q1454">
+        <v>22.85</v>
+      </c>
+      <c r="R1454">
+        <v>4.62</v>
+      </c>
+      <c r="S1454">
+        <v>60</v>
+      </c>
+      <c r="T1454">
+        <v>12</v>
+      </c>
+      <c r="U1454">
+        <v>54</v>
+      </c>
+      <c r="V1454">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1455" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1455" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C1455" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1455" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1455" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1455" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1455" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H1455">
+        <v>8.98</v>
+      </c>
+      <c r="I1455">
+        <v>1.26</v>
+      </c>
+      <c r="J1455">
+        <v>7.71</v>
+      </c>
+      <c r="K1455">
+        <v>1.2</v>
+      </c>
+      <c r="L1455">
+        <v>0.08</v>
+      </c>
+      <c r="M1455">
+        <v>0</v>
+      </c>
+      <c r="N1455">
+        <v>0</v>
+      </c>
+      <c r="O1455">
+        <v>0</v>
+      </c>
+      <c r="P1455">
+        <v>4.75</v>
+      </c>
+      <c r="Q1455">
+        <v>22.77</v>
+      </c>
+      <c r="R1455">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="S1455">
+        <v>73</v>
+      </c>
+      <c r="T1455">
+        <v>5</v>
+      </c>
+      <c r="U1455">
+        <v>40</v>
+      </c>
+      <c r="V1455">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1456" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1456" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C1456" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1456" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1456" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1456" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1456" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H1456">
+        <v>10.38</v>
+      </c>
+      <c r="I1456">
+        <v>1.22</v>
+      </c>
+      <c r="J1456">
+        <v>9.15</v>
+      </c>
+      <c r="K1456">
+        <v>1.22</v>
+      </c>
+      <c r="L1456">
+        <v>0.01</v>
+      </c>
+      <c r="M1456">
+        <v>0</v>
+      </c>
+      <c r="N1456">
+        <v>0</v>
+      </c>
+      <c r="O1456">
+        <v>0</v>
+      </c>
+      <c r="P1456">
+        <v>5.42</v>
+      </c>
+      <c r="Q1456">
+        <v>20.36</v>
+      </c>
+      <c r="R1456">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S1456">
+        <v>58</v>
+      </c>
+      <c r="T1456">
+        <v>5</v>
+      </c>
+      <c r="U1456">
+        <v>30</v>
+      </c>
+      <c r="V1456">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1457" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1457" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1457" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1457" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1457" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1457" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H1457">
+        <v>7.16</v>
+      </c>
+      <c r="I1457">
+        <v>1.28</v>
+      </c>
+      <c r="J1457">
+        <v>5.87</v>
+      </c>
+      <c r="K1457">
+        <v>0.71</v>
+      </c>
+      <c r="L1457">
+        <v>0.37</v>
+      </c>
+      <c r="M1457">
+        <v>0.19</v>
+      </c>
+      <c r="N1457">
+        <v>0.02</v>
+      </c>
+      <c r="O1457">
+        <v>10</v>
+      </c>
+      <c r="P1457">
+        <v>4.7</v>
+      </c>
+      <c r="Q1457">
+        <v>31.19</v>
+      </c>
+      <c r="R1457">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S1457">
+        <v>37</v>
+      </c>
+      <c r="T1457">
+        <v>4</v>
+      </c>
+      <c r="U1457">
+        <v>19</v>
+      </c>
+      <c r="V1457">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1458" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1458" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1458" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1458" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1458" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1458" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H1458">
+        <v>5.52</v>
+      </c>
+      <c r="I1458">
+        <v>0.45</v>
+      </c>
+      <c r="J1458">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="K1458">
+        <v>0.32</v>
+      </c>
+      <c r="L1458">
+        <v>0.1</v>
+      </c>
+      <c r="M1458">
+        <v>0.03</v>
+      </c>
+      <c r="N1458">
+        <v>0.01</v>
+      </c>
+      <c r="O1458">
+        <v>2</v>
+      </c>
+      <c r="P1458">
+        <v>3.49</v>
+      </c>
+      <c r="Q1458">
+        <v>30.41</v>
+      </c>
+      <c r="R1458">
+        <v>4.63</v>
+      </c>
+      <c r="S1458">
+        <v>20</v>
+      </c>
+      <c r="T1458">
+        <v>3</v>
+      </c>
+      <c r="U1458">
+        <v>5</v>
+      </c>
+      <c r="V1458">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1459" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1459" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1459" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1459" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1459" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1459" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H1459">
+        <v>7.49</v>
+      </c>
+      <c r="I1459">
+        <v>1.29</v>
+      </c>
+      <c r="J1459">
+        <v>6.18</v>
+      </c>
+      <c r="K1459">
+        <v>0.89</v>
+      </c>
+      <c r="L1459">
+        <v>0.4</v>
+      </c>
+      <c r="M1459">
+        <v>0.03</v>
+      </c>
+      <c r="N1459">
+        <v>0</v>
+      </c>
+      <c r="O1459">
+        <v>4</v>
+      </c>
+      <c r="P1459">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="Q1459">
+        <v>26.56</v>
+      </c>
+      <c r="R1459">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="S1459">
+        <v>40</v>
+      </c>
+      <c r="T1459">
+        <v>5</v>
+      </c>
+      <c r="U1459">
+        <v>27</v>
+      </c>
+      <c r="V1459">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1460" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1460" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1460" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1460" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1460" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H1460">
+        <v>7.04</v>
+      </c>
+      <c r="I1460">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="J1460">
+        <v>5.91</v>
+      </c>
+      <c r="K1460">
+        <v>0.64</v>
+      </c>
+      <c r="L1460">
+        <v>0.43</v>
+      </c>
+      <c r="M1460">
+        <v>0.06</v>
+      </c>
+      <c r="N1460">
+        <v>0</v>
+      </c>
+      <c r="O1460">
+        <v>9</v>
+      </c>
+      <c r="P1460">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="Q1460">
+        <v>28.77</v>
+      </c>
+      <c r="R1460">
+        <v>4.84</v>
+      </c>
+      <c r="S1460">
+        <v>86</v>
+      </c>
+      <c r="T1460">
+        <v>13</v>
+      </c>
+      <c r="U1460">
+        <v>45</v>
+      </c>
+      <c r="V1460">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1461" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1461" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1461" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1461" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1461" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H1461">
+        <v>6.21</v>
+      </c>
+      <c r="I1461">
+        <v>0.86</v>
+      </c>
+      <c r="J1461">
+        <v>5.33</v>
+      </c>
+      <c r="K1461">
+        <v>0.43</v>
+      </c>
+      <c r="L1461">
+        <v>0.2</v>
+      </c>
+      <c r="M1461">
+        <v>0.2</v>
+      </c>
+      <c r="N1461">
+        <v>0.04</v>
+      </c>
+      <c r="O1461">
+        <v>10</v>
+      </c>
+      <c r="P1461">
+        <v>3.73</v>
+      </c>
+      <c r="Q1461">
+        <v>31.73</v>
+      </c>
+      <c r="R1461">
+        <v>4.8</v>
+      </c>
+      <c r="S1461">
+        <v>45</v>
+      </c>
+      <c r="T1461">
+        <v>10</v>
+      </c>
+      <c r="U1461">
+        <v>34</v>
+      </c>
+      <c r="V1461">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1462" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1462" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1462" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1462" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1462" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H1462">
+        <v>6.5</v>
+      </c>
+      <c r="I1462">
+        <v>0.4</v>
+      </c>
+      <c r="J1462">
+        <v>6.09</v>
+      </c>
+      <c r="K1462">
+        <v>0.25</v>
+      </c>
+      <c r="L1462">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M1462">
+        <v>0.03</v>
+      </c>
+      <c r="N1462">
+        <v>0</v>
+      </c>
+      <c r="O1462">
+        <v>6</v>
+      </c>
+      <c r="P1462">
+        <v>3.28</v>
+      </c>
+      <c r="Q1462">
+        <v>31.06</v>
+      </c>
+      <c r="R1462">
+        <v>5.24</v>
+      </c>
+      <c r="S1462">
+        <v>10</v>
+      </c>
+      <c r="T1462">
+        <v>7</v>
+      </c>
+      <c r="U1462">
+        <v>14</v>
+      </c>
+      <c r="V1462">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1463" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1463" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1463" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1463" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1463" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H1463">
+        <v>6.82</v>
+      </c>
+      <c r="I1463">
+        <v>0.7</v>
+      </c>
+      <c r="J1463">
+        <v>6.11</v>
+      </c>
+      <c r="K1463">
+        <v>0.49</v>
+      </c>
+      <c r="L1463">
+        <v>0.22</v>
+      </c>
+      <c r="M1463">
+        <v>0.01</v>
+      </c>
+      <c r="N1463">
+        <v>0</v>
+      </c>
+      <c r="O1463">
+        <v>2</v>
+      </c>
+      <c r="P1463">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="Q1463">
+        <v>25.56</v>
+      </c>
+      <c r="R1463">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S1463">
+        <v>22</v>
+      </c>
+      <c r="T1463">
+        <v>5</v>
+      </c>
+      <c r="U1463">
+        <v>7</v>
+      </c>
+      <c r="V1463">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1464" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1464" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1464" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="F1464" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1464" t="s">
+        <v>1219</v>
+      </c>
+      <c r="H1464">
+        <v>7.82</v>
+      </c>
+      <c r="I1464">
+        <v>0.6</v>
+      </c>
+      <c r="J1464">
+        <v>7.2</v>
+      </c>
+      <c r="K1464">
+        <v>0.32</v>
+      </c>
+      <c r="L1464">
+        <v>0.17</v>
+      </c>
+      <c r="M1464">
+        <v>0.09</v>
+      </c>
+      <c r="N1464">
+        <v>0.04</v>
+      </c>
+      <c r="O1464">
+        <v>7</v>
+      </c>
+      <c r="P1464">
+        <v>3.63</v>
+      </c>
+      <c r="Q1464">
+        <v>33.22</v>
+      </c>
+      <c r="R1464">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="S1464">
+        <v>20</v>
+      </c>
+      <c r="T1464">
+        <v>5</v>
+      </c>
+      <c r="U1464">
+        <v>18</v>
+      </c>
+      <c r="V1464">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1465" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1465" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1465" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1465" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1465" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H1465">
+        <v>5.81</v>
+      </c>
+      <c r="I1465">
+        <v>0.79</v>
+      </c>
+      <c r="J1465">
+        <v>5</v>
+      </c>
+      <c r="K1465">
+        <v>0.44</v>
+      </c>
+      <c r="L1465">
+        <v>0.32</v>
+      </c>
+      <c r="M1465">
+        <v>0.04</v>
+      </c>
+      <c r="N1465">
+        <v>0</v>
+      </c>
+      <c r="O1465">
+        <v>5</v>
+      </c>
+      <c r="P1465">
+        <v>3.77</v>
+      </c>
+      <c r="Q1465">
+        <v>27.01</v>
+      </c>
+      <c r="R1465">
+        <v>4.3</v>
+      </c>
+      <c r="S1465">
+        <v>19</v>
+      </c>
+      <c r="T1465">
+        <v>4</v>
+      </c>
+      <c r="U1465">
+        <v>17</v>
+      </c>
+      <c r="V1465">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1466" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1466" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1466" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1466" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1466" t="s">
+        <v>764</v>
+      </c>
+      <c r="H1466">
+        <v>7.08</v>
+      </c>
+      <c r="I1466">
+        <v>0.71</v>
+      </c>
+      <c r="J1466">
+        <v>6.35</v>
+      </c>
+      <c r="K1466">
+        <v>0.48</v>
+      </c>
+      <c r="L1466">
+        <v>0.18</v>
+      </c>
+      <c r="M1466">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N1466">
+        <v>0</v>
+      </c>
+      <c r="O1466">
+        <v>6</v>
+      </c>
+      <c r="P1466">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="Q1466">
+        <v>27.77</v>
+      </c>
+      <c r="R1466">
+        <v>5.52</v>
+      </c>
+      <c r="S1466">
+        <v>51</v>
+      </c>
+      <c r="T1466">
+        <v>13</v>
+      </c>
+      <c r="U1466">
+        <v>39</v>
+      </c>
+      <c r="V1466">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1467" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1467" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1467" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1467" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1467" t="s">
+        <v>510</v>
+      </c>
+      <c r="H1467">
+        <v>6.15</v>
+      </c>
+      <c r="I1467">
+        <v>0.9</v>
+      </c>
+      <c r="J1467">
+        <v>5.22</v>
+      </c>
+      <c r="K1467">
+        <v>0.44</v>
+      </c>
+      <c r="L1467">
+        <v>0.34</v>
+      </c>
+      <c r="M1467">
+        <v>0.13</v>
+      </c>
+      <c r="N1467">
+        <v>0.01</v>
+      </c>
+      <c r="O1467">
+        <v>12</v>
+      </c>
+      <c r="P1467">
+        <v>3.77</v>
+      </c>
+      <c r="Q1467">
+        <v>31.41</v>
+      </c>
+      <c r="R1467">
+        <v>5.23</v>
+      </c>
+      <c r="S1467">
+        <v>58</v>
+      </c>
+      <c r="T1467">
+        <v>25</v>
+      </c>
+      <c r="U1467">
+        <v>54</v>
+      </c>
+      <c r="V1467">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1468" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1468" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1468" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1468" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1468" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H1468">
+        <v>2.63</v>
+      </c>
+      <c r="I1468">
+        <v>0.2</v>
+      </c>
+      <c r="J1468">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="K1468">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L1468">
+        <v>0.06</v>
+      </c>
+      <c r="M1468">
+        <v>0</v>
+      </c>
+      <c r="N1468">
+        <v>0</v>
+      </c>
+      <c r="O1468">
+        <v>1</v>
+      </c>
+      <c r="P1468">
+        <v>3.1</v>
+      </c>
+      <c r="Q1468">
+        <v>25.1</v>
+      </c>
+      <c r="R1468">
+        <v>3.94</v>
+      </c>
+      <c r="S1468">
+        <v>13</v>
+      </c>
+      <c r="T1468">
+        <v>0</v>
+      </c>
+      <c r="U1468">
+        <v>2</v>
+      </c>
+      <c r="V1468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1469" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1469" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1469" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1469" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1469" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H1469">
+        <v>6.57</v>
+      </c>
+      <c r="I1469">
+        <v>0.87</v>
+      </c>
+      <c r="J1469">
+        <v>5.68</v>
+      </c>
+      <c r="K1469">
+        <v>0.52</v>
+      </c>
+      <c r="L1469">
+        <v>0.32</v>
+      </c>
+      <c r="M1469">
+        <v>0.05</v>
+      </c>
+      <c r="N1469">
+        <v>0</v>
+      </c>
+      <c r="O1469">
+        <v>11</v>
+      </c>
+      <c r="P1469">
+        <v>4.04</v>
+      </c>
+      <c r="Q1469">
+        <v>27.74</v>
+      </c>
+      <c r="R1469">
+        <v>5.22</v>
+      </c>
+      <c r="S1469">
+        <v>62</v>
+      </c>
+      <c r="T1469">
+        <v>14</v>
+      </c>
+      <c r="U1469">
+        <v>46</v>
+      </c>
+      <c r="V1469">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1470" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1470" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1470" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1470" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1470" t="s">
+        <v>544</v>
+      </c>
+      <c r="H1470">
+        <v>2.98</v>
+      </c>
+      <c r="I1470">
+        <v>0.45</v>
+      </c>
+      <c r="J1470">
+        <v>2.52</v>
+      </c>
+      <c r="K1470">
+        <v>0.17</v>
+      </c>
+      <c r="L1470">
+        <v>0.15</v>
+      </c>
+      <c r="M1470">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N1470">
+        <v>0</v>
+      </c>
+      <c r="O1470">
+        <v>9</v>
+      </c>
+      <c r="P1470">
+        <v>3.66</v>
+      </c>
+      <c r="Q1470">
+        <v>28.84</v>
+      </c>
+      <c r="R1470">
+        <v>4.26</v>
+      </c>
+      <c r="S1470">
+        <v>16</v>
+      </c>
+      <c r="T1470">
+        <v>1</v>
+      </c>
+      <c r="U1470">
+        <v>3</v>
+      </c>
+      <c r="V1470">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17767789-A423-5948-82A6-546AC6FE02C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B3CDFB-8317-8246-A498-1A7BEB19083B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8322" uniqueCount="1223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8604" uniqueCount="1251">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3705,6 +3704,90 @@
   </si>
   <si>
     <t>01:30:00</t>
+  </si>
+  <si>
+    <t>01:06:52</t>
+  </si>
+  <si>
+    <t>00:53:03</t>
+  </si>
+  <si>
+    <t>01:06:45</t>
+  </si>
+  <si>
+    <t>01:05:51</t>
+  </si>
+  <si>
+    <t>01:05:44</t>
+  </si>
+  <si>
+    <t>01:11:50</t>
+  </si>
+  <si>
+    <t>01:21:07</t>
+  </si>
+  <si>
+    <t>01:39:33</t>
+  </si>
+  <si>
+    <t>00:26:49</t>
+  </si>
+  <si>
+    <t>01:39:18</t>
+  </si>
+  <si>
+    <t>00:26:50</t>
+  </si>
+  <si>
+    <t>00:17:33</t>
+  </si>
+  <si>
+    <t>N3 J19 VS Gallia Lucciana</t>
+  </si>
+  <si>
+    <t>01:36:27</t>
+  </si>
+  <si>
+    <t>01:37:11</t>
+  </si>
+  <si>
+    <t>01:36:48</t>
+  </si>
+  <si>
+    <t>01:43:10</t>
+  </si>
+  <si>
+    <t>01:43:01</t>
+  </si>
+  <si>
+    <t>01:49:27</t>
+  </si>
+  <si>
+    <t>01:49:10</t>
+  </si>
+  <si>
+    <t>01:50:10</t>
+  </si>
+  <si>
+    <t>01:49:35</t>
+  </si>
+  <si>
+    <t>01:34:16</t>
+  </si>
+  <si>
+    <t>01:33:09</t>
+  </si>
+  <si>
+    <t>01:33:10</t>
+  </si>
+  <si>
+    <t>01:32:41</t>
+  </si>
+  <si>
+    <t>01:33:24</t>
+  </si>
+  <si>
+    <t>01:21:09</t>
   </si>
 </sst>
 </file>
@@ -4108,7 +4191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1470"/>
+  <dimension ref="A1:V1517"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -102538,6 +102621,3202 @@
         <v>2</v>
       </c>
     </row>
+    <row r="1471" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1471" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1471" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1471" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1471" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1471" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1471" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H1471">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="I1471">
+        <v>0.27</v>
+      </c>
+      <c r="J1471">
+        <v>4.83</v>
+      </c>
+      <c r="K1471">
+        <v>0.25</v>
+      </c>
+      <c r="L1471">
+        <v>0.02</v>
+      </c>
+      <c r="M1471">
+        <v>0</v>
+      </c>
+      <c r="N1471">
+        <v>0</v>
+      </c>
+      <c r="O1471">
+        <v>0</v>
+      </c>
+      <c r="P1471">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="Q1471">
+        <v>23.06</v>
+      </c>
+      <c r="R1471">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="S1471">
+        <v>27</v>
+      </c>
+      <c r="T1471">
+        <v>3</v>
+      </c>
+      <c r="U1471">
+        <v>17</v>
+      </c>
+      <c r="V1471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1472" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1472" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1472" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1472" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1472" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1472" t="s">
+        <v>883</v>
+      </c>
+      <c r="H1472">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="I1472">
+        <v>0.21</v>
+      </c>
+      <c r="J1472">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="K1472">
+        <v>0.21</v>
+      </c>
+      <c r="L1472">
+        <v>0</v>
+      </c>
+      <c r="M1472">
+        <v>0</v>
+      </c>
+      <c r="N1472">
+        <v>0</v>
+      </c>
+      <c r="O1472">
+        <v>0</v>
+      </c>
+      <c r="P1472">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="Q1472">
+        <v>20.6</v>
+      </c>
+      <c r="R1472">
+        <v>4.12</v>
+      </c>
+      <c r="S1472">
+        <v>21</v>
+      </c>
+      <c r="T1472">
+        <v>2</v>
+      </c>
+      <c r="U1472">
+        <v>9</v>
+      </c>
+      <c r="V1472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1473" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1473" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1473" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1473" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1473" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1473" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H1473">
+        <v>4.05</v>
+      </c>
+      <c r="I1473">
+        <v>0.23</v>
+      </c>
+      <c r="J1473">
+        <v>3.82</v>
+      </c>
+      <c r="K1473">
+        <v>0.22</v>
+      </c>
+      <c r="L1473">
+        <v>0.01</v>
+      </c>
+      <c r="M1473">
+        <v>0</v>
+      </c>
+      <c r="N1473">
+        <v>0</v>
+      </c>
+      <c r="O1473">
+        <v>0</v>
+      </c>
+      <c r="P1473">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="Q1473">
+        <v>22.78</v>
+      </c>
+      <c r="R1473">
+        <v>4.13</v>
+      </c>
+      <c r="S1473">
+        <v>20</v>
+      </c>
+      <c r="T1473">
+        <v>1</v>
+      </c>
+      <c r="U1473">
+        <v>19</v>
+      </c>
+      <c r="V1473">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1474" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1474" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1474" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1474" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1474" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1474" t="s">
+        <v>883</v>
+      </c>
+      <c r="H1474">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="I1474">
+        <v>0.15</v>
+      </c>
+      <c r="J1474">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="K1474">
+        <v>0.13</v>
+      </c>
+      <c r="L1474">
+        <v>0.03</v>
+      </c>
+      <c r="M1474">
+        <v>0</v>
+      </c>
+      <c r="N1474">
+        <v>0</v>
+      </c>
+      <c r="O1474">
+        <v>0</v>
+      </c>
+      <c r="P1474">
+        <v>3.91</v>
+      </c>
+      <c r="Q1474">
+        <v>22.51</v>
+      </c>
+      <c r="R1474">
+        <v>4.59</v>
+      </c>
+      <c r="S1474">
+        <v>29</v>
+      </c>
+      <c r="T1474">
+        <v>5</v>
+      </c>
+      <c r="U1474">
+        <v>22</v>
+      </c>
+      <c r="V1474">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1475" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1475" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1475" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1475" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1475" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1475" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H1475">
+        <v>4.21</v>
+      </c>
+      <c r="I1475">
+        <v>0.24</v>
+      </c>
+      <c r="J1475">
+        <v>3.96</v>
+      </c>
+      <c r="K1475">
+        <v>0.2</v>
+      </c>
+      <c r="L1475">
+        <v>0.05</v>
+      </c>
+      <c r="M1475">
+        <v>0</v>
+      </c>
+      <c r="N1475">
+        <v>0</v>
+      </c>
+      <c r="O1475">
+        <v>0</v>
+      </c>
+      <c r="P1475">
+        <v>3.79</v>
+      </c>
+      <c r="Q1475">
+        <v>23.64</v>
+      </c>
+      <c r="R1475">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S1475">
+        <v>25</v>
+      </c>
+      <c r="T1475">
+        <v>5</v>
+      </c>
+      <c r="U1475">
+        <v>15</v>
+      </c>
+      <c r="V1475">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1476" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1476" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1476" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1476" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1476" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1476" t="s">
+        <v>969</v>
+      </c>
+      <c r="H1476">
+        <v>4.22</v>
+      </c>
+      <c r="I1476">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J1476">
+        <v>4.07</v>
+      </c>
+      <c r="K1476">
+        <v>0.13</v>
+      </c>
+      <c r="L1476">
+        <v>0.01</v>
+      </c>
+      <c r="M1476">
+        <v>0</v>
+      </c>
+      <c r="N1476">
+        <v>0</v>
+      </c>
+      <c r="O1476">
+        <v>0</v>
+      </c>
+      <c r="P1476">
+        <v>3.39</v>
+      </c>
+      <c r="Q1476">
+        <v>23.1</v>
+      </c>
+      <c r="R1476">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="S1476">
+        <v>23</v>
+      </c>
+      <c r="T1476">
+        <v>5</v>
+      </c>
+      <c r="U1476">
+        <v>18</v>
+      </c>
+      <c r="V1476">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1477" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1477" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1477" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1477" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1477" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1477" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H1477">
+        <v>5.65</v>
+      </c>
+      <c r="I1477">
+        <v>0.32</v>
+      </c>
+      <c r="J1477">
+        <v>5.32</v>
+      </c>
+      <c r="K1477">
+        <v>0.3</v>
+      </c>
+      <c r="L1477">
+        <v>0.03</v>
+      </c>
+      <c r="M1477">
+        <v>0</v>
+      </c>
+      <c r="N1477">
+        <v>0</v>
+      </c>
+      <c r="O1477">
+        <v>0</v>
+      </c>
+      <c r="P1477">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="Q1477">
+        <v>24.68</v>
+      </c>
+      <c r="R1477">
+        <v>5.41</v>
+      </c>
+      <c r="S1477">
+        <v>69</v>
+      </c>
+      <c r="T1477">
+        <v>19</v>
+      </c>
+      <c r="U1477">
+        <v>47</v>
+      </c>
+      <c r="V1477">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1478" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1478" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1478" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1478" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1478" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1478" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H1478">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="I1478">
+        <v>0.13</v>
+      </c>
+      <c r="J1478">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="K1478">
+        <v>0.13</v>
+      </c>
+      <c r="L1478">
+        <v>0</v>
+      </c>
+      <c r="M1478">
+        <v>0</v>
+      </c>
+      <c r="N1478">
+        <v>0</v>
+      </c>
+      <c r="O1478">
+        <v>0</v>
+      </c>
+      <c r="P1478">
+        <v>3.66</v>
+      </c>
+      <c r="Q1478">
+        <v>19.47</v>
+      </c>
+      <c r="R1478">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="S1478">
+        <v>41</v>
+      </c>
+      <c r="T1478">
+        <v>6</v>
+      </c>
+      <c r="U1478">
+        <v>36</v>
+      </c>
+      <c r="V1478">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1479" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1479" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1479" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1479" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1479" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1479" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H1479">
+        <v>8.75</v>
+      </c>
+      <c r="I1479">
+        <v>2.27</v>
+      </c>
+      <c r="J1479">
+        <v>6.45</v>
+      </c>
+      <c r="K1479">
+        <v>1.76</v>
+      </c>
+      <c r="L1479">
+        <v>0.45</v>
+      </c>
+      <c r="M1479">
+        <v>0.08</v>
+      </c>
+      <c r="N1479">
+        <v>0.01</v>
+      </c>
+      <c r="O1479">
+        <v>8</v>
+      </c>
+      <c r="P1479">
+        <v>7.25</v>
+      </c>
+      <c r="Q1479">
+        <v>30.24</v>
+      </c>
+      <c r="R1479">
+        <v>4.51</v>
+      </c>
+      <c r="S1479">
+        <v>43</v>
+      </c>
+      <c r="T1479">
+        <v>8</v>
+      </c>
+      <c r="U1479">
+        <v>27</v>
+      </c>
+      <c r="V1479">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1480" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1480" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1480" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1480" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1480" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1480" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H1480">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="I1480">
+        <v>2.08</v>
+      </c>
+      <c r="J1480">
+        <v>7.52</v>
+      </c>
+      <c r="K1480">
+        <v>1.38</v>
+      </c>
+      <c r="L1480">
+        <v>0.6</v>
+      </c>
+      <c r="M1480">
+        <v>0.12</v>
+      </c>
+      <c r="N1480">
+        <v>0</v>
+      </c>
+      <c r="O1480">
+        <v>14</v>
+      </c>
+      <c r="P1480">
+        <v>7.04</v>
+      </c>
+      <c r="Q1480">
+        <v>30.19</v>
+      </c>
+      <c r="R1480">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="S1480">
+        <v>40</v>
+      </c>
+      <c r="T1480">
+        <v>9</v>
+      </c>
+      <c r="U1480">
+        <v>32</v>
+      </c>
+      <c r="V1480">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1481" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1481" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1481" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1481" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1481" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1481" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H1481">
+        <v>10.91</v>
+      </c>
+      <c r="I1481">
+        <v>1.61</v>
+      </c>
+      <c r="J1481">
+        <v>9.27</v>
+      </c>
+      <c r="K1481">
+        <v>1.21</v>
+      </c>
+      <c r="L1481">
+        <v>0.35</v>
+      </c>
+      <c r="M1481">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N1481">
+        <v>0.01</v>
+      </c>
+      <c r="O1481">
+        <v>11</v>
+      </c>
+      <c r="P1481">
+        <v>6.52</v>
+      </c>
+      <c r="Q1481">
+        <v>30.87</v>
+      </c>
+      <c r="R1481">
+        <v>4.66</v>
+      </c>
+      <c r="S1481">
+        <v>40</v>
+      </c>
+      <c r="T1481">
+        <v>6</v>
+      </c>
+      <c r="U1481">
+        <v>36</v>
+      </c>
+      <c r="V1481">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1482" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1482" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1482" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1482" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1482" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1482" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H1482">
+        <v>2.9</v>
+      </c>
+      <c r="I1482">
+        <v>0.62</v>
+      </c>
+      <c r="J1482">
+        <v>2.27</v>
+      </c>
+      <c r="K1482">
+        <v>0.39</v>
+      </c>
+      <c r="L1482">
+        <v>0.18</v>
+      </c>
+      <c r="M1482">
+        <v>0.06</v>
+      </c>
+      <c r="N1482">
+        <v>0</v>
+      </c>
+      <c r="O1482">
+        <v>6</v>
+      </c>
+      <c r="P1482">
+        <v>6.35</v>
+      </c>
+      <c r="Q1482">
+        <v>27.15</v>
+      </c>
+      <c r="R1482">
+        <v>4.45</v>
+      </c>
+      <c r="S1482">
+        <v>19</v>
+      </c>
+      <c r="T1482">
+        <v>3</v>
+      </c>
+      <c r="U1482">
+        <v>5</v>
+      </c>
+      <c r="V1482">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1483" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1483" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1483" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1483" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1483" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1483" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H1483">
+        <v>9.89</v>
+      </c>
+      <c r="I1483">
+        <v>1.44</v>
+      </c>
+      <c r="J1483">
+        <v>8.43</v>
+      </c>
+      <c r="K1483">
+        <v>1.07</v>
+      </c>
+      <c r="L1483">
+        <v>0.32</v>
+      </c>
+      <c r="M1483">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N1483">
+        <v>0</v>
+      </c>
+      <c r="O1483">
+        <v>7</v>
+      </c>
+      <c r="P1483">
+        <v>5.9</v>
+      </c>
+      <c r="Q1483">
+        <v>27.55</v>
+      </c>
+      <c r="R1483">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="S1483">
+        <v>41</v>
+      </c>
+      <c r="T1483">
+        <v>9</v>
+      </c>
+      <c r="U1483">
+        <v>36</v>
+      </c>
+      <c r="V1483">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1484" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1484" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1484" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1484" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1484" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1484" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H1484">
+        <v>10.49</v>
+      </c>
+      <c r="I1484">
+        <v>1.93</v>
+      </c>
+      <c r="J1484">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="K1484">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L1484">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M1484">
+        <v>0.18</v>
+      </c>
+      <c r="N1484">
+        <v>0.05</v>
+      </c>
+      <c r="O1484">
+        <v>14</v>
+      </c>
+      <c r="P1484">
+        <v>6.18</v>
+      </c>
+      <c r="Q1484">
+        <v>32.119999999999997</v>
+      </c>
+      <c r="R1484">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="S1484">
+        <v>32</v>
+      </c>
+      <c r="T1484">
+        <v>4</v>
+      </c>
+      <c r="U1484">
+        <v>31</v>
+      </c>
+      <c r="V1484">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1485" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1485" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1485" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1485" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1485" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1485" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H1485">
+        <v>10.94</v>
+      </c>
+      <c r="I1485">
+        <v>1.8</v>
+      </c>
+      <c r="J1485">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="K1485">
+        <v>1.18</v>
+      </c>
+      <c r="L1485">
+        <v>0.51</v>
+      </c>
+      <c r="M1485">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N1485">
+        <v>0</v>
+      </c>
+      <c r="O1485">
+        <v>13</v>
+      </c>
+      <c r="P1485">
+        <v>6.56</v>
+      </c>
+      <c r="Q1485">
+        <v>29.15</v>
+      </c>
+      <c r="R1485">
+        <v>5.09</v>
+      </c>
+      <c r="S1485">
+        <v>45</v>
+      </c>
+      <c r="T1485">
+        <v>8</v>
+      </c>
+      <c r="U1485">
+        <v>47</v>
+      </c>
+      <c r="V1485">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1486" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1486" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1486" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1486" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1486" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1486" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H1486">
+        <v>2.76</v>
+      </c>
+      <c r="I1486">
+        <v>0.61</v>
+      </c>
+      <c r="J1486">
+        <v>2.15</v>
+      </c>
+      <c r="K1486">
+        <v>0.43</v>
+      </c>
+      <c r="L1486">
+        <v>0.13</v>
+      </c>
+      <c r="M1486">
+        <v>0.05</v>
+      </c>
+      <c r="N1486">
+        <v>0</v>
+      </c>
+      <c r="O1486">
+        <v>4</v>
+      </c>
+      <c r="P1486">
+        <v>6.13</v>
+      </c>
+      <c r="Q1486">
+        <v>27.33</v>
+      </c>
+      <c r="R1486">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="S1486">
+        <v>15</v>
+      </c>
+      <c r="T1486">
+        <v>4</v>
+      </c>
+      <c r="U1486">
+        <v>12</v>
+      </c>
+      <c r="V1486">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1487" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1487" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1487" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1487" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1487" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1487" t="s">
+        <v>558</v>
+      </c>
+      <c r="H1487">
+        <v>11.17</v>
+      </c>
+      <c r="I1487">
+        <v>1.76</v>
+      </c>
+      <c r="J1487">
+        <v>9.39</v>
+      </c>
+      <c r="K1487">
+        <v>1.35</v>
+      </c>
+      <c r="L1487">
+        <v>0.37</v>
+      </c>
+      <c r="M1487">
+        <v>0.06</v>
+      </c>
+      <c r="N1487">
+        <v>0.01</v>
+      </c>
+      <c r="O1487">
+        <v>6</v>
+      </c>
+      <c r="P1487">
+        <v>6.74</v>
+      </c>
+      <c r="Q1487">
+        <v>30.17</v>
+      </c>
+      <c r="R1487">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="S1487">
+        <v>37</v>
+      </c>
+      <c r="T1487">
+        <v>5</v>
+      </c>
+      <c r="U1487">
+        <v>39</v>
+      </c>
+      <c r="V1487">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1488" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1488" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1488" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1488" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1488" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1488" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1488" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H1488">
+        <v>9.51</v>
+      </c>
+      <c r="I1488">
+        <v>1.37</v>
+      </c>
+      <c r="J1488">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="K1488">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="L1488">
+        <v>0.3</v>
+      </c>
+      <c r="M1488">
+        <v>0</v>
+      </c>
+      <c r="N1488">
+        <v>0</v>
+      </c>
+      <c r="O1488">
+        <v>2</v>
+      </c>
+      <c r="P1488">
+        <v>5.72</v>
+      </c>
+      <c r="Q1488">
+        <v>25.12</v>
+      </c>
+      <c r="R1488">
+        <v>4.47</v>
+      </c>
+      <c r="S1488">
+        <v>24</v>
+      </c>
+      <c r="T1488">
+        <v>6</v>
+      </c>
+      <c r="U1488">
+        <v>29</v>
+      </c>
+      <c r="V1488">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1489" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1489" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1489" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1489" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1489" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1489" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1489" t="s">
+        <v>1234</v>
+      </c>
+      <c r="H1489">
+        <v>2.08</v>
+      </c>
+      <c r="I1489">
+        <v>0.53</v>
+      </c>
+      <c r="J1489">
+        <v>1.54</v>
+      </c>
+      <c r="K1489">
+        <v>0.41</v>
+      </c>
+      <c r="L1489">
+        <v>0.13</v>
+      </c>
+      <c r="M1489">
+        <v>0</v>
+      </c>
+      <c r="N1489">
+        <v>0</v>
+      </c>
+      <c r="O1489">
+        <v>1</v>
+      </c>
+      <c r="P1489">
+        <v>7.04</v>
+      </c>
+      <c r="Q1489">
+        <v>25.33</v>
+      </c>
+      <c r="R1489">
+        <v>4.76</v>
+      </c>
+      <c r="S1489">
+        <v>5</v>
+      </c>
+      <c r="T1489">
+        <v>2</v>
+      </c>
+      <c r="U1489">
+        <v>14</v>
+      </c>
+      <c r="V1489">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1490" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B1490" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C1490" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1490" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1490" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1490" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1490" t="s">
+        <v>564</v>
+      </c>
+      <c r="H1490">
+        <v>11.85</v>
+      </c>
+      <c r="I1490">
+        <v>2.66</v>
+      </c>
+      <c r="J1490">
+        <v>9.16</v>
+      </c>
+      <c r="K1490">
+        <v>2.15</v>
+      </c>
+      <c r="L1490">
+        <v>0.47</v>
+      </c>
+      <c r="M1490">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N1490">
+        <v>0</v>
+      </c>
+      <c r="O1490">
+        <v>10</v>
+      </c>
+      <c r="P1490">
+        <v>7.11</v>
+      </c>
+      <c r="Q1490">
+        <v>27.35</v>
+      </c>
+      <c r="R1490">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="S1490">
+        <v>38</v>
+      </c>
+      <c r="T1490">
+        <v>3</v>
+      </c>
+      <c r="U1490">
+        <v>33</v>
+      </c>
+      <c r="V1490">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1491" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1491" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C1491" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1491" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E1491" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1491" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1491" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H1491">
+        <v>8.44</v>
+      </c>
+      <c r="I1491">
+        <v>0.46</v>
+      </c>
+      <c r="J1491">
+        <v>7.97</v>
+      </c>
+      <c r="K1491">
+        <v>0.4</v>
+      </c>
+      <c r="L1491">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M1491">
+        <v>0</v>
+      </c>
+      <c r="N1491">
+        <v>0</v>
+      </c>
+      <c r="O1491">
+        <v>0</v>
+      </c>
+      <c r="P1491">
+        <v>5.18</v>
+      </c>
+      <c r="Q1491">
+        <v>24.13</v>
+      </c>
+      <c r="R1491">
+        <v>5</v>
+      </c>
+      <c r="S1491">
+        <v>33</v>
+      </c>
+      <c r="T1491">
+        <v>4</v>
+      </c>
+      <c r="U1491">
+        <v>16</v>
+      </c>
+      <c r="V1491">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1492" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1492" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C1492" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1492" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E1492" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1492" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1492" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H1492">
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="I1492">
+        <v>0.19</v>
+      </c>
+      <c r="J1492">
+        <v>8.02</v>
+      </c>
+      <c r="K1492">
+        <v>0.18</v>
+      </c>
+      <c r="L1492">
+        <v>0.01</v>
+      </c>
+      <c r="M1492">
+        <v>0</v>
+      </c>
+      <c r="N1492">
+        <v>0</v>
+      </c>
+      <c r="O1492">
+        <v>0</v>
+      </c>
+      <c r="P1492">
+        <v>4.99</v>
+      </c>
+      <c r="Q1492">
+        <v>22.67</v>
+      </c>
+      <c r="R1492">
+        <v>4.33</v>
+      </c>
+      <c r="S1492">
+        <v>22</v>
+      </c>
+      <c r="T1492">
+        <v>2</v>
+      </c>
+      <c r="U1492">
+        <v>7</v>
+      </c>
+      <c r="V1492">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1493" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1493" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C1493" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1493" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E1493" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1493" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1493" t="s">
+        <v>590</v>
+      </c>
+      <c r="H1493">
+        <v>7.3</v>
+      </c>
+      <c r="I1493">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J1493">
+        <v>7.15</v>
+      </c>
+      <c r="K1493">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L1493">
+        <v>0</v>
+      </c>
+      <c r="M1493">
+        <v>0</v>
+      </c>
+      <c r="N1493">
+        <v>0</v>
+      </c>
+      <c r="O1493">
+        <v>0</v>
+      </c>
+      <c r="P1493">
+        <v>3.93</v>
+      </c>
+      <c r="Q1493">
+        <v>23.61</v>
+      </c>
+      <c r="R1493">
+        <v>4.41</v>
+      </c>
+      <c r="S1493">
+        <v>28</v>
+      </c>
+      <c r="T1493">
+        <v>3</v>
+      </c>
+      <c r="U1493">
+        <v>15</v>
+      </c>
+      <c r="V1493">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1494" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1494" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C1494" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1494" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E1494" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="F1494" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1494" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H1494">
+        <v>7.19</v>
+      </c>
+      <c r="I1494">
+        <v>0.04</v>
+      </c>
+      <c r="J1494">
+        <v>7.15</v>
+      </c>
+      <c r="K1494">
+        <v>0.04</v>
+      </c>
+      <c r="L1494">
+        <v>0</v>
+      </c>
+      <c r="M1494">
+        <v>0</v>
+      </c>
+      <c r="N1494">
+        <v>0</v>
+      </c>
+      <c r="O1494">
+        <v>0</v>
+      </c>
+      <c r="P1494">
+        <v>3.76</v>
+      </c>
+      <c r="Q1494">
+        <v>19.45</v>
+      </c>
+      <c r="R1494">
+        <v>3.41</v>
+      </c>
+      <c r="S1494">
+        <v>3</v>
+      </c>
+      <c r="T1494">
+        <v>0</v>
+      </c>
+      <c r="U1494">
+        <v>3</v>
+      </c>
+      <c r="V1494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1495" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1495" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1495" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1495" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1495" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="F1495" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1495" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H1495">
+        <v>7.12</v>
+      </c>
+      <c r="I1495">
+        <v>0.24</v>
+      </c>
+      <c r="J1495">
+        <v>6.87</v>
+      </c>
+      <c r="K1495">
+        <v>0.2</v>
+      </c>
+      <c r="L1495">
+        <v>0.05</v>
+      </c>
+      <c r="M1495">
+        <v>0</v>
+      </c>
+      <c r="N1495">
+        <v>0</v>
+      </c>
+      <c r="O1495">
+        <v>0</v>
+      </c>
+      <c r="P1495">
+        <v>4.08</v>
+      </c>
+      <c r="Q1495">
+        <v>24.98</v>
+      </c>
+      <c r="R1495">
+        <v>4.46</v>
+      </c>
+      <c r="S1495">
+        <v>35</v>
+      </c>
+      <c r="T1495">
+        <v>3</v>
+      </c>
+      <c r="U1495">
+        <v>27</v>
+      </c>
+      <c r="V1495">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1496" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1496" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1496" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1496" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1496" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1496" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1496" t="s">
+        <v>207</v>
+      </c>
+      <c r="H1496">
+        <v>6.18</v>
+      </c>
+      <c r="I1496">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J1496">
+        <v>6.04</v>
+      </c>
+      <c r="K1496">
+        <v>0.13</v>
+      </c>
+      <c r="L1496">
+        <v>0.02</v>
+      </c>
+      <c r="M1496">
+        <v>0</v>
+      </c>
+      <c r="N1496">
+        <v>0</v>
+      </c>
+      <c r="O1496">
+        <v>0</v>
+      </c>
+      <c r="P1496">
+        <v>3.18</v>
+      </c>
+      <c r="Q1496">
+        <v>22.31</v>
+      </c>
+      <c r="R1496">
+        <v>4.49</v>
+      </c>
+      <c r="S1496">
+        <v>24</v>
+      </c>
+      <c r="T1496">
+        <v>6</v>
+      </c>
+      <c r="U1496">
+        <v>16</v>
+      </c>
+      <c r="V1496">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1497" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1497" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1497" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1497" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1497" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1497" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1497" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H1497">
+        <v>7.71</v>
+      </c>
+      <c r="I1497">
+        <v>0.36</v>
+      </c>
+      <c r="J1497">
+        <v>7.34</v>
+      </c>
+      <c r="K1497">
+        <v>0.31</v>
+      </c>
+      <c r="L1497">
+        <v>0.06</v>
+      </c>
+      <c r="M1497">
+        <v>0</v>
+      </c>
+      <c r="N1497">
+        <v>0</v>
+      </c>
+      <c r="O1497">
+        <v>1</v>
+      </c>
+      <c r="P1497">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q1497">
+        <v>25.54</v>
+      </c>
+      <c r="R1497">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="S1497">
+        <v>40</v>
+      </c>
+      <c r="T1497">
+        <v>5</v>
+      </c>
+      <c r="U1497">
+        <v>42</v>
+      </c>
+      <c r="V1497">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1498" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1498" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1498" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1498" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1498" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1498" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H1498">
+        <v>7.95</v>
+      </c>
+      <c r="I1498">
+        <v>0.31</v>
+      </c>
+      <c r="J1498">
+        <v>7.62</v>
+      </c>
+      <c r="K1498">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L1498">
+        <v>0.04</v>
+      </c>
+      <c r="M1498">
+        <v>0</v>
+      </c>
+      <c r="N1498">
+        <v>0</v>
+      </c>
+      <c r="O1498">
+        <v>0</v>
+      </c>
+      <c r="P1498">
+        <v>3.96</v>
+      </c>
+      <c r="Q1498">
+        <v>22.8</v>
+      </c>
+      <c r="R1498">
+        <v>5.45</v>
+      </c>
+      <c r="S1498">
+        <v>98</v>
+      </c>
+      <c r="T1498">
+        <v>17</v>
+      </c>
+      <c r="U1498">
+        <v>78</v>
+      </c>
+      <c r="V1498">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1499" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1499" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1499" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1499" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1499" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1499" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1499">
+        <v>8.09</v>
+      </c>
+      <c r="I1499">
+        <v>0.25</v>
+      </c>
+      <c r="J1499">
+        <v>7.83</v>
+      </c>
+      <c r="K1499">
+        <v>0.25</v>
+      </c>
+      <c r="L1499">
+        <v>0.01</v>
+      </c>
+      <c r="M1499">
+        <v>0</v>
+      </c>
+      <c r="N1499">
+        <v>0</v>
+      </c>
+      <c r="O1499">
+        <v>0</v>
+      </c>
+      <c r="P1499">
+        <v>4.3</v>
+      </c>
+      <c r="Q1499">
+        <v>21.23</v>
+      </c>
+      <c r="R1499">
+        <v>4.26</v>
+      </c>
+      <c r="S1499">
+        <v>39</v>
+      </c>
+      <c r="T1499">
+        <v>3</v>
+      </c>
+      <c r="U1499">
+        <v>56</v>
+      </c>
+      <c r="V1499">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1500" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1500" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1500" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1500" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1500" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1500" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H1500">
+        <v>6.37</v>
+      </c>
+      <c r="I1500">
+        <v>0.16</v>
+      </c>
+      <c r="J1500">
+        <v>6.21</v>
+      </c>
+      <c r="K1500">
+        <v>0.16</v>
+      </c>
+      <c r="L1500">
+        <v>0</v>
+      </c>
+      <c r="M1500">
+        <v>0</v>
+      </c>
+      <c r="N1500">
+        <v>0</v>
+      </c>
+      <c r="O1500">
+        <v>0</v>
+      </c>
+      <c r="P1500">
+        <v>3.66</v>
+      </c>
+      <c r="Q1500">
+        <v>20.05</v>
+      </c>
+      <c r="R1500">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="S1500">
+        <v>30</v>
+      </c>
+      <c r="T1500">
+        <v>2</v>
+      </c>
+      <c r="U1500">
+        <v>30</v>
+      </c>
+      <c r="V1500">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1501" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1501" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1501" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1501" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1501" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1501" t="s">
+        <v>584</v>
+      </c>
+      <c r="H1501">
+        <v>7.19</v>
+      </c>
+      <c r="I1501">
+        <v>0.17</v>
+      </c>
+      <c r="J1501">
+        <v>7.01</v>
+      </c>
+      <c r="K1501">
+        <v>0.17</v>
+      </c>
+      <c r="L1501">
+        <v>0.01</v>
+      </c>
+      <c r="M1501">
+        <v>0</v>
+      </c>
+      <c r="N1501">
+        <v>0</v>
+      </c>
+      <c r="O1501">
+        <v>0</v>
+      </c>
+      <c r="P1501">
+        <v>3.54</v>
+      </c>
+      <c r="Q1501">
+        <v>24.97</v>
+      </c>
+      <c r="R1501">
+        <v>5.22</v>
+      </c>
+      <c r="S1501">
+        <v>52</v>
+      </c>
+      <c r="T1501">
+        <v>6</v>
+      </c>
+      <c r="U1501">
+        <v>43</v>
+      </c>
+      <c r="V1501">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1502" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1502" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1502" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1502" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1502" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1502" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H1502">
+        <v>6.83</v>
+      </c>
+      <c r="I1502">
+        <v>0.16</v>
+      </c>
+      <c r="J1502">
+        <v>6.66</v>
+      </c>
+      <c r="K1502">
+        <v>0.15</v>
+      </c>
+      <c r="L1502">
+        <v>0.02</v>
+      </c>
+      <c r="M1502">
+        <v>0</v>
+      </c>
+      <c r="N1502">
+        <v>0</v>
+      </c>
+      <c r="O1502">
+        <v>0</v>
+      </c>
+      <c r="P1502">
+        <v>3.13</v>
+      </c>
+      <c r="Q1502">
+        <v>21.64</v>
+      </c>
+      <c r="R1502">
+        <v>6.02</v>
+      </c>
+      <c r="S1502">
+        <v>48</v>
+      </c>
+      <c r="T1502">
+        <v>7</v>
+      </c>
+      <c r="U1502">
+        <v>40</v>
+      </c>
+      <c r="V1502">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1503" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1503" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1503" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1503" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1503" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1503" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H1503">
+        <v>5.62</v>
+      </c>
+      <c r="I1503">
+        <v>0.09</v>
+      </c>
+      <c r="J1503">
+        <v>5.53</v>
+      </c>
+      <c r="K1503">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L1503">
+        <v>0.03</v>
+      </c>
+      <c r="M1503">
+        <v>0</v>
+      </c>
+      <c r="N1503">
+        <v>0</v>
+      </c>
+      <c r="O1503">
+        <v>0</v>
+      </c>
+      <c r="P1503">
+        <v>2.93</v>
+      </c>
+      <c r="Q1503">
+        <v>24.1</v>
+      </c>
+      <c r="R1503">
+        <v>3.94</v>
+      </c>
+      <c r="S1503">
+        <v>23</v>
+      </c>
+      <c r="T1503">
+        <v>0</v>
+      </c>
+      <c r="U1503">
+        <v>15</v>
+      </c>
+      <c r="V1503">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1504" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1504" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1504" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1504" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1504" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1504" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H1504">
+        <v>7.09</v>
+      </c>
+      <c r="I1504">
+        <v>0.41</v>
+      </c>
+      <c r="J1504">
+        <v>6.67</v>
+      </c>
+      <c r="K1504">
+        <v>0.38</v>
+      </c>
+      <c r="L1504">
+        <v>0.04</v>
+      </c>
+      <c r="M1504">
+        <v>0</v>
+      </c>
+      <c r="N1504">
+        <v>0</v>
+      </c>
+      <c r="O1504">
+        <v>0</v>
+      </c>
+      <c r="P1504">
+        <v>3.56</v>
+      </c>
+      <c r="Q1504">
+        <v>22.66</v>
+      </c>
+      <c r="R1504">
+        <v>5.45</v>
+      </c>
+      <c r="S1504">
+        <v>75</v>
+      </c>
+      <c r="T1504">
+        <v>27</v>
+      </c>
+      <c r="U1504">
+        <v>84</v>
+      </c>
+      <c r="V1504">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1505" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1505" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1505" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1505" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1505" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1505" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1505" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H1505">
+        <v>8.09</v>
+      </c>
+      <c r="I1505">
+        <v>0.17</v>
+      </c>
+      <c r="J1505">
+        <v>7.92</v>
+      </c>
+      <c r="K1505">
+        <v>0.16</v>
+      </c>
+      <c r="L1505">
+        <v>0.02</v>
+      </c>
+      <c r="M1505">
+        <v>0</v>
+      </c>
+      <c r="N1505">
+        <v>0</v>
+      </c>
+      <c r="O1505">
+        <v>0</v>
+      </c>
+      <c r="P1505">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="Q1505">
+        <v>22.65</v>
+      </c>
+      <c r="R1505">
+        <v>4.45</v>
+      </c>
+      <c r="S1505">
+        <v>32</v>
+      </c>
+      <c r="T1505">
+        <v>5</v>
+      </c>
+      <c r="U1505">
+        <v>20</v>
+      </c>
+      <c r="V1505">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1506" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1506" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1506" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1506" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1506" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1506" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H1506">
+        <v>7.6</v>
+      </c>
+      <c r="I1506">
+        <v>0.31</v>
+      </c>
+      <c r="J1506">
+        <v>7.28</v>
+      </c>
+      <c r="K1506">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L1506">
+        <v>0.03</v>
+      </c>
+      <c r="M1506">
+        <v>0</v>
+      </c>
+      <c r="N1506">
+        <v>0</v>
+      </c>
+      <c r="O1506">
+        <v>0</v>
+      </c>
+      <c r="P1506">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="Q1506">
+        <v>23.16</v>
+      </c>
+      <c r="R1506">
+        <v>4.54</v>
+      </c>
+      <c r="S1506">
+        <v>46</v>
+      </c>
+      <c r="T1506">
+        <v>9</v>
+      </c>
+      <c r="U1506">
+        <v>42</v>
+      </c>
+      <c r="V1506">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1507" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1507" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1507" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1507" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1507" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1507" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1507" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H1507">
+        <v>6.27</v>
+      </c>
+      <c r="I1507">
+        <v>0.74</v>
+      </c>
+      <c r="J1507">
+        <v>5.51</v>
+      </c>
+      <c r="K1507">
+        <v>0.41</v>
+      </c>
+      <c r="L1507">
+        <v>0.26</v>
+      </c>
+      <c r="M1507">
+        <v>0.08</v>
+      </c>
+      <c r="N1507">
+        <v>0</v>
+      </c>
+      <c r="O1507">
+        <v>9</v>
+      </c>
+      <c r="P1507">
+        <v>3.94</v>
+      </c>
+      <c r="Q1507">
+        <v>29.9</v>
+      </c>
+      <c r="R1507">
+        <v>4.88</v>
+      </c>
+      <c r="S1507">
+        <v>16</v>
+      </c>
+      <c r="T1507">
+        <v>4</v>
+      </c>
+      <c r="U1507">
+        <v>20</v>
+      </c>
+      <c r="V1507">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1508" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1508" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1508" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1508" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1508" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1508" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1508" t="s">
+        <v>672</v>
+      </c>
+      <c r="H1508">
+        <v>5.83</v>
+      </c>
+      <c r="I1508">
+        <v>0.63</v>
+      </c>
+      <c r="J1508">
+        <v>5.18</v>
+      </c>
+      <c r="K1508">
+        <v>0.36</v>
+      </c>
+      <c r="L1508">
+        <v>0.27</v>
+      </c>
+      <c r="M1508">
+        <v>0.02</v>
+      </c>
+      <c r="N1508">
+        <v>0</v>
+      </c>
+      <c r="O1508">
+        <v>4</v>
+      </c>
+      <c r="P1508">
+        <v>3.26</v>
+      </c>
+      <c r="Q1508">
+        <v>26.57</v>
+      </c>
+      <c r="R1508">
+        <v>4.62</v>
+      </c>
+      <c r="S1508">
+        <v>48</v>
+      </c>
+      <c r="T1508">
+        <v>6</v>
+      </c>
+      <c r="U1508">
+        <v>30</v>
+      </c>
+      <c r="V1508">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1509" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1509" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1509" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1509" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1509" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1509" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1509" t="s">
+        <v>707</v>
+      </c>
+      <c r="H1509">
+        <v>5.91</v>
+      </c>
+      <c r="I1509">
+        <v>0.75</v>
+      </c>
+      <c r="J1509">
+        <v>5.15</v>
+      </c>
+      <c r="K1509">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L1509">
+        <v>0.16</v>
+      </c>
+      <c r="M1509">
+        <v>0.02</v>
+      </c>
+      <c r="N1509">
+        <v>0</v>
+      </c>
+      <c r="O1509">
+        <v>4</v>
+      </c>
+      <c r="P1509">
+        <v>3.69</v>
+      </c>
+      <c r="Q1509">
+        <v>25.78</v>
+      </c>
+      <c r="R1509">
+        <v>4.43</v>
+      </c>
+      <c r="S1509">
+        <v>35</v>
+      </c>
+      <c r="T1509">
+        <v>12</v>
+      </c>
+      <c r="U1509">
+        <v>25</v>
+      </c>
+      <c r="V1509">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1510" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1510" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1510" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1510" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1510" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1510" t="s">
+        <v>1246</v>
+      </c>
+      <c r="H1510">
+        <v>6.19</v>
+      </c>
+      <c r="I1510">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J1510">
+        <v>5.6</v>
+      </c>
+      <c r="K1510">
+        <v>0.43</v>
+      </c>
+      <c r="L1510">
+        <v>0.16</v>
+      </c>
+      <c r="M1510">
+        <v>0</v>
+      </c>
+      <c r="N1510">
+        <v>0</v>
+      </c>
+      <c r="O1510">
+        <v>0</v>
+      </c>
+      <c r="P1510">
+        <v>3.91</v>
+      </c>
+      <c r="Q1510">
+        <v>24.89</v>
+      </c>
+      <c r="R1510">
+        <v>4.67</v>
+      </c>
+      <c r="S1510">
+        <v>25</v>
+      </c>
+      <c r="T1510">
+        <v>4</v>
+      </c>
+      <c r="U1510">
+        <v>12</v>
+      </c>
+      <c r="V1510">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1511" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1511" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1511" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1511" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1511" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1511" t="s">
+        <v>943</v>
+      </c>
+      <c r="H1511">
+        <v>5.82</v>
+      </c>
+      <c r="I1511">
+        <v>0.64</v>
+      </c>
+      <c r="J1511">
+        <v>5.16</v>
+      </c>
+      <c r="K1511">
+        <v>0.31</v>
+      </c>
+      <c r="L1511">
+        <v>0.17</v>
+      </c>
+      <c r="M1511">
+        <v>0.16</v>
+      </c>
+      <c r="N1511">
+        <v>0.02</v>
+      </c>
+      <c r="O1511">
+        <v>11</v>
+      </c>
+      <c r="P1511">
+        <v>3.37</v>
+      </c>
+      <c r="Q1511">
+        <v>33.58</v>
+      </c>
+      <c r="R1511">
+        <v>4.62</v>
+      </c>
+      <c r="S1511">
+        <v>45</v>
+      </c>
+      <c r="T1511">
+        <v>13</v>
+      </c>
+      <c r="U1511">
+        <v>50</v>
+      </c>
+      <c r="V1511">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1512" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1512" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1512" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1512" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1512" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1512" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1512" t="s">
+        <v>1247</v>
+      </c>
+      <c r="H1512">
+        <v>5.78</v>
+      </c>
+      <c r="I1512">
+        <v>0.44</v>
+      </c>
+      <c r="J1512">
+        <v>5.33</v>
+      </c>
+      <c r="K1512">
+        <v>0.26</v>
+      </c>
+      <c r="L1512">
+        <v>0.1</v>
+      </c>
+      <c r="M1512">
+        <v>0.09</v>
+      </c>
+      <c r="N1512">
+        <v>0</v>
+      </c>
+      <c r="O1512">
+        <v>7</v>
+      </c>
+      <c r="P1512">
+        <v>3.29</v>
+      </c>
+      <c r="Q1512">
+        <v>30.08</v>
+      </c>
+      <c r="R1512">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="S1512">
+        <v>30</v>
+      </c>
+      <c r="T1512">
+        <v>6</v>
+      </c>
+      <c r="U1512">
+        <v>31</v>
+      </c>
+      <c r="V1512">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1513" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1513" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1513" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1513" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1513" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1513" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1513" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H1513">
+        <v>4.99</v>
+      </c>
+      <c r="I1513">
+        <v>0.4</v>
+      </c>
+      <c r="J1513">
+        <v>4.58</v>
+      </c>
+      <c r="K1513">
+        <v>0.23</v>
+      </c>
+      <c r="L1513">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M1513">
+        <v>0.04</v>
+      </c>
+      <c r="N1513">
+        <v>0</v>
+      </c>
+      <c r="O1513">
+        <v>3</v>
+      </c>
+      <c r="P1513">
+        <v>2.97</v>
+      </c>
+      <c r="Q1513">
+        <v>28.18</v>
+      </c>
+      <c r="R1513">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="S1513">
+        <v>15</v>
+      </c>
+      <c r="T1513">
+        <v>1</v>
+      </c>
+      <c r="U1513">
+        <v>12</v>
+      </c>
+      <c r="V1513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1514" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1514" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1514" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1514" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1514" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1514" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1514" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H1514">
+        <v>4.71</v>
+      </c>
+      <c r="I1514">
+        <v>0.54</v>
+      </c>
+      <c r="J1514">
+        <v>4.16</v>
+      </c>
+      <c r="K1514">
+        <v>0.32</v>
+      </c>
+      <c r="L1514">
+        <v>0.16</v>
+      </c>
+      <c r="M1514">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N1514">
+        <v>0</v>
+      </c>
+      <c r="O1514">
+        <v>8</v>
+      </c>
+      <c r="P1514">
+        <v>3.41</v>
+      </c>
+      <c r="Q1514">
+        <v>29.12</v>
+      </c>
+      <c r="R1514">
+        <v>3.96</v>
+      </c>
+      <c r="S1514">
+        <v>31</v>
+      </c>
+      <c r="T1514">
+        <v>0</v>
+      </c>
+      <c r="U1514">
+        <v>19</v>
+      </c>
+      <c r="V1514">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1515" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1515" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1515" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1515" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1515" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1515" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1515" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H1515">
+        <v>5.9</v>
+      </c>
+      <c r="I1515">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J1515">
+        <v>5.32</v>
+      </c>
+      <c r="K1515">
+        <v>0.33</v>
+      </c>
+      <c r="L1515">
+        <v>0.17</v>
+      </c>
+      <c r="M1515">
+        <v>0.09</v>
+      </c>
+      <c r="N1515">
+        <v>0</v>
+      </c>
+      <c r="O1515">
+        <v>7</v>
+      </c>
+      <c r="P1515">
+        <v>3.74</v>
+      </c>
+      <c r="Q1515">
+        <v>28.89</v>
+      </c>
+      <c r="R1515">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="S1515">
+        <v>36</v>
+      </c>
+      <c r="T1515">
+        <v>3</v>
+      </c>
+      <c r="U1515">
+        <v>25</v>
+      </c>
+      <c r="V1515">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1516" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1516" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1516" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1516" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1516" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1516" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1516" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H1516">
+        <v>6.4</v>
+      </c>
+      <c r="I1516">
+        <v>0.7</v>
+      </c>
+      <c r="J1516">
+        <v>5.69</v>
+      </c>
+      <c r="K1516">
+        <v>0.47</v>
+      </c>
+      <c r="L1516">
+        <v>0.21</v>
+      </c>
+      <c r="M1516">
+        <v>0.03</v>
+      </c>
+      <c r="N1516">
+        <v>0</v>
+      </c>
+      <c r="O1516">
+        <v>3</v>
+      </c>
+      <c r="P1516">
+        <v>4.04</v>
+      </c>
+      <c r="Q1516">
+        <v>27.7</v>
+      </c>
+      <c r="R1516">
+        <v>4.09</v>
+      </c>
+      <c r="S1516">
+        <v>33</v>
+      </c>
+      <c r="T1516">
+        <v>2</v>
+      </c>
+      <c r="U1516">
+        <v>27</v>
+      </c>
+      <c r="V1516">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1517" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1517" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C1517" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1517" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1517" t="s">
+        <v>741</v>
+      </c>
+      <c r="F1517" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1517" t="s">
+        <v>1250</v>
+      </c>
+      <c r="H1517">
+        <v>5.4</v>
+      </c>
+      <c r="I1517">
+        <v>0.49</v>
+      </c>
+      <c r="J1517">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K1517">
+        <v>0.25</v>
+      </c>
+      <c r="L1517">
+        <v>0.18</v>
+      </c>
+      <c r="M1517">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N1517">
+        <v>0</v>
+      </c>
+      <c r="O1517">
+        <v>6</v>
+      </c>
+      <c r="P1517">
+        <v>3.92</v>
+      </c>
+      <c r="Q1517">
+        <v>27.69</v>
+      </c>
+      <c r="R1517">
+        <v>4.45</v>
+      </c>
+      <c r="S1517">
+        <v>18</v>
+      </c>
+      <c r="T1517">
+        <v>2</v>
+      </c>
+      <c r="U1517">
+        <v>15</v>
+      </c>
+      <c r="V1517">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B3CDFB-8317-8246-A498-1A7BEB19083B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FE41BF-1BD3-0D4C-9060-B682B92E05B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8604" uniqueCount="1251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8646" uniqueCount="1256">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3788,6 +3788,21 @@
   </si>
   <si>
     <t>01:21:09</t>
+  </si>
+  <si>
+    <t>01:18:09</t>
+  </si>
+  <si>
+    <t>01:16:01</t>
+  </si>
+  <si>
+    <t>01:17:55</t>
+  </si>
+  <si>
+    <t>01:17:39</t>
+  </si>
+  <si>
+    <t>01:17:54</t>
   </si>
 </sst>
 </file>
@@ -4191,7 +4206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1517"/>
+  <dimension ref="A1:V1524"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -105817,6 +105832,482 @@
         <v>5</v>
       </c>
     </row>
+    <row r="1518" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1518" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1518" s="1">
+        <v>46101</v>
+      </c>
+      <c r="C1518" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1518" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1518" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1518" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1518" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1518">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="I1518">
+        <v>0.25</v>
+      </c>
+      <c r="J1518">
+        <v>4.54</v>
+      </c>
+      <c r="K1518">
+        <v>0.2</v>
+      </c>
+      <c r="L1518">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M1518">
+        <v>0</v>
+      </c>
+      <c r="N1518">
+        <v>0</v>
+      </c>
+      <c r="O1518">
+        <v>0</v>
+      </c>
+      <c r="P1518">
+        <v>3.59</v>
+      </c>
+      <c r="Q1518">
+        <v>24.54</v>
+      </c>
+      <c r="R1518">
+        <v>4.38</v>
+      </c>
+      <c r="S1518">
+        <v>16</v>
+      </c>
+      <c r="T1518">
+        <v>3</v>
+      </c>
+      <c r="U1518">
+        <v>12</v>
+      </c>
+      <c r="V1518">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1519" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1519" s="1">
+        <v>46101</v>
+      </c>
+      <c r="C1519" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1519" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1519" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1519" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1519" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H1519">
+        <v>5.07</v>
+      </c>
+      <c r="I1519">
+        <v>0.17</v>
+      </c>
+      <c r="J1519">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="K1519">
+        <v>0.16</v>
+      </c>
+      <c r="L1519">
+        <v>0.02</v>
+      </c>
+      <c r="M1519">
+        <v>0</v>
+      </c>
+      <c r="N1519">
+        <v>0</v>
+      </c>
+      <c r="O1519">
+        <v>0</v>
+      </c>
+      <c r="P1519">
+        <v>3.52</v>
+      </c>
+      <c r="Q1519">
+        <v>24.19</v>
+      </c>
+      <c r="R1519">
+        <v>5.96</v>
+      </c>
+      <c r="S1519">
+        <v>51</v>
+      </c>
+      <c r="T1519">
+        <v>9</v>
+      </c>
+      <c r="U1519">
+        <v>44</v>
+      </c>
+      <c r="V1519">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1520" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1520" s="1">
+        <v>46101</v>
+      </c>
+      <c r="C1520" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1520" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1520" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1520" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1520" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H1520">
+        <v>5.92</v>
+      </c>
+      <c r="I1520">
+        <v>0.48</v>
+      </c>
+      <c r="J1520">
+        <v>5.43</v>
+      </c>
+      <c r="K1520">
+        <v>0.33</v>
+      </c>
+      <c r="L1520">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M1520">
+        <v>0.02</v>
+      </c>
+      <c r="N1520">
+        <v>0</v>
+      </c>
+      <c r="O1520">
+        <v>4</v>
+      </c>
+      <c r="P1520">
+        <v>4.46</v>
+      </c>
+      <c r="Q1520">
+        <v>27.62</v>
+      </c>
+      <c r="R1520">
+        <v>4.72</v>
+      </c>
+      <c r="S1520">
+        <v>30</v>
+      </c>
+      <c r="T1520">
+        <v>12</v>
+      </c>
+      <c r="U1520">
+        <v>23</v>
+      </c>
+      <c r="V1520">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1521" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1521" s="1">
+        <v>46101</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1521" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1521" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1521" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1521" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H1521">
+        <v>5.37</v>
+      </c>
+      <c r="I1521">
+        <v>0.31</v>
+      </c>
+      <c r="J1521">
+        <v>5.05</v>
+      </c>
+      <c r="K1521">
+        <v>0.27</v>
+      </c>
+      <c r="L1521">
+        <v>0.05</v>
+      </c>
+      <c r="M1521">
+        <v>0</v>
+      </c>
+      <c r="N1521">
+        <v>0</v>
+      </c>
+      <c r="O1521">
+        <v>0</v>
+      </c>
+      <c r="P1521">
+        <v>4.09</v>
+      </c>
+      <c r="Q1521">
+        <v>23.3</v>
+      </c>
+      <c r="R1521">
+        <v>4.5</v>
+      </c>
+      <c r="S1521">
+        <v>31</v>
+      </c>
+      <c r="T1521">
+        <v>9</v>
+      </c>
+      <c r="U1521">
+        <v>21</v>
+      </c>
+      <c r="V1521">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1522" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1522" s="1">
+        <v>46101</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1522" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1522" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1522" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1522" t="s">
+        <v>375</v>
+      </c>
+      <c r="H1522">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="I1522">
+        <v>0.32</v>
+      </c>
+      <c r="J1522">
+        <v>4.45</v>
+      </c>
+      <c r="K1522">
+        <v>0.2</v>
+      </c>
+      <c r="L1522">
+        <v>0.12</v>
+      </c>
+      <c r="M1522">
+        <v>0.01</v>
+      </c>
+      <c r="N1522">
+        <v>0</v>
+      </c>
+      <c r="O1522">
+        <v>1</v>
+      </c>
+      <c r="P1522">
+        <v>3.6</v>
+      </c>
+      <c r="Q1522">
+        <v>26.13</v>
+      </c>
+      <c r="R1522">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S1522">
+        <v>29</v>
+      </c>
+      <c r="T1522">
+        <v>8</v>
+      </c>
+      <c r="U1522">
+        <v>17</v>
+      </c>
+      <c r="V1522">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1523" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1523" s="1">
+        <v>46101</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1523" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1523" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1523" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1523" t="s">
+        <v>1255</v>
+      </c>
+      <c r="H1523">
+        <v>5.93</v>
+      </c>
+      <c r="I1523">
+        <v>0.25</v>
+      </c>
+      <c r="J1523">
+        <v>5.67</v>
+      </c>
+      <c r="K1523">
+        <v>0.21</v>
+      </c>
+      <c r="L1523">
+        <v>0.05</v>
+      </c>
+      <c r="M1523">
+        <v>0</v>
+      </c>
+      <c r="N1523">
+        <v>0</v>
+      </c>
+      <c r="O1523">
+        <v>0</v>
+      </c>
+      <c r="P1523">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="Q1523">
+        <v>24.03</v>
+      </c>
+      <c r="R1523">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="S1523">
+        <v>14</v>
+      </c>
+      <c r="T1523">
+        <v>5</v>
+      </c>
+      <c r="U1523">
+        <v>8</v>
+      </c>
+      <c r="V1523">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1524" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1524" s="1">
+        <v>46101</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1524" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1524" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1524" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1524" t="s">
+        <v>292</v>
+      </c>
+      <c r="H1524">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="I1524">
+        <v>0.37</v>
+      </c>
+      <c r="J1524">
+        <v>4.51</v>
+      </c>
+      <c r="K1524">
+        <v>0.26</v>
+      </c>
+      <c r="L1524">
+        <v>0.11</v>
+      </c>
+      <c r="M1524">
+        <v>0.01</v>
+      </c>
+      <c r="N1524">
+        <v>0</v>
+      </c>
+      <c r="O1524">
+        <v>2</v>
+      </c>
+      <c r="P1524">
+        <v>3.56</v>
+      </c>
+      <c r="Q1524">
+        <v>26.9</v>
+      </c>
+      <c r="R1524">
+        <v>5.48</v>
+      </c>
+      <c r="S1524">
+        <v>52</v>
+      </c>
+      <c r="T1524">
+        <v>21</v>
+      </c>
+      <c r="U1524">
+        <v>34</v>
+      </c>
+      <c r="V1524">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FE41BF-1BD3-0D4C-9060-B682B92E05B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB493685-5D8F-7446-91F2-17F3E46392FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8646" uniqueCount="1256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8718" uniqueCount="1262">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3803,6 +3803,24 @@
   </si>
   <si>
     <t>01:17:54</t>
+  </si>
+  <si>
+    <t>01:40:42</t>
+  </si>
+  <si>
+    <t>00:17:59</t>
+  </si>
+  <si>
+    <t>01:21:54</t>
+  </si>
+  <si>
+    <t>00:35:26</t>
+  </si>
+  <si>
+    <t>01:09:32</t>
+  </si>
+  <si>
+    <t>N3 J20 VS Cannet 21/03/2026</t>
   </si>
 </sst>
 </file>
@@ -4206,7 +4224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1524"/>
+  <dimension ref="A1:V1536"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -106308,6 +106326,822 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1525" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1525" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1525" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1525" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1525" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1525" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1525" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H1525">
+        <v>9.65</v>
+      </c>
+      <c r="I1525">
+        <v>1.04</v>
+      </c>
+      <c r="J1525">
+        <v>8.59</v>
+      </c>
+      <c r="K1525">
+        <v>0.75</v>
+      </c>
+      <c r="L1525">
+        <v>0.23</v>
+      </c>
+      <c r="M1525">
+        <v>0.06</v>
+      </c>
+      <c r="N1525">
+        <v>0.01</v>
+      </c>
+      <c r="O1525">
+        <v>5</v>
+      </c>
+      <c r="P1525">
+        <v>5.66</v>
+      </c>
+      <c r="Q1525">
+        <v>31.49</v>
+      </c>
+      <c r="R1525">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="S1525">
+        <v>28</v>
+      </c>
+      <c r="T1525">
+        <v>4</v>
+      </c>
+      <c r="U1525">
+        <v>22</v>
+      </c>
+      <c r="V1525">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1526" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1526" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1526" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1526" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1526" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1526" t="s">
+        <v>922</v>
+      </c>
+      <c r="H1526">
+        <v>11.66</v>
+      </c>
+      <c r="I1526">
+        <v>2.73</v>
+      </c>
+      <c r="J1526">
+        <v>8.9</v>
+      </c>
+      <c r="K1526">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="L1526">
+        <v>0.5</v>
+      </c>
+      <c r="M1526">
+        <v>0.08</v>
+      </c>
+      <c r="N1526">
+        <v>0</v>
+      </c>
+      <c r="O1526">
+        <v>5</v>
+      </c>
+      <c r="P1526">
+        <v>7.47</v>
+      </c>
+      <c r="Q1526">
+        <v>27.87</v>
+      </c>
+      <c r="R1526">
+        <v>4.2</v>
+      </c>
+      <c r="S1526">
+        <v>36</v>
+      </c>
+      <c r="T1526">
+        <v>1</v>
+      </c>
+      <c r="U1526">
+        <v>30</v>
+      </c>
+      <c r="V1526">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1527" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1527" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1527" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1527" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1527" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1527" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H1527">
+        <v>12.93</v>
+      </c>
+      <c r="I1527">
+        <v>3.72</v>
+      </c>
+      <c r="J1527">
+        <v>9.17</v>
+      </c>
+      <c r="K1527">
+        <v>2.58</v>
+      </c>
+      <c r="L1527">
+        <v>0.98</v>
+      </c>
+      <c r="M1527">
+        <v>0.2</v>
+      </c>
+      <c r="N1527">
+        <v>0</v>
+      </c>
+      <c r="O1527">
+        <v>16</v>
+      </c>
+      <c r="P1527">
+        <v>7.67</v>
+      </c>
+      <c r="Q1527">
+        <v>28.59</v>
+      </c>
+      <c r="R1527">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="S1527">
+        <v>63</v>
+      </c>
+      <c r="T1527">
+        <v>11</v>
+      </c>
+      <c r="U1527">
+        <v>54</v>
+      </c>
+      <c r="V1527">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1528" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1528" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1528" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1528" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1528" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1528" t="s">
+        <v>893</v>
+      </c>
+      <c r="H1528">
+        <v>11.54</v>
+      </c>
+      <c r="I1528">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J1528">
+        <v>9.25</v>
+      </c>
+      <c r="K1528">
+        <v>1.69</v>
+      </c>
+      <c r="L1528">
+        <v>0.49</v>
+      </c>
+      <c r="M1528">
+        <v>0.1</v>
+      </c>
+      <c r="N1528">
+        <v>0</v>
+      </c>
+      <c r="O1528">
+        <v>8</v>
+      </c>
+      <c r="P1528">
+        <v>6.83</v>
+      </c>
+      <c r="Q1528">
+        <v>27.98</v>
+      </c>
+      <c r="R1528">
+        <v>4.68</v>
+      </c>
+      <c r="S1528">
+        <v>39</v>
+      </c>
+      <c r="T1528">
+        <v>9</v>
+      </c>
+      <c r="U1528">
+        <v>40</v>
+      </c>
+      <c r="V1528">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1529" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1529" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1529" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1529" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1529" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1529" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H1529">
+        <v>1.87</v>
+      </c>
+      <c r="I1529">
+        <v>0.51</v>
+      </c>
+      <c r="J1529">
+        <v>1.35</v>
+      </c>
+      <c r="K1529">
+        <v>0.27</v>
+      </c>
+      <c r="L1529">
+        <v>0.18</v>
+      </c>
+      <c r="M1529">
+        <v>0.06</v>
+      </c>
+      <c r="N1529">
+        <v>0.01</v>
+      </c>
+      <c r="O1529">
+        <v>5</v>
+      </c>
+      <c r="P1529">
+        <v>6.16</v>
+      </c>
+      <c r="Q1529">
+        <v>30.9</v>
+      </c>
+      <c r="R1529">
+        <v>4.5</v>
+      </c>
+      <c r="S1529">
+        <v>11</v>
+      </c>
+      <c r="T1529">
+        <v>5</v>
+      </c>
+      <c r="U1529">
+        <v>10</v>
+      </c>
+      <c r="V1529">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1530" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1530" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1530" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1530" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1530" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1530" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H1530">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="I1530">
+        <v>1.3</v>
+      </c>
+      <c r="J1530">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="K1530">
+        <v>0.9</v>
+      </c>
+      <c r="L1530">
+        <v>0.33</v>
+      </c>
+      <c r="M1530">
+        <v>0.08</v>
+      </c>
+      <c r="N1530">
+        <v>0</v>
+      </c>
+      <c r="O1530">
+        <v>7</v>
+      </c>
+      <c r="P1530">
+        <v>5.94</v>
+      </c>
+      <c r="Q1530">
+        <v>27.23</v>
+      </c>
+      <c r="R1530">
+        <v>4.12</v>
+      </c>
+      <c r="S1530">
+        <v>18</v>
+      </c>
+      <c r="T1530">
+        <v>3</v>
+      </c>
+      <c r="U1530">
+        <v>16</v>
+      </c>
+      <c r="V1530">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1531" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1531" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1531" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1531" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1531" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1531" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H1531">
+        <v>8.06</v>
+      </c>
+      <c r="I1531">
+        <v>1.34</v>
+      </c>
+      <c r="J1531">
+        <v>6.7</v>
+      </c>
+      <c r="K1531">
+        <v>1.01</v>
+      </c>
+      <c r="L1531">
+        <v>0.26</v>
+      </c>
+      <c r="M1531">
+        <v>0.08</v>
+      </c>
+      <c r="N1531">
+        <v>0</v>
+      </c>
+      <c r="O1531">
+        <v>8</v>
+      </c>
+      <c r="P1531">
+        <v>5.83</v>
+      </c>
+      <c r="Q1531">
+        <v>28.96</v>
+      </c>
+      <c r="R1531">
+        <v>4.79</v>
+      </c>
+      <c r="S1531">
+        <v>29</v>
+      </c>
+      <c r="T1531">
+        <v>5</v>
+      </c>
+      <c r="U1531">
+        <v>34</v>
+      </c>
+      <c r="V1531">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1532" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1532" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1532" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1532" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1532" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1532" t="s">
+        <v>753</v>
+      </c>
+      <c r="H1532">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="I1532">
+        <v>1.61</v>
+      </c>
+      <c r="J1532">
+        <v>8.33</v>
+      </c>
+      <c r="K1532">
+        <v>1.05</v>
+      </c>
+      <c r="L1532">
+        <v>0.52</v>
+      </c>
+      <c r="M1532">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N1532">
+        <v>0</v>
+      </c>
+      <c r="O1532">
+        <v>7</v>
+      </c>
+      <c r="P1532">
+        <v>6.16</v>
+      </c>
+      <c r="Q1532">
+        <v>29.34</v>
+      </c>
+      <c r="R1532">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="S1532">
+        <v>11</v>
+      </c>
+      <c r="T1532">
+        <v>1</v>
+      </c>
+      <c r="U1532">
+        <v>19</v>
+      </c>
+      <c r="V1532">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1533" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1533" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1533" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1533" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1533" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1533" t="s">
+        <v>969</v>
+      </c>
+      <c r="H1533">
+        <v>8.07</v>
+      </c>
+      <c r="I1533">
+        <v>1.97</v>
+      </c>
+      <c r="J1533">
+        <v>6.08</v>
+      </c>
+      <c r="K1533">
+        <v>1.32</v>
+      </c>
+      <c r="L1533">
+        <v>0.51</v>
+      </c>
+      <c r="M1533">
+        <v>0.16</v>
+      </c>
+      <c r="N1533">
+        <v>0</v>
+      </c>
+      <c r="O1533">
+        <v>11</v>
+      </c>
+      <c r="P1533">
+        <v>7.37</v>
+      </c>
+      <c r="Q1533">
+        <v>28.25</v>
+      </c>
+      <c r="R1533">
+        <v>4.55</v>
+      </c>
+      <c r="S1533">
+        <v>25</v>
+      </c>
+      <c r="T1533">
+        <v>11</v>
+      </c>
+      <c r="U1533">
+        <v>39</v>
+      </c>
+      <c r="V1533">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1534" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1534" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1534" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1534" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1534" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1534" t="s">
+        <v>893</v>
+      </c>
+      <c r="H1534">
+        <v>12</v>
+      </c>
+      <c r="I1534">
+        <v>2.78</v>
+      </c>
+      <c r="J1534">
+        <v>9.19</v>
+      </c>
+      <c r="K1534">
+        <v>1.8</v>
+      </c>
+      <c r="L1534">
+        <v>0.7</v>
+      </c>
+      <c r="M1534">
+        <v>0.31</v>
+      </c>
+      <c r="N1534">
+        <v>0</v>
+      </c>
+      <c r="O1534">
+        <v>20</v>
+      </c>
+      <c r="P1534">
+        <v>7.02</v>
+      </c>
+      <c r="Q1534">
+        <v>29.96</v>
+      </c>
+      <c r="R1534">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="S1534">
+        <v>39</v>
+      </c>
+      <c r="T1534">
+        <v>11</v>
+      </c>
+      <c r="U1534">
+        <v>41</v>
+      </c>
+      <c r="V1534">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1535" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1535" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1535" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1535" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1535" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1535" t="s">
+        <v>1259</v>
+      </c>
+      <c r="H1535">
+        <v>3.4</v>
+      </c>
+      <c r="I1535">
+        <v>0.67</v>
+      </c>
+      <c r="J1535">
+        <v>2.73</v>
+      </c>
+      <c r="K1535">
+        <v>0.32</v>
+      </c>
+      <c r="L1535">
+        <v>0.22</v>
+      </c>
+      <c r="M1535">
+        <v>0.13</v>
+      </c>
+      <c r="N1535">
+        <v>0.01</v>
+      </c>
+      <c r="O1535">
+        <v>10</v>
+      </c>
+      <c r="P1535">
+        <v>5.69</v>
+      </c>
+      <c r="Q1535">
+        <v>30.64</v>
+      </c>
+      <c r="R1535">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="S1535">
+        <v>13</v>
+      </c>
+      <c r="T1535">
+        <v>6</v>
+      </c>
+      <c r="U1535">
+        <v>13</v>
+      </c>
+      <c r="V1535">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1536" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1536" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1536" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1536" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1536" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1536" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H1536">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="I1536">
+        <v>2.04</v>
+      </c>
+      <c r="J1536">
+        <v>6.56</v>
+      </c>
+      <c r="K1536">
+        <v>1.21</v>
+      </c>
+      <c r="L1536">
+        <v>0.65</v>
+      </c>
+      <c r="M1536">
+        <v>0.17</v>
+      </c>
+      <c r="N1536">
+        <v>0.02</v>
+      </c>
+      <c r="O1536">
+        <v>14</v>
+      </c>
+      <c r="P1536">
+        <v>7.38</v>
+      </c>
+      <c r="Q1536">
+        <v>31.87</v>
+      </c>
+      <c r="R1536">
+        <v>5.15</v>
+      </c>
+      <c r="S1536">
+        <v>42</v>
+      </c>
+      <c r="T1536">
+        <v>8</v>
+      </c>
+      <c r="U1536">
+        <v>34</v>
+      </c>
+      <c r="V1536">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB493685-5D8F-7446-91F2-17F3E46392FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CA79F4-F2F0-6C44-9CDB-FE31B3B1F2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8718" uniqueCount="1262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8826" uniqueCount="1271">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3821,6 +3821,33 @@
   </si>
   <si>
     <t>N3 J20 VS Cannet 21/03/2026</t>
+  </si>
+  <si>
+    <t>01:56:42</t>
+  </si>
+  <si>
+    <t>01:58:19</t>
+  </si>
+  <si>
+    <t>01:56:41</t>
+  </si>
+  <si>
+    <t>01:55:47</t>
+  </si>
+  <si>
+    <t>01:25:35</t>
+  </si>
+  <si>
+    <t>01:25:49</t>
+  </si>
+  <si>
+    <t>01:25:27</t>
+  </si>
+  <si>
+    <t>01:25:34</t>
+  </si>
+  <si>
+    <t>01:26:04</t>
   </si>
 </sst>
 </file>
@@ -4224,7 +4251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1536"/>
+  <dimension ref="A1:V1554"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -107142,6 +107169,1230 @@
         <v>13</v>
       </c>
     </row>
+    <row r="1537" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1537" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1537" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1537" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1537" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="F1537" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1537" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H1537">
+        <v>8.01</v>
+      </c>
+      <c r="I1537">
+        <v>0.36</v>
+      </c>
+      <c r="J1537">
+        <v>7.64</v>
+      </c>
+      <c r="K1537">
+        <v>0.36</v>
+      </c>
+      <c r="L1537">
+        <v>0</v>
+      </c>
+      <c r="M1537">
+        <v>0</v>
+      </c>
+      <c r="N1537">
+        <v>0</v>
+      </c>
+      <c r="O1537">
+        <v>0</v>
+      </c>
+      <c r="P1537">
+        <v>3.8</v>
+      </c>
+      <c r="Q1537">
+        <v>20.37</v>
+      </c>
+      <c r="R1537">
+        <v>3.51</v>
+      </c>
+      <c r="S1537">
+        <v>16</v>
+      </c>
+      <c r="T1537">
+        <v>0</v>
+      </c>
+      <c r="U1537">
+        <v>24</v>
+      </c>
+      <c r="V1537">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1538" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1538" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1538" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1538" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1538" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1538" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H1538">
+        <v>9.36</v>
+      </c>
+      <c r="I1538">
+        <v>0.34</v>
+      </c>
+      <c r="J1538">
+        <v>9.01</v>
+      </c>
+      <c r="K1538">
+        <v>0.31</v>
+      </c>
+      <c r="L1538">
+        <v>0.04</v>
+      </c>
+      <c r="M1538">
+        <v>0</v>
+      </c>
+      <c r="N1538">
+        <v>0</v>
+      </c>
+      <c r="O1538">
+        <v>0</v>
+      </c>
+      <c r="P1538">
+        <v>3.67</v>
+      </c>
+      <c r="Q1538">
+        <v>22.01</v>
+      </c>
+      <c r="R1538">
+        <v>4.55</v>
+      </c>
+      <c r="S1538">
+        <v>16</v>
+      </c>
+      <c r="T1538">
+        <v>2</v>
+      </c>
+      <c r="U1538">
+        <v>15</v>
+      </c>
+      <c r="V1538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1539" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1539" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1539" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1539" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1539" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1539" t="s">
+        <v>233</v>
+      </c>
+      <c r="H1539">
+        <v>9.44</v>
+      </c>
+      <c r="I1539">
+        <v>0.78</v>
+      </c>
+      <c r="J1539">
+        <v>8.65</v>
+      </c>
+      <c r="K1539">
+        <v>0.46</v>
+      </c>
+      <c r="L1539">
+        <v>0.33</v>
+      </c>
+      <c r="M1539">
+        <v>0</v>
+      </c>
+      <c r="N1539">
+        <v>0</v>
+      </c>
+      <c r="O1539">
+        <v>0</v>
+      </c>
+      <c r="P1539">
+        <v>4.42</v>
+      </c>
+      <c r="Q1539">
+        <v>23.7</v>
+      </c>
+      <c r="R1539">
+        <v>5.54</v>
+      </c>
+      <c r="S1539">
+        <v>76</v>
+      </c>
+      <c r="T1539">
+        <v>19</v>
+      </c>
+      <c r="U1539">
+        <v>69</v>
+      </c>
+      <c r="V1539">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1540" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1540" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1540" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1540" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1540" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1540" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H1540">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="I1540">
+        <v>0.69</v>
+      </c>
+      <c r="J1540">
+        <v>8.52</v>
+      </c>
+      <c r="K1540">
+        <v>0.63</v>
+      </c>
+      <c r="L1540">
+        <v>0.06</v>
+      </c>
+      <c r="M1540">
+        <v>0.01</v>
+      </c>
+      <c r="N1540">
+        <v>0</v>
+      </c>
+      <c r="O1540">
+        <v>1</v>
+      </c>
+      <c r="P1540">
+        <v>4.57</v>
+      </c>
+      <c r="Q1540">
+        <v>25.7</v>
+      </c>
+      <c r="R1540">
+        <v>4.92</v>
+      </c>
+      <c r="S1540">
+        <v>51</v>
+      </c>
+      <c r="T1540">
+        <v>8</v>
+      </c>
+      <c r="U1540">
+        <v>20</v>
+      </c>
+      <c r="V1540">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1541" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1541" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1541" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1541" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1541" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1541" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H1541">
+        <v>9.31</v>
+      </c>
+      <c r="I1541">
+        <v>0.7</v>
+      </c>
+      <c r="J1541">
+        <v>8.61</v>
+      </c>
+      <c r="K1541">
+        <v>0.63</v>
+      </c>
+      <c r="L1541">
+        <v>0.08</v>
+      </c>
+      <c r="M1541">
+        <v>0</v>
+      </c>
+      <c r="N1541">
+        <v>0</v>
+      </c>
+      <c r="O1541">
+        <v>0</v>
+      </c>
+      <c r="P1541">
+        <v>4.66</v>
+      </c>
+      <c r="Q1541">
+        <v>21.57</v>
+      </c>
+      <c r="R1541">
+        <v>4.55</v>
+      </c>
+      <c r="S1541">
+        <v>54</v>
+      </c>
+      <c r="T1541">
+        <v>5</v>
+      </c>
+      <c r="U1541">
+        <v>34</v>
+      </c>
+      <c r="V1541">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1542" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1542" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1542" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1542" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1542" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1542" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H1542">
+        <v>8.39</v>
+      </c>
+      <c r="I1542">
+        <v>0.72</v>
+      </c>
+      <c r="J1542">
+        <v>7.65</v>
+      </c>
+      <c r="K1542">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L1542">
+        <v>0.18</v>
+      </c>
+      <c r="M1542">
+        <v>0</v>
+      </c>
+      <c r="N1542">
+        <v>0</v>
+      </c>
+      <c r="O1542">
+        <v>0</v>
+      </c>
+      <c r="P1542">
+        <v>3.98</v>
+      </c>
+      <c r="Q1542">
+        <v>23.9</v>
+      </c>
+      <c r="R1542">
+        <v>5.26</v>
+      </c>
+      <c r="S1542">
+        <v>69</v>
+      </c>
+      <c r="T1542">
+        <v>25</v>
+      </c>
+      <c r="U1542">
+        <v>59</v>
+      </c>
+      <c r="V1542">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1543" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1543" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1543" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1543" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1543" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1543" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1543">
+        <v>6.89</v>
+      </c>
+      <c r="I1543">
+        <v>0.65</v>
+      </c>
+      <c r="J1543">
+        <v>6.21</v>
+      </c>
+      <c r="K1543">
+        <v>0.54</v>
+      </c>
+      <c r="L1543">
+        <v>0.12</v>
+      </c>
+      <c r="M1543">
+        <v>0.02</v>
+      </c>
+      <c r="N1543">
+        <v>0</v>
+      </c>
+      <c r="O1543">
+        <v>1</v>
+      </c>
+      <c r="P1543">
+        <v>4.78</v>
+      </c>
+      <c r="Q1543">
+        <v>28.94</v>
+      </c>
+      <c r="R1543">
+        <v>4.95</v>
+      </c>
+      <c r="S1543">
+        <v>50</v>
+      </c>
+      <c r="T1543">
+        <v>21</v>
+      </c>
+      <c r="U1543">
+        <v>31</v>
+      </c>
+      <c r="V1543">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1544" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1544" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1544" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1544" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1544" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1544" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H1544">
+        <v>5.04</v>
+      </c>
+      <c r="I1544">
+        <v>0.16</v>
+      </c>
+      <c r="J1544">
+        <v>4.87</v>
+      </c>
+      <c r="K1544">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L1544">
+        <v>0.03</v>
+      </c>
+      <c r="M1544">
+        <v>0</v>
+      </c>
+      <c r="N1544">
+        <v>0</v>
+      </c>
+      <c r="O1544">
+        <v>0</v>
+      </c>
+      <c r="P1544">
+        <v>3.48</v>
+      </c>
+      <c r="Q1544">
+        <v>23.56</v>
+      </c>
+      <c r="R1544">
+        <v>3.95</v>
+      </c>
+      <c r="S1544">
+        <v>16</v>
+      </c>
+      <c r="T1544">
+        <v>0</v>
+      </c>
+      <c r="U1544">
+        <v>7</v>
+      </c>
+      <c r="V1544">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1545" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1545" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1545" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1545" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1545" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1545" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H1545">
+        <v>5.92</v>
+      </c>
+      <c r="I1545">
+        <v>0.48</v>
+      </c>
+      <c r="J1545">
+        <v>5.42</v>
+      </c>
+      <c r="K1545">
+        <v>0.32</v>
+      </c>
+      <c r="L1545">
+        <v>0.12</v>
+      </c>
+      <c r="M1545">
+        <v>0.06</v>
+      </c>
+      <c r="N1545">
+        <v>0</v>
+      </c>
+      <c r="O1545">
+        <v>4</v>
+      </c>
+      <c r="P1545">
+        <v>3.74</v>
+      </c>
+      <c r="Q1545">
+        <v>29.14</v>
+      </c>
+      <c r="R1545">
+        <v>4.93</v>
+      </c>
+      <c r="S1545">
+        <v>63</v>
+      </c>
+      <c r="T1545">
+        <v>15</v>
+      </c>
+      <c r="U1545">
+        <v>53</v>
+      </c>
+      <c r="V1545">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1546" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1546" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1546" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1546" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1546" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1546" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H1546">
+        <v>7.25</v>
+      </c>
+      <c r="I1546">
+        <v>0.52</v>
+      </c>
+      <c r="J1546">
+        <v>6.71</v>
+      </c>
+      <c r="K1546">
+        <v>0.45</v>
+      </c>
+      <c r="L1546">
+        <v>0.08</v>
+      </c>
+      <c r="M1546">
+        <v>0.01</v>
+      </c>
+      <c r="N1546">
+        <v>0</v>
+      </c>
+      <c r="O1546">
+        <v>1</v>
+      </c>
+      <c r="P1546">
+        <v>4.59</v>
+      </c>
+      <c r="Q1546">
+        <v>27.71</v>
+      </c>
+      <c r="R1546">
+        <v>4.68</v>
+      </c>
+      <c r="S1546">
+        <v>56</v>
+      </c>
+      <c r="T1546">
+        <v>15</v>
+      </c>
+      <c r="U1546">
+        <v>61</v>
+      </c>
+      <c r="V1546">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1547" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1547" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1547" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1547" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1547" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1547" t="s">
+        <v>398</v>
+      </c>
+      <c r="H1547">
+        <v>7.16</v>
+      </c>
+      <c r="I1547">
+        <v>0.67</v>
+      </c>
+      <c r="J1547">
+        <v>6.48</v>
+      </c>
+      <c r="K1547">
+        <v>0.59</v>
+      </c>
+      <c r="L1547">
+        <v>0.09</v>
+      </c>
+      <c r="M1547">
+        <v>0</v>
+      </c>
+      <c r="N1547">
+        <v>0</v>
+      </c>
+      <c r="O1547">
+        <v>0</v>
+      </c>
+      <c r="P1547">
+        <v>4.93</v>
+      </c>
+      <c r="Q1547">
+        <v>24.33</v>
+      </c>
+      <c r="R1547">
+        <v>5.17</v>
+      </c>
+      <c r="S1547">
+        <v>36</v>
+      </c>
+      <c r="T1547">
+        <v>6</v>
+      </c>
+      <c r="U1547">
+        <v>32</v>
+      </c>
+      <c r="V1547">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1548" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1548" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1548" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1548" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1548" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1548" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H1548">
+        <v>6.18</v>
+      </c>
+      <c r="I1548">
+        <v>0.18</v>
+      </c>
+      <c r="J1548">
+        <v>5.99</v>
+      </c>
+      <c r="K1548">
+        <v>0.16</v>
+      </c>
+      <c r="L1548">
+        <v>0.03</v>
+      </c>
+      <c r="M1548">
+        <v>0</v>
+      </c>
+      <c r="N1548">
+        <v>0</v>
+      </c>
+      <c r="O1548">
+        <v>0</v>
+      </c>
+      <c r="P1548">
+        <v>3.64</v>
+      </c>
+      <c r="Q1548">
+        <v>23.89</v>
+      </c>
+      <c r="R1548">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="S1548">
+        <v>37</v>
+      </c>
+      <c r="T1548">
+        <v>2</v>
+      </c>
+      <c r="U1548">
+        <v>30</v>
+      </c>
+      <c r="V1548">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1549" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1549" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1549" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1549" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1549" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1549" t="s">
+        <v>626</v>
+      </c>
+      <c r="H1549">
+        <v>7.27</v>
+      </c>
+      <c r="I1549">
+        <v>0.22</v>
+      </c>
+      <c r="J1549">
+        <v>7.04</v>
+      </c>
+      <c r="K1549">
+        <v>0.2</v>
+      </c>
+      <c r="L1549">
+        <v>0.02</v>
+      </c>
+      <c r="M1549">
+        <v>0</v>
+      </c>
+      <c r="N1549">
+        <v>0</v>
+      </c>
+      <c r="O1549">
+        <v>1</v>
+      </c>
+      <c r="P1549">
+        <v>3.72</v>
+      </c>
+      <c r="Q1549">
+        <v>25.71</v>
+      </c>
+      <c r="R1549">
+        <v>3.44</v>
+      </c>
+      <c r="S1549">
+        <v>9</v>
+      </c>
+      <c r="T1549">
+        <v>0</v>
+      </c>
+      <c r="U1549">
+        <v>8</v>
+      </c>
+      <c r="V1549">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1550" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1550" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1550" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1550" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1550" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1550" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1550">
+        <v>7.12</v>
+      </c>
+      <c r="I1550">
+        <v>0.33</v>
+      </c>
+      <c r="J1550">
+        <v>6.79</v>
+      </c>
+      <c r="K1550">
+        <v>0.31</v>
+      </c>
+      <c r="L1550">
+        <v>0.02</v>
+      </c>
+      <c r="M1550">
+        <v>0</v>
+      </c>
+      <c r="N1550">
+        <v>0</v>
+      </c>
+      <c r="O1550">
+        <v>0</v>
+      </c>
+      <c r="P1550">
+        <v>4.96</v>
+      </c>
+      <c r="Q1550">
+        <v>22.27</v>
+      </c>
+      <c r="R1550">
+        <v>4.41</v>
+      </c>
+      <c r="S1550">
+        <v>23</v>
+      </c>
+      <c r="T1550">
+        <v>7</v>
+      </c>
+      <c r="U1550">
+        <v>22</v>
+      </c>
+      <c r="V1550">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1551" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1551" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1551" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1551" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1551" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1551" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H1551">
+        <v>6.45</v>
+      </c>
+      <c r="I1551">
+        <v>0.77</v>
+      </c>
+      <c r="J1551">
+        <v>5.67</v>
+      </c>
+      <c r="K1551">
+        <v>0.54</v>
+      </c>
+      <c r="L1551">
+        <v>0.2</v>
+      </c>
+      <c r="M1551">
+        <v>0.04</v>
+      </c>
+      <c r="N1551">
+        <v>0</v>
+      </c>
+      <c r="O1551">
+        <v>5</v>
+      </c>
+      <c r="P1551">
+        <v>4.5</v>
+      </c>
+      <c r="Q1551">
+        <v>28.07</v>
+      </c>
+      <c r="R1551">
+        <v>5.3</v>
+      </c>
+      <c r="S1551">
+        <v>46</v>
+      </c>
+      <c r="T1551">
+        <v>11</v>
+      </c>
+      <c r="U1551">
+        <v>26</v>
+      </c>
+      <c r="V1551">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1552" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1552" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1552" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1552" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1552" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1552" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1552">
+        <v>6.89</v>
+      </c>
+      <c r="I1552">
+        <v>0.73</v>
+      </c>
+      <c r="J1552">
+        <v>6.14</v>
+      </c>
+      <c r="K1552">
+        <v>0.5</v>
+      </c>
+      <c r="L1552">
+        <v>0.23</v>
+      </c>
+      <c r="M1552">
+        <v>0.02</v>
+      </c>
+      <c r="N1552">
+        <v>0</v>
+      </c>
+      <c r="O1552">
+        <v>3</v>
+      </c>
+      <c r="P1552">
+        <v>4.46</v>
+      </c>
+      <c r="Q1552">
+        <v>28.11</v>
+      </c>
+      <c r="R1552">
+        <v>5.57</v>
+      </c>
+      <c r="S1552">
+        <v>82</v>
+      </c>
+      <c r="T1552">
+        <v>28</v>
+      </c>
+      <c r="U1552">
+        <v>74</v>
+      </c>
+      <c r="V1552">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1553" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1553" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1553" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1553" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1553" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1553" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H1553">
+        <v>6.23</v>
+      </c>
+      <c r="I1553">
+        <v>0.64</v>
+      </c>
+      <c r="J1553">
+        <v>5.57</v>
+      </c>
+      <c r="K1553">
+        <v>0.51</v>
+      </c>
+      <c r="L1553">
+        <v>0.13</v>
+      </c>
+      <c r="M1553">
+        <v>0.01</v>
+      </c>
+      <c r="N1553">
+        <v>0</v>
+      </c>
+      <c r="O1553">
+        <v>2</v>
+      </c>
+      <c r="P1553">
+        <v>4.04</v>
+      </c>
+      <c r="Q1553">
+        <v>27.64</v>
+      </c>
+      <c r="R1553">
+        <v>5.49</v>
+      </c>
+      <c r="S1553">
+        <v>58</v>
+      </c>
+      <c r="T1553">
+        <v>25</v>
+      </c>
+      <c r="U1553">
+        <v>49</v>
+      </c>
+      <c r="V1553">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1554" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1554" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1554" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1554" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="F1554" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1554" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H1554">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="I1554">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J1554">
+        <v>4.96</v>
+      </c>
+      <c r="K1554">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L1554">
+        <v>0.01</v>
+      </c>
+      <c r="M1554">
+        <v>0</v>
+      </c>
+      <c r="N1554">
+        <v>0</v>
+      </c>
+      <c r="O1554">
+        <v>0</v>
+      </c>
+      <c r="P1554">
+        <v>3.14</v>
+      </c>
+      <c r="Q1554">
+        <v>23.79</v>
+      </c>
+      <c r="R1554">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="S1554">
+        <v>14</v>
+      </c>
+      <c r="T1554">
+        <v>1</v>
+      </c>
+      <c r="U1554">
+        <v>13</v>
+      </c>
+      <c r="V1554">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CA79F4-F2F0-6C44-9CDB-FE31B3B1F2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDFF5FC-EABE-E84B-A6DE-860D7C00F02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8826" uniqueCount="1271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8940" uniqueCount="1284">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3848,6 +3848,45 @@
   </si>
   <si>
     <t>01:26:04</t>
+  </si>
+  <si>
+    <t>01:18:05</t>
+  </si>
+  <si>
+    <t>01:18:32</t>
+  </si>
+  <si>
+    <t>01:17:58</t>
+  </si>
+  <si>
+    <t>01:18:33</t>
+  </si>
+  <si>
+    <t>01:27:57</t>
+  </si>
+  <si>
+    <t>01:41:46</t>
+  </si>
+  <si>
+    <t>01:25:08</t>
+  </si>
+  <si>
+    <t>00:08:38</t>
+  </si>
+  <si>
+    <t>01:41:08</t>
+  </si>
+  <si>
+    <t>00:58:45</t>
+  </si>
+  <si>
+    <t>00:13:19</t>
+  </si>
+  <si>
+    <t>01:42:01</t>
+  </si>
+  <si>
+    <t>01:41:23</t>
   </si>
 </sst>
 </file>
@@ -4251,7 +4290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1554"/>
+  <dimension ref="A1:V1573"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -108393,6 +108432,1298 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1555" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1555" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1555" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1555" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1555" t="s">
+        <v>914</v>
+      </c>
+      <c r="F1555" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1555" t="s">
+        <v>420</v>
+      </c>
+      <c r="H1555">
+        <v>5.69</v>
+      </c>
+      <c r="I1555">
+        <v>0.19</v>
+      </c>
+      <c r="J1555">
+        <v>5.49</v>
+      </c>
+      <c r="K1555">
+        <v>0.17</v>
+      </c>
+      <c r="L1555">
+        <v>0.03</v>
+      </c>
+      <c r="M1555">
+        <v>0</v>
+      </c>
+      <c r="N1555">
+        <v>0</v>
+      </c>
+      <c r="O1555">
+        <v>0</v>
+      </c>
+      <c r="P1555">
+        <v>3.84</v>
+      </c>
+      <c r="Q1555">
+        <v>23.72</v>
+      </c>
+      <c r="R1555">
+        <v>5.58</v>
+      </c>
+      <c r="S1555">
+        <v>46</v>
+      </c>
+      <c r="T1555">
+        <v>10</v>
+      </c>
+      <c r="U1555">
+        <v>29</v>
+      </c>
+      <c r="V1555">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1556" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1556" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1556" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1556" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1556" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1556" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1556">
+        <v>7.32</v>
+      </c>
+      <c r="I1556">
+        <v>0.17</v>
+      </c>
+      <c r="J1556">
+        <v>7.15</v>
+      </c>
+      <c r="K1556">
+        <v>0.15</v>
+      </c>
+      <c r="L1556">
+        <v>0.02</v>
+      </c>
+      <c r="M1556">
+        <v>0</v>
+      </c>
+      <c r="N1556">
+        <v>0</v>
+      </c>
+      <c r="O1556">
+        <v>0</v>
+      </c>
+      <c r="P1556">
+        <v>3.78</v>
+      </c>
+      <c r="Q1556">
+        <v>23.05</v>
+      </c>
+      <c r="R1556">
+        <v>4.18</v>
+      </c>
+      <c r="S1556">
+        <v>9</v>
+      </c>
+      <c r="T1556">
+        <v>1</v>
+      </c>
+      <c r="U1556">
+        <v>8</v>
+      </c>
+      <c r="V1556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1557" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1557" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1557" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1557" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1557" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1557" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H1557">
+        <v>6.23</v>
+      </c>
+      <c r="I1557">
+        <v>0.52</v>
+      </c>
+      <c r="J1557">
+        <v>5.69</v>
+      </c>
+      <c r="K1557">
+        <v>0.39</v>
+      </c>
+      <c r="L1557">
+        <v>0.12</v>
+      </c>
+      <c r="M1557">
+        <v>0.02</v>
+      </c>
+      <c r="N1557">
+        <v>0</v>
+      </c>
+      <c r="O1557">
+        <v>3</v>
+      </c>
+      <c r="P1557">
+        <v>4.72</v>
+      </c>
+      <c r="Q1557">
+        <v>26.02</v>
+      </c>
+      <c r="R1557">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S1557">
+        <v>39</v>
+      </c>
+      <c r="T1557">
+        <v>8</v>
+      </c>
+      <c r="U1557">
+        <v>26</v>
+      </c>
+      <c r="V1557">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1558" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1558" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1558" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1558" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1558" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1558" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H1558">
+        <v>6.33</v>
+      </c>
+      <c r="I1558">
+        <v>0.51</v>
+      </c>
+      <c r="J1558">
+        <v>5.8</v>
+      </c>
+      <c r="K1558">
+        <v>0.38</v>
+      </c>
+      <c r="L1558">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M1558">
+        <v>0</v>
+      </c>
+      <c r="N1558">
+        <v>0</v>
+      </c>
+      <c r="O1558">
+        <v>0</v>
+      </c>
+      <c r="P1558">
+        <v>4.74</v>
+      </c>
+      <c r="Q1558">
+        <v>24.69</v>
+      </c>
+      <c r="R1558">
+        <v>4.95</v>
+      </c>
+      <c r="S1558">
+        <v>35</v>
+      </c>
+      <c r="T1558">
+        <v>7</v>
+      </c>
+      <c r="U1558">
+        <v>32</v>
+      </c>
+      <c r="V1558">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1559" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1559" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1559" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1559" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1559" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1559" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H1559">
+        <v>5.82</v>
+      </c>
+      <c r="I1559">
+        <v>0.3</v>
+      </c>
+      <c r="J1559">
+        <v>5.5</v>
+      </c>
+      <c r="K1559">
+        <v>0.3</v>
+      </c>
+      <c r="L1559">
+        <v>0.02</v>
+      </c>
+      <c r="M1559">
+        <v>0</v>
+      </c>
+      <c r="N1559">
+        <v>0</v>
+      </c>
+      <c r="O1559">
+        <v>0</v>
+      </c>
+      <c r="P1559">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="Q1559">
+        <v>24.39</v>
+      </c>
+      <c r="R1559">
+        <v>5.13</v>
+      </c>
+      <c r="S1559">
+        <v>35</v>
+      </c>
+      <c r="T1559">
+        <v>12</v>
+      </c>
+      <c r="U1559">
+        <v>34</v>
+      </c>
+      <c r="V1559">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1560" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1560" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1560" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1560" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1560" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1560" t="s">
+        <v>714</v>
+      </c>
+      <c r="H1560">
+        <v>4.45</v>
+      </c>
+      <c r="I1560">
+        <v>0.15</v>
+      </c>
+      <c r="J1560">
+        <v>4.29</v>
+      </c>
+      <c r="K1560">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L1560">
+        <v>0.02</v>
+      </c>
+      <c r="M1560">
+        <v>0</v>
+      </c>
+      <c r="N1560">
+        <v>0</v>
+      </c>
+      <c r="O1560">
+        <v>0</v>
+      </c>
+      <c r="P1560">
+        <v>3.83</v>
+      </c>
+      <c r="Q1560">
+        <v>24.41</v>
+      </c>
+      <c r="R1560">
+        <v>5.22</v>
+      </c>
+      <c r="S1560">
+        <v>19</v>
+      </c>
+      <c r="T1560">
+        <v>6</v>
+      </c>
+      <c r="U1560">
+        <v>23</v>
+      </c>
+      <c r="V1560">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1561" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1561" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1561" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1561" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1561" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1561" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H1561">
+        <v>5.03</v>
+      </c>
+      <c r="I1561">
+        <v>0.2</v>
+      </c>
+      <c r="J1561">
+        <v>4.82</v>
+      </c>
+      <c r="K1561">
+        <v>0.18</v>
+      </c>
+      <c r="L1561">
+        <v>0.03</v>
+      </c>
+      <c r="M1561">
+        <v>0</v>
+      </c>
+      <c r="N1561">
+        <v>0</v>
+      </c>
+      <c r="O1561">
+        <v>0</v>
+      </c>
+      <c r="P1561">
+        <v>3.82</v>
+      </c>
+      <c r="Q1561">
+        <v>22.99</v>
+      </c>
+      <c r="R1561">
+        <v>4.57</v>
+      </c>
+      <c r="S1561">
+        <v>22</v>
+      </c>
+      <c r="T1561">
+        <v>3</v>
+      </c>
+      <c r="U1561">
+        <v>20</v>
+      </c>
+      <c r="V1561">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1562" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1562" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1562" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1562" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1562" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1562" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H1562">
+        <v>6.38</v>
+      </c>
+      <c r="I1562">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J1562">
+        <v>5.8</v>
+      </c>
+      <c r="K1562">
+        <v>0.42</v>
+      </c>
+      <c r="L1562">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M1562">
+        <v>0.02</v>
+      </c>
+      <c r="N1562">
+        <v>0</v>
+      </c>
+      <c r="O1562">
+        <v>3</v>
+      </c>
+      <c r="P1562">
+        <v>4.54</v>
+      </c>
+      <c r="Q1562">
+        <v>27.91</v>
+      </c>
+      <c r="R1562">
+        <v>6.37</v>
+      </c>
+      <c r="S1562">
+        <v>65</v>
+      </c>
+      <c r="T1562">
+        <v>16</v>
+      </c>
+      <c r="U1562">
+        <v>44</v>
+      </c>
+      <c r="V1562">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1563" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1563" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1563" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1563" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1563" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1563" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H1563">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="I1563">
+        <v>1.49</v>
+      </c>
+      <c r="J1563">
+        <v>7.19</v>
+      </c>
+      <c r="K1563">
+        <v>1.17</v>
+      </c>
+      <c r="L1563">
+        <v>0.32</v>
+      </c>
+      <c r="M1563">
+        <v>0.03</v>
+      </c>
+      <c r="N1563">
+        <v>0</v>
+      </c>
+      <c r="O1563">
+        <v>2</v>
+      </c>
+      <c r="P1563">
+        <v>5.91</v>
+      </c>
+      <c r="Q1563">
+        <v>26.32</v>
+      </c>
+      <c r="R1563">
+        <v>4.79</v>
+      </c>
+      <c r="S1563">
+        <v>40</v>
+      </c>
+      <c r="T1563">
+        <v>4</v>
+      </c>
+      <c r="U1563">
+        <v>33</v>
+      </c>
+      <c r="V1563">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1564" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1564" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1564" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1564" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1564" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1564" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H1564">
+        <v>11.38</v>
+      </c>
+      <c r="I1564">
+        <v>2.16</v>
+      </c>
+      <c r="J1564">
+        <v>9.19</v>
+      </c>
+      <c r="K1564">
+        <v>1.61</v>
+      </c>
+      <c r="L1564">
+        <v>0.53</v>
+      </c>
+      <c r="M1564">
+        <v>0.05</v>
+      </c>
+      <c r="N1564">
+        <v>0</v>
+      </c>
+      <c r="O1564">
+        <v>6</v>
+      </c>
+      <c r="P1564">
+        <v>6.71</v>
+      </c>
+      <c r="Q1564">
+        <v>26.92</v>
+      </c>
+      <c r="R1564">
+        <v>4.57</v>
+      </c>
+      <c r="S1564">
+        <v>50</v>
+      </c>
+      <c r="T1564">
+        <v>8</v>
+      </c>
+      <c r="U1564">
+        <v>55</v>
+      </c>
+      <c r="V1564">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1565" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1565" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1565" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1565" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1565" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1565" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H1565">
+        <v>7.65</v>
+      </c>
+      <c r="I1565">
+        <v>1.02</v>
+      </c>
+      <c r="J1565">
+        <v>6.61</v>
+      </c>
+      <c r="K1565">
+        <v>0.68</v>
+      </c>
+      <c r="L1565">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M1565">
+        <v>0.08</v>
+      </c>
+      <c r="N1565">
+        <v>0</v>
+      </c>
+      <c r="O1565">
+        <v>7</v>
+      </c>
+      <c r="P1565">
+        <v>5.32</v>
+      </c>
+      <c r="Q1565">
+        <v>29.16</v>
+      </c>
+      <c r="R1565">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="S1565">
+        <v>36</v>
+      </c>
+      <c r="T1565">
+        <v>3</v>
+      </c>
+      <c r="U1565">
+        <v>28</v>
+      </c>
+      <c r="V1565">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1566" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1566" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1566" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1566" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1566" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1566" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H1566">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I1566">
+        <v>0.2</v>
+      </c>
+      <c r="J1566">
+        <v>0.94</v>
+      </c>
+      <c r="K1566">
+        <v>0.17</v>
+      </c>
+      <c r="L1566">
+        <v>0.02</v>
+      </c>
+      <c r="M1566">
+        <v>0.01</v>
+      </c>
+      <c r="N1566">
+        <v>0</v>
+      </c>
+      <c r="O1566">
+        <v>1</v>
+      </c>
+      <c r="P1566">
+        <v>6.65</v>
+      </c>
+      <c r="Q1566">
+        <v>27.88</v>
+      </c>
+      <c r="R1566">
+        <v>3.05</v>
+      </c>
+      <c r="S1566">
+        <v>1</v>
+      </c>
+      <c r="T1566">
+        <v>0</v>
+      </c>
+      <c r="U1566">
+        <v>2</v>
+      </c>
+      <c r="V1566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1567" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1567" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1567" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1567" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1567" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1567" t="s">
+        <v>404</v>
+      </c>
+      <c r="H1567">
+        <v>11.07</v>
+      </c>
+      <c r="I1567">
+        <v>2.65</v>
+      </c>
+      <c r="J1567">
+        <v>8.39</v>
+      </c>
+      <c r="K1567">
+        <v>2.12</v>
+      </c>
+      <c r="L1567">
+        <v>0.51</v>
+      </c>
+      <c r="M1567">
+        <v>0.05</v>
+      </c>
+      <c r="N1567">
+        <v>0</v>
+      </c>
+      <c r="O1567">
+        <v>4</v>
+      </c>
+      <c r="P1567">
+        <v>7.5</v>
+      </c>
+      <c r="Q1567">
+        <v>27.86</v>
+      </c>
+      <c r="R1567">
+        <v>4.82</v>
+      </c>
+      <c r="S1567">
+        <v>51</v>
+      </c>
+      <c r="T1567">
+        <v>6</v>
+      </c>
+      <c r="U1567">
+        <v>50</v>
+      </c>
+      <c r="V1567">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1568" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1568" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1568" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1568" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1568" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1568" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H1568">
+        <v>9.66</v>
+      </c>
+      <c r="I1568">
+        <v>1.27</v>
+      </c>
+      <c r="J1568">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="K1568">
+        <v>1</v>
+      </c>
+      <c r="L1568">
+        <v>0.22</v>
+      </c>
+      <c r="M1568">
+        <v>0.06</v>
+      </c>
+      <c r="N1568">
+        <v>0</v>
+      </c>
+      <c r="O1568">
+        <v>4</v>
+      </c>
+      <c r="P1568">
+        <v>5.7</v>
+      </c>
+      <c r="Q1568">
+        <v>27.67</v>
+      </c>
+      <c r="R1568">
+        <v>4.49</v>
+      </c>
+      <c r="S1568">
+        <v>26</v>
+      </c>
+      <c r="T1568">
+        <v>2</v>
+      </c>
+      <c r="U1568">
+        <v>22</v>
+      </c>
+      <c r="V1568">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1569" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1569" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1569" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1569" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1569" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1569" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H1569">
+        <v>6.36</v>
+      </c>
+      <c r="I1569">
+        <v>1.29</v>
+      </c>
+      <c r="J1569">
+        <v>5.05</v>
+      </c>
+      <c r="K1569">
+        <v>0.71</v>
+      </c>
+      <c r="L1569">
+        <v>0.44</v>
+      </c>
+      <c r="M1569">
+        <v>0.13</v>
+      </c>
+      <c r="N1569">
+        <v>0.02</v>
+      </c>
+      <c r="O1569">
+        <v>11</v>
+      </c>
+      <c r="P1569">
+        <v>6.39</v>
+      </c>
+      <c r="Q1569">
+        <v>30.89</v>
+      </c>
+      <c r="R1569">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="S1569">
+        <v>30</v>
+      </c>
+      <c r="T1569">
+        <v>9</v>
+      </c>
+      <c r="U1569">
+        <v>25</v>
+      </c>
+      <c r="V1569">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1570" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1570" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1570" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1570" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1570" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1570" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H1570">
+        <v>1.73</v>
+      </c>
+      <c r="I1570">
+        <v>0.34</v>
+      </c>
+      <c r="J1570">
+        <v>1.39</v>
+      </c>
+      <c r="K1570">
+        <v>0.31</v>
+      </c>
+      <c r="L1570">
+        <v>0.03</v>
+      </c>
+      <c r="M1570">
+        <v>0</v>
+      </c>
+      <c r="N1570">
+        <v>0</v>
+      </c>
+      <c r="O1570">
+        <v>0</v>
+      </c>
+      <c r="P1570">
+        <v>7.79</v>
+      </c>
+      <c r="Q1570">
+        <v>23.49</v>
+      </c>
+      <c r="R1570">
+        <v>4.22</v>
+      </c>
+      <c r="S1570">
+        <v>5</v>
+      </c>
+      <c r="T1570">
+        <v>1</v>
+      </c>
+      <c r="U1570">
+        <v>4</v>
+      </c>
+      <c r="V1570">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1571" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1571" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1571" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1571" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1571" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1571" t="s">
+        <v>628</v>
+      </c>
+      <c r="H1571">
+        <v>9.11</v>
+      </c>
+      <c r="I1571">
+        <v>1.97</v>
+      </c>
+      <c r="J1571">
+        <v>7.11</v>
+      </c>
+      <c r="K1571">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L1571">
+        <v>0.66</v>
+      </c>
+      <c r="M1571">
+        <v>0.18</v>
+      </c>
+      <c r="N1571">
+        <v>0.01</v>
+      </c>
+      <c r="O1571">
+        <v>10</v>
+      </c>
+      <c r="P1571">
+        <v>6.77</v>
+      </c>
+      <c r="Q1571">
+        <v>30.24</v>
+      </c>
+      <c r="R1571">
+        <v>4.63</v>
+      </c>
+      <c r="S1571">
+        <v>40</v>
+      </c>
+      <c r="T1571">
+        <v>7</v>
+      </c>
+      <c r="U1571">
+        <v>40</v>
+      </c>
+      <c r="V1571">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1572" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1572" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1572" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1572" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1572" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1572" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H1572">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I1572">
+        <v>0.94</v>
+      </c>
+      <c r="J1572">
+        <v>7.75</v>
+      </c>
+      <c r="K1572">
+        <v>0.61</v>
+      </c>
+      <c r="L1572">
+        <v>0.24</v>
+      </c>
+      <c r="M1572">
+        <v>0.11</v>
+      </c>
+      <c r="N1572">
+        <v>0</v>
+      </c>
+      <c r="O1572">
+        <v>6</v>
+      </c>
+      <c r="P1572">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="Q1572">
+        <v>28.94</v>
+      </c>
+      <c r="R1572">
+        <v>3.96</v>
+      </c>
+      <c r="S1572">
+        <v>27</v>
+      </c>
+      <c r="T1572">
+        <v>0</v>
+      </c>
+      <c r="U1572">
+        <v>28</v>
+      </c>
+      <c r="V1572">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1573" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1573" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1573" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1573" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1573" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1573" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H1573">
+        <v>12.02</v>
+      </c>
+      <c r="I1573">
+        <v>2.41</v>
+      </c>
+      <c r="J1573">
+        <v>9.59</v>
+      </c>
+      <c r="K1573">
+        <v>1.85</v>
+      </c>
+      <c r="L1573">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M1573">
+        <v>0.03</v>
+      </c>
+      <c r="N1573">
+        <v>0</v>
+      </c>
+      <c r="O1573">
+        <v>2</v>
+      </c>
+      <c r="P1573">
+        <v>7.09</v>
+      </c>
+      <c r="Q1573">
+        <v>27.02</v>
+      </c>
+      <c r="R1573">
+        <v>4.54</v>
+      </c>
+      <c r="S1573">
+        <v>31</v>
+      </c>
+      <c r="T1573">
+        <v>4</v>
+      </c>
+      <c r="U1573">
+        <v>37</v>
+      </c>
+      <c r="V1573">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDFF5FC-EABE-E84B-A6DE-860D7C00F02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BB122C-B76D-4547-AABC-B4236B38D525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8940" uniqueCount="1284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9156" uniqueCount="1316">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3887,13 +3887,109 @@
   </si>
   <si>
     <t>01:41:23</t>
+  </si>
+  <si>
+    <t>01:17:16</t>
+  </si>
+  <si>
+    <t>01:33:46</t>
+  </si>
+  <si>
+    <t>01:34:01</t>
+  </si>
+  <si>
+    <t>01:34:20</t>
+  </si>
+  <si>
+    <t>01:34:35</t>
+  </si>
+  <si>
+    <t>N3 J21 VS Beaucaire 28/03/2026</t>
+  </si>
+  <si>
+    <t>01:35:17</t>
+  </si>
+  <si>
+    <t>01:23:38</t>
+  </si>
+  <si>
+    <t>01:33:30</t>
+  </si>
+  <si>
+    <t>01:35:40</t>
+  </si>
+  <si>
+    <t>01:11:51</t>
+  </si>
+  <si>
+    <t>01:36:43</t>
+  </si>
+  <si>
+    <t>01:33:20</t>
+  </si>
+  <si>
+    <t>01:33:28</t>
+  </si>
+  <si>
+    <t>01:33:36</t>
+  </si>
+  <si>
+    <t>01:35:01</t>
+  </si>
+  <si>
+    <t>01:35:00</t>
+  </si>
+  <si>
+    <t>01:35:37</t>
+  </si>
+  <si>
+    <t>01:35:08</t>
+  </si>
+  <si>
+    <t>01:36:19</t>
+  </si>
+  <si>
+    <t>01:42:42</t>
+  </si>
+  <si>
+    <t>01:41:14</t>
+  </si>
+  <si>
+    <t>01:35:33</t>
+  </si>
+  <si>
+    <t>01:41:41</t>
+  </si>
+  <si>
+    <t>01:40:57</t>
+  </si>
+  <si>
+    <t>00:51:17</t>
+  </si>
+  <si>
+    <t>00:50:24</t>
+  </si>
+  <si>
+    <t>00:50:33</t>
+  </si>
+  <si>
+    <t>00:35:50</t>
+  </si>
+  <si>
+    <t>00:51:08</t>
+  </si>
+  <si>
+    <t>00:40:21</t>
+  </si>
+  <si>
+    <t>N3 J17 VS Seyssinet 04/04/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3930,6 +4026,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3951,7 +4053,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3976,6 +4078,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4290,7 +4393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1573"/>
+  <dimension ref="A1:V1609"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -108978,7 +109081,7 @@
     </row>
     <row r="1563" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1563" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1563" s="1">
         <v>46109</v>
@@ -109046,7 +109149,7 @@
     </row>
     <row r="1564" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1564" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1564" s="1">
         <v>46109</v>
@@ -109114,7 +109217,7 @@
     </row>
     <row r="1565" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1565" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1565" s="1">
         <v>46109</v>
@@ -109182,7 +109285,7 @@
     </row>
     <row r="1566" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1566" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1566" s="1">
         <v>46109</v>
@@ -109250,7 +109353,7 @@
     </row>
     <row r="1567" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1567" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1567" s="1">
         <v>46109</v>
@@ -109318,7 +109421,7 @@
     </row>
     <row r="1568" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1568" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1568" s="1">
         <v>46109</v>
@@ -109386,7 +109489,7 @@
     </row>
     <row r="1569" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1569" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1569" s="1">
         <v>46109</v>
@@ -109454,7 +109557,7 @@
     </row>
     <row r="1570" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1570" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1570" s="1">
         <v>46109</v>
@@ -109522,7 +109625,7 @@
     </row>
     <row r="1571" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1571" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1571" s="1">
         <v>46109</v>
@@ -109590,7 +109693,7 @@
     </row>
     <row r="1572" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1572" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1572" s="1">
         <v>46109</v>
@@ -109658,7 +109761,7 @@
     </row>
     <row r="1573" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1573" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="B1573" s="1">
         <v>46109</v>
@@ -109722,6 +109825,2454 @@
       </c>
       <c r="V1573">
         <v>11</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1574" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1574" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1574" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1574" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1574" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1574" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H1574">
+        <v>6.07</v>
+      </c>
+      <c r="I1574">
+        <v>0.1</v>
+      </c>
+      <c r="J1574">
+        <v>5.97</v>
+      </c>
+      <c r="K1574">
+        <v>0.1</v>
+      </c>
+      <c r="L1574">
+        <v>0</v>
+      </c>
+      <c r="M1574">
+        <v>0</v>
+      </c>
+      <c r="N1574">
+        <v>0</v>
+      </c>
+      <c r="O1574">
+        <v>0</v>
+      </c>
+      <c r="P1574">
+        <v>4.66</v>
+      </c>
+      <c r="Q1574">
+        <v>19.75</v>
+      </c>
+      <c r="R1574">
+        <v>4.21</v>
+      </c>
+      <c r="S1574">
+        <v>29</v>
+      </c>
+      <c r="T1574">
+        <v>2</v>
+      </c>
+      <c r="U1574">
+        <v>23</v>
+      </c>
+      <c r="V1574">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1575" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1575" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1575" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1575" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1575" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1575" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H1575">
+        <v>7.98</v>
+      </c>
+      <c r="I1575">
+        <v>0.2</v>
+      </c>
+      <c r="J1575">
+        <v>7.77</v>
+      </c>
+      <c r="K1575">
+        <v>0.2</v>
+      </c>
+      <c r="L1575">
+        <v>0.01</v>
+      </c>
+      <c r="M1575">
+        <v>0</v>
+      </c>
+      <c r="N1575">
+        <v>0</v>
+      </c>
+      <c r="O1575">
+        <v>0</v>
+      </c>
+      <c r="P1575">
+        <v>4.59</v>
+      </c>
+      <c r="Q1575">
+        <v>23.79</v>
+      </c>
+      <c r="R1575">
+        <v>5.15</v>
+      </c>
+      <c r="S1575">
+        <v>72</v>
+      </c>
+      <c r="T1575">
+        <v>9</v>
+      </c>
+      <c r="U1575">
+        <v>59</v>
+      </c>
+      <c r="V1575">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1576" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1576" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1576" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1576" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1576" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1576" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H1576">
+        <v>7.55</v>
+      </c>
+      <c r="I1576">
+        <v>0.11</v>
+      </c>
+      <c r="J1576">
+        <v>7.44</v>
+      </c>
+      <c r="K1576">
+        <v>0.11</v>
+      </c>
+      <c r="L1576">
+        <v>0</v>
+      </c>
+      <c r="M1576">
+        <v>0</v>
+      </c>
+      <c r="N1576">
+        <v>0</v>
+      </c>
+      <c r="O1576">
+        <v>0</v>
+      </c>
+      <c r="P1576">
+        <v>4.75</v>
+      </c>
+      <c r="Q1576">
+        <v>20.7</v>
+      </c>
+      <c r="R1576">
+        <v>4.18</v>
+      </c>
+      <c r="S1576">
+        <v>34</v>
+      </c>
+      <c r="T1576">
+        <v>3</v>
+      </c>
+      <c r="U1576">
+        <v>20</v>
+      </c>
+      <c r="V1576">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1577" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1577" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1577" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1577" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1577" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1577" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1577">
+        <v>6.61</v>
+      </c>
+      <c r="I1577">
+        <v>0.17</v>
+      </c>
+      <c r="J1577">
+        <v>6.43</v>
+      </c>
+      <c r="K1577">
+        <v>0.17</v>
+      </c>
+      <c r="L1577">
+        <v>0.01</v>
+      </c>
+      <c r="M1577">
+        <v>0</v>
+      </c>
+      <c r="N1577">
+        <v>0</v>
+      </c>
+      <c r="O1577">
+        <v>0</v>
+      </c>
+      <c r="P1577">
+        <v>3.92</v>
+      </c>
+      <c r="Q1577">
+        <v>21.89</v>
+      </c>
+      <c r="R1577">
+        <v>5.34</v>
+      </c>
+      <c r="S1577">
+        <v>66</v>
+      </c>
+      <c r="T1577">
+        <v>21</v>
+      </c>
+      <c r="U1577">
+        <v>57</v>
+      </c>
+      <c r="V1577">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1578" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1578" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1578" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1578" s="12" t="s">
+        <v>741</v>
+      </c>
+      <c r="F1578" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1578" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H1578">
+        <v>6.9</v>
+      </c>
+      <c r="I1578">
+        <v>0.15</v>
+      </c>
+      <c r="J1578">
+        <v>6.74</v>
+      </c>
+      <c r="K1578">
+        <v>0.15</v>
+      </c>
+      <c r="L1578">
+        <v>0.01</v>
+      </c>
+      <c r="M1578">
+        <v>0</v>
+      </c>
+      <c r="N1578">
+        <v>0</v>
+      </c>
+      <c r="O1578">
+        <v>0</v>
+      </c>
+      <c r="P1578">
+        <v>4.32</v>
+      </c>
+      <c r="Q1578">
+        <v>20.98</v>
+      </c>
+      <c r="R1578">
+        <v>3.82</v>
+      </c>
+      <c r="S1578">
+        <v>25</v>
+      </c>
+      <c r="T1578">
+        <v>0</v>
+      </c>
+      <c r="U1578">
+        <v>20</v>
+      </c>
+      <c r="V1578">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1579" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1579" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1579" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1579" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1579" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1579" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H1579">
+        <v>7.5</v>
+      </c>
+      <c r="I1579">
+        <v>0.24</v>
+      </c>
+      <c r="J1579">
+        <v>7.25</v>
+      </c>
+      <c r="K1579">
+        <v>0.25</v>
+      </c>
+      <c r="L1579">
+        <v>0.01</v>
+      </c>
+      <c r="M1579">
+        <v>0</v>
+      </c>
+      <c r="N1579">
+        <v>0</v>
+      </c>
+      <c r="O1579">
+        <v>0</v>
+      </c>
+      <c r="P1579">
+        <v>4.29</v>
+      </c>
+      <c r="Q1579">
+        <v>22.61</v>
+      </c>
+      <c r="R1579">
+        <v>4.96</v>
+      </c>
+      <c r="S1579">
+        <v>55</v>
+      </c>
+      <c r="T1579">
+        <v>14</v>
+      </c>
+      <c r="U1579">
+        <v>47</v>
+      </c>
+      <c r="V1579">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1580" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1580" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1580" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1580" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1580" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1580" t="s">
+        <v>1290</v>
+      </c>
+      <c r="H1580">
+        <v>7.84</v>
+      </c>
+      <c r="I1580">
+        <v>0.31</v>
+      </c>
+      <c r="J1580">
+        <v>7.52</v>
+      </c>
+      <c r="K1580">
+        <v>0.19</v>
+      </c>
+      <c r="L1580">
+        <v>0.1</v>
+      </c>
+      <c r="M1580">
+        <v>0.03</v>
+      </c>
+      <c r="N1580">
+        <v>0</v>
+      </c>
+      <c r="O1580">
+        <v>5</v>
+      </c>
+      <c r="P1580">
+        <v>3.68</v>
+      </c>
+      <c r="Q1580">
+        <v>30.41</v>
+      </c>
+      <c r="R1580">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="S1580">
+        <v>35</v>
+      </c>
+      <c r="T1580">
+        <v>2</v>
+      </c>
+      <c r="U1580">
+        <v>34</v>
+      </c>
+      <c r="V1580">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1581" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1581" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1581" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1581" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1581" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1581" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H1581">
+        <v>8.18</v>
+      </c>
+      <c r="I1581">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J1581">
+        <v>7.61</v>
+      </c>
+      <c r="K1581">
+        <v>0.3</v>
+      </c>
+      <c r="L1581">
+        <v>0.18</v>
+      </c>
+      <c r="M1581">
+        <v>0.09</v>
+      </c>
+      <c r="N1581">
+        <v>0</v>
+      </c>
+      <c r="O1581">
+        <v>6</v>
+      </c>
+      <c r="P1581">
+        <v>4.03</v>
+      </c>
+      <c r="Q1581">
+        <v>28.81</v>
+      </c>
+      <c r="R1581">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="S1581">
+        <v>14</v>
+      </c>
+      <c r="T1581">
+        <v>5</v>
+      </c>
+      <c r="U1581">
+        <v>11</v>
+      </c>
+      <c r="V1581">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1582" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1582" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1582" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1582" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1582" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1582" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H1582">
+        <v>7.37</v>
+      </c>
+      <c r="I1582">
+        <v>0.78</v>
+      </c>
+      <c r="J1582">
+        <v>6.58</v>
+      </c>
+      <c r="K1582">
+        <v>0.5</v>
+      </c>
+      <c r="L1582">
+        <v>0.21</v>
+      </c>
+      <c r="M1582">
+        <v>0.08</v>
+      </c>
+      <c r="N1582">
+        <v>0.01</v>
+      </c>
+      <c r="O1582">
+        <v>6</v>
+      </c>
+      <c r="P1582">
+        <v>4.66</v>
+      </c>
+      <c r="Q1582">
+        <v>30.73</v>
+      </c>
+      <c r="R1582">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="S1582">
+        <v>39</v>
+      </c>
+      <c r="T1582">
+        <v>1</v>
+      </c>
+      <c r="U1582">
+        <v>32</v>
+      </c>
+      <c r="V1582">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1583" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1583" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1583" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1583" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1583" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1583" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H1583">
+        <v>7.18</v>
+      </c>
+      <c r="I1583">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J1583">
+        <v>6.59</v>
+      </c>
+      <c r="K1583">
+        <v>0.48</v>
+      </c>
+      <c r="L1583">
+        <v>0.11</v>
+      </c>
+      <c r="M1583">
+        <v>0</v>
+      </c>
+      <c r="N1583">
+        <v>0</v>
+      </c>
+      <c r="O1583">
+        <v>0</v>
+      </c>
+      <c r="P1583">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q1583">
+        <v>22.65</v>
+      </c>
+      <c r="R1583">
+        <v>4.22</v>
+      </c>
+      <c r="S1583">
+        <v>26</v>
+      </c>
+      <c r="T1583">
+        <v>1</v>
+      </c>
+      <c r="U1583">
+        <v>22</v>
+      </c>
+      <c r="V1583">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1584" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1584" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1584" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1584" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1584" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1584" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H1584">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="I1584">
+        <v>0.39</v>
+      </c>
+      <c r="J1584">
+        <v>4.45</v>
+      </c>
+      <c r="K1584">
+        <v>0.25</v>
+      </c>
+      <c r="L1584">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M1584">
+        <v>0.01</v>
+      </c>
+      <c r="N1584">
+        <v>0</v>
+      </c>
+      <c r="O1584">
+        <v>3</v>
+      </c>
+      <c r="P1584">
+        <v>3.53</v>
+      </c>
+      <c r="Q1584">
+        <v>26.02</v>
+      </c>
+      <c r="R1584">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="S1584">
+        <v>30</v>
+      </c>
+      <c r="T1584">
+        <v>2</v>
+      </c>
+      <c r="U1584">
+        <v>20</v>
+      </c>
+      <c r="V1584">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1585" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1585" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1585" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1585" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1585" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1585" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1585" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H1585">
+        <v>7.7</v>
+      </c>
+      <c r="I1585">
+        <v>0.44</v>
+      </c>
+      <c r="J1585">
+        <v>7.25</v>
+      </c>
+      <c r="K1585">
+        <v>0.38</v>
+      </c>
+      <c r="L1585">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M1585">
+        <v>0</v>
+      </c>
+      <c r="N1585">
+        <v>0</v>
+      </c>
+      <c r="O1585">
+        <v>1</v>
+      </c>
+      <c r="P1585">
+        <v>4.68</v>
+      </c>
+      <c r="Q1585">
+        <v>25.71</v>
+      </c>
+      <c r="R1585">
+        <v>3.83</v>
+      </c>
+      <c r="S1585">
+        <v>25</v>
+      </c>
+      <c r="T1585">
+        <v>0</v>
+      </c>
+      <c r="U1585">
+        <v>14</v>
+      </c>
+      <c r="V1585">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1586" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1586" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1586" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1586" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1586" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1586" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1586" t="s">
+        <v>684</v>
+      </c>
+      <c r="H1586">
+        <v>7.39</v>
+      </c>
+      <c r="I1586">
+        <v>0.83</v>
+      </c>
+      <c r="J1586">
+        <v>6.54</v>
+      </c>
+      <c r="K1586">
+        <v>0.53</v>
+      </c>
+      <c r="L1586">
+        <v>0.22</v>
+      </c>
+      <c r="M1586">
+        <v>0.1</v>
+      </c>
+      <c r="N1586">
+        <v>0</v>
+      </c>
+      <c r="O1586">
+        <v>8</v>
+      </c>
+      <c r="P1586">
+        <v>4.76</v>
+      </c>
+      <c r="Q1586">
+        <v>30.31</v>
+      </c>
+      <c r="R1586">
+        <v>5.48</v>
+      </c>
+      <c r="S1586">
+        <v>57</v>
+      </c>
+      <c r="T1586">
+        <v>16</v>
+      </c>
+      <c r="U1586">
+        <v>41</v>
+      </c>
+      <c r="V1586">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1587" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1587" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1587" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1587" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1587" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1587" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1587" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H1587">
+        <v>7.16</v>
+      </c>
+      <c r="I1587">
+        <v>0.48</v>
+      </c>
+      <c r="J1587">
+        <v>6.66</v>
+      </c>
+      <c r="K1587">
+        <v>0.4</v>
+      </c>
+      <c r="L1587">
+        <v>0.08</v>
+      </c>
+      <c r="M1587">
+        <v>0.02</v>
+      </c>
+      <c r="N1587">
+        <v>0</v>
+      </c>
+      <c r="O1587">
+        <v>3</v>
+      </c>
+      <c r="P1587">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="Q1587">
+        <v>27.58</v>
+      </c>
+      <c r="R1587">
+        <v>5.01</v>
+      </c>
+      <c r="S1587">
+        <v>61</v>
+      </c>
+      <c r="T1587">
+        <v>13</v>
+      </c>
+      <c r="U1587">
+        <v>47</v>
+      </c>
+      <c r="V1587">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1588" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1588" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1588" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1588" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1588" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1588" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1588" t="s">
+        <v>1297</v>
+      </c>
+      <c r="H1588">
+        <v>7.71</v>
+      </c>
+      <c r="I1588">
+        <v>0.67</v>
+      </c>
+      <c r="J1588">
+        <v>7.02</v>
+      </c>
+      <c r="K1588">
+        <v>0.61</v>
+      </c>
+      <c r="L1588">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M1588">
+        <v>0</v>
+      </c>
+      <c r="N1588">
+        <v>0</v>
+      </c>
+      <c r="O1588">
+        <v>0</v>
+      </c>
+      <c r="P1588">
+        <v>4.83</v>
+      </c>
+      <c r="Q1588">
+        <v>23.19</v>
+      </c>
+      <c r="R1588">
+        <v>4.75</v>
+      </c>
+      <c r="S1588">
+        <v>39</v>
+      </c>
+      <c r="T1588">
+        <v>11</v>
+      </c>
+      <c r="U1588">
+        <v>25</v>
+      </c>
+      <c r="V1588">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1589" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1589" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1589" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1589" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1589" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1589" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1589" t="s">
+        <v>443</v>
+      </c>
+      <c r="H1589">
+        <v>7.06</v>
+      </c>
+      <c r="I1589">
+        <v>0.82</v>
+      </c>
+      <c r="J1589">
+        <v>6.21</v>
+      </c>
+      <c r="K1589">
+        <v>0.49</v>
+      </c>
+      <c r="L1589">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M1589">
+        <v>0.06</v>
+      </c>
+      <c r="N1589">
+        <v>0.01</v>
+      </c>
+      <c r="O1589">
+        <v>12</v>
+      </c>
+      <c r="P1589">
+        <v>4.29</v>
+      </c>
+      <c r="Q1589">
+        <v>31.28</v>
+      </c>
+      <c r="R1589">
+        <v>6.4</v>
+      </c>
+      <c r="S1589">
+        <v>94</v>
+      </c>
+      <c r="T1589">
+        <v>30</v>
+      </c>
+      <c r="U1589">
+        <v>64</v>
+      </c>
+      <c r="V1589">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1590" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1590" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1590" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1590" t="s">
+        <v>741</v>
+      </c>
+      <c r="F1590" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1590" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H1590">
+        <v>7.02</v>
+      </c>
+      <c r="I1590">
+        <v>0.84</v>
+      </c>
+      <c r="J1590">
+        <v>6.17</v>
+      </c>
+      <c r="K1590">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L1590">
+        <v>0.18</v>
+      </c>
+      <c r="M1590">
+        <v>0.11</v>
+      </c>
+      <c r="N1590">
+        <v>0</v>
+      </c>
+      <c r="O1590">
+        <v>7</v>
+      </c>
+      <c r="P1590">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="Q1590">
+        <v>29.53</v>
+      </c>
+      <c r="R1590">
+        <v>4.68</v>
+      </c>
+      <c r="S1590">
+        <v>31</v>
+      </c>
+      <c r="T1590">
+        <v>3</v>
+      </c>
+      <c r="U1590">
+        <v>25</v>
+      </c>
+      <c r="V1590">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1591" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1591" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1591" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1591" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1591" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1591" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H1591">
+        <v>6.52</v>
+      </c>
+      <c r="I1591">
+        <v>0.27</v>
+      </c>
+      <c r="J1591">
+        <v>6.24</v>
+      </c>
+      <c r="K1591">
+        <v>0.25</v>
+      </c>
+      <c r="L1591">
+        <v>0.02</v>
+      </c>
+      <c r="M1591">
+        <v>0</v>
+      </c>
+      <c r="N1591">
+        <v>0</v>
+      </c>
+      <c r="O1591">
+        <v>0</v>
+      </c>
+      <c r="P1591">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="Q1591">
+        <v>22.65</v>
+      </c>
+      <c r="R1591">
+        <v>4.26</v>
+      </c>
+      <c r="S1591">
+        <v>39</v>
+      </c>
+      <c r="T1591">
+        <v>3</v>
+      </c>
+      <c r="U1591">
+        <v>17</v>
+      </c>
+      <c r="V1591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1592" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1592" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C1592" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1592" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1592" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1592" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1592" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H1592">
+        <v>6.96</v>
+      </c>
+      <c r="I1592">
+        <v>0.22</v>
+      </c>
+      <c r="J1592">
+        <v>6.74</v>
+      </c>
+      <c r="K1592">
+        <v>0.21</v>
+      </c>
+      <c r="L1592">
+        <v>0.02</v>
+      </c>
+      <c r="M1592">
+        <v>0</v>
+      </c>
+      <c r="N1592">
+        <v>0</v>
+      </c>
+      <c r="O1592">
+        <v>0</v>
+      </c>
+      <c r="P1592">
+        <v>3.79</v>
+      </c>
+      <c r="Q1592">
+        <v>21.72</v>
+      </c>
+      <c r="R1592">
+        <v>5.19</v>
+      </c>
+      <c r="S1592">
+        <v>39</v>
+      </c>
+      <c r="T1592">
+        <v>9</v>
+      </c>
+      <c r="U1592">
+        <v>50</v>
+      </c>
+      <c r="V1592">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1593" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1593" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C1593" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1593" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1593" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1593" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1593" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H1593">
+        <v>6.92</v>
+      </c>
+      <c r="I1593">
+        <v>0.22</v>
+      </c>
+      <c r="J1593">
+        <v>6.69</v>
+      </c>
+      <c r="K1593">
+        <v>0.19</v>
+      </c>
+      <c r="L1593">
+        <v>0.04</v>
+      </c>
+      <c r="M1593">
+        <v>0</v>
+      </c>
+      <c r="N1593">
+        <v>0</v>
+      </c>
+      <c r="O1593">
+        <v>0</v>
+      </c>
+      <c r="P1593">
+        <v>4.26</v>
+      </c>
+      <c r="Q1593">
+        <v>24.44</v>
+      </c>
+      <c r="R1593">
+        <v>4.59</v>
+      </c>
+      <c r="S1593">
+        <v>27</v>
+      </c>
+      <c r="T1593">
+        <v>3</v>
+      </c>
+      <c r="U1593">
+        <v>16</v>
+      </c>
+      <c r="V1593">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1594" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1594" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C1594" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1594" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1594" t="s">
+        <v>741</v>
+      </c>
+      <c r="F1594" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1594" t="s">
+        <v>1302</v>
+      </c>
+      <c r="H1594">
+        <v>6.88</v>
+      </c>
+      <c r="I1594">
+        <v>0.41</v>
+      </c>
+      <c r="J1594">
+        <v>6.46</v>
+      </c>
+      <c r="K1594">
+        <v>0.35</v>
+      </c>
+      <c r="L1594">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M1594">
+        <v>0</v>
+      </c>
+      <c r="N1594">
+        <v>0</v>
+      </c>
+      <c r="O1594">
+        <v>1</v>
+      </c>
+      <c r="P1594">
+        <v>3.88</v>
+      </c>
+      <c r="Q1594">
+        <v>25.3</v>
+      </c>
+      <c r="R1594">
+        <v>5.28</v>
+      </c>
+      <c r="S1594">
+        <v>55</v>
+      </c>
+      <c r="T1594">
+        <v>16</v>
+      </c>
+      <c r="U1594">
+        <v>38</v>
+      </c>
+      <c r="V1594">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1595" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1595" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C1595" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1595" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1595" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1595" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1595" t="s">
+        <v>1303</v>
+      </c>
+      <c r="H1595">
+        <v>6.84</v>
+      </c>
+      <c r="I1595">
+        <v>0.38</v>
+      </c>
+      <c r="J1595">
+        <v>6.44</v>
+      </c>
+      <c r="K1595">
+        <v>0.27</v>
+      </c>
+      <c r="L1595">
+        <v>0.12</v>
+      </c>
+      <c r="M1595">
+        <v>0.01</v>
+      </c>
+      <c r="N1595">
+        <v>0</v>
+      </c>
+      <c r="O1595">
+        <v>2</v>
+      </c>
+      <c r="P1595">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="Q1595">
+        <v>26.19</v>
+      </c>
+      <c r="R1595">
+        <v>4.97</v>
+      </c>
+      <c r="S1595">
+        <v>48</v>
+      </c>
+      <c r="T1595">
+        <v>9</v>
+      </c>
+      <c r="U1595">
+        <v>27</v>
+      </c>
+      <c r="V1595">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1596" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1596" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C1596" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1596" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1596" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1596" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1596" t="s">
+        <v>1303</v>
+      </c>
+      <c r="H1596">
+        <v>7.39</v>
+      </c>
+      <c r="I1596">
+        <v>0.3</v>
+      </c>
+      <c r="J1596">
+        <v>7.09</v>
+      </c>
+      <c r="K1596">
+        <v>0.22</v>
+      </c>
+      <c r="L1596">
+        <v>0.08</v>
+      </c>
+      <c r="M1596">
+        <v>0.01</v>
+      </c>
+      <c r="N1596">
+        <v>0</v>
+      </c>
+      <c r="O1596">
+        <v>1</v>
+      </c>
+      <c r="P1596">
+        <v>3.19</v>
+      </c>
+      <c r="Q1596">
+        <v>25.53</v>
+      </c>
+      <c r="R1596">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="S1596">
+        <v>9</v>
+      </c>
+      <c r="T1596">
+        <v>1</v>
+      </c>
+      <c r="U1596">
+        <v>9</v>
+      </c>
+      <c r="V1596">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1597" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1597" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1597" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1597" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1597" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1597" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H1597">
+        <v>11.54</v>
+      </c>
+      <c r="I1597">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="J1597">
+        <v>9.51</v>
+      </c>
+      <c r="K1597">
+        <v>1.43</v>
+      </c>
+      <c r="L1597">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M1597">
+        <v>0.04</v>
+      </c>
+      <c r="N1597">
+        <v>0</v>
+      </c>
+      <c r="O1597">
+        <v>6</v>
+      </c>
+      <c r="P1597">
+        <v>6.67</v>
+      </c>
+      <c r="Q1597">
+        <v>26.83</v>
+      </c>
+      <c r="R1597">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="S1597">
+        <v>36</v>
+      </c>
+      <c r="T1597">
+        <v>2</v>
+      </c>
+      <c r="U1597">
+        <v>32</v>
+      </c>
+      <c r="V1597">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1598" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1598" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1598" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1598" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1598" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1598" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1598" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H1598">
+        <v>10.62</v>
+      </c>
+      <c r="I1598">
+        <v>1.3</v>
+      </c>
+      <c r="J1598">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="K1598">
+        <v>0.95</v>
+      </c>
+      <c r="L1598">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M1598">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N1598">
+        <v>0.02</v>
+      </c>
+      <c r="O1598">
+        <v>4</v>
+      </c>
+      <c r="P1598">
+        <v>6.3</v>
+      </c>
+      <c r="Q1598">
+        <v>31.14</v>
+      </c>
+      <c r="R1598">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S1598">
+        <v>38</v>
+      </c>
+      <c r="T1598">
+        <v>1</v>
+      </c>
+      <c r="U1598">
+        <v>34</v>
+      </c>
+      <c r="V1598">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1599" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1599" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1599" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1599" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1599" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1599" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1599" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H1599">
+        <v>10.65</v>
+      </c>
+      <c r="I1599">
+        <v>2.58</v>
+      </c>
+      <c r="J1599">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="K1599">
+        <v>1.46</v>
+      </c>
+      <c r="L1599">
+        <v>0.85</v>
+      </c>
+      <c r="M1599">
+        <v>0.25</v>
+      </c>
+      <c r="N1599">
+        <v>0.06</v>
+      </c>
+      <c r="O1599">
+        <v>16</v>
+      </c>
+      <c r="P1599">
+        <v>6.63</v>
+      </c>
+      <c r="Q1599">
+        <v>32.21</v>
+      </c>
+      <c r="R1599">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="S1599">
+        <v>52</v>
+      </c>
+      <c r="T1599">
+        <v>7</v>
+      </c>
+      <c r="U1599">
+        <v>50</v>
+      </c>
+      <c r="V1599">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1600" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1600" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1600" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1600" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1600" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1600" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1600" t="s">
+        <v>690</v>
+      </c>
+      <c r="H1600">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="I1600">
+        <v>2.15</v>
+      </c>
+      <c r="J1600">
+        <v>5.96</v>
+      </c>
+      <c r="K1600">
+        <v>1.61</v>
+      </c>
+      <c r="L1600">
+        <v>0.52</v>
+      </c>
+      <c r="M1600">
+        <v>0.03</v>
+      </c>
+      <c r="N1600">
+        <v>0.01</v>
+      </c>
+      <c r="O1600">
+        <v>2</v>
+      </c>
+      <c r="P1600">
+        <v>7.37</v>
+      </c>
+      <c r="Q1600">
+        <v>30.62</v>
+      </c>
+      <c r="R1600">
+        <v>4.5</v>
+      </c>
+      <c r="S1600">
+        <v>36</v>
+      </c>
+      <c r="T1600">
+        <v>6</v>
+      </c>
+      <c r="U1600">
+        <v>36</v>
+      </c>
+      <c r="V1600">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1601" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1601" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1601" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1601" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1601" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1601" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1601" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H1601">
+        <v>12.35</v>
+      </c>
+      <c r="I1601">
+        <v>2.73</v>
+      </c>
+      <c r="J1601">
+        <v>9.59</v>
+      </c>
+      <c r="K1601">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="L1601">
+        <v>0.63</v>
+      </c>
+      <c r="M1601">
+        <v>0.1</v>
+      </c>
+      <c r="N1601">
+        <v>0</v>
+      </c>
+      <c r="O1601">
+        <v>6</v>
+      </c>
+      <c r="P1601">
+        <v>7.24</v>
+      </c>
+      <c r="Q1601">
+        <v>28.95</v>
+      </c>
+      <c r="R1601">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="S1601">
+        <v>32</v>
+      </c>
+      <c r="T1601">
+        <v>6</v>
+      </c>
+      <c r="U1601">
+        <v>46</v>
+      </c>
+      <c r="V1601">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1602" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1602" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1602" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1602" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1602" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1602" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1602" t="s">
+        <v>1308</v>
+      </c>
+      <c r="H1602">
+        <v>11.62</v>
+      </c>
+      <c r="I1602">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="J1602">
+        <v>9.42</v>
+      </c>
+      <c r="K1602">
+        <v>1.46</v>
+      </c>
+      <c r="L1602">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M1602">
+        <v>0.17</v>
+      </c>
+      <c r="N1602">
+        <v>0.01</v>
+      </c>
+      <c r="O1602">
+        <v>13</v>
+      </c>
+      <c r="P1602">
+        <v>6.88</v>
+      </c>
+      <c r="Q1602">
+        <v>30.58</v>
+      </c>
+      <c r="R1602">
+        <v>4.53</v>
+      </c>
+      <c r="S1602">
+        <v>31</v>
+      </c>
+      <c r="T1602">
+        <v>4</v>
+      </c>
+      <c r="U1602">
+        <v>45</v>
+      </c>
+      <c r="V1602">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1603" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1603" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1603" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1603" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1603" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1603" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1603" t="s">
+        <v>1309</v>
+      </c>
+      <c r="H1603">
+        <v>6.2</v>
+      </c>
+      <c r="I1603">
+        <v>1.43</v>
+      </c>
+      <c r="J1603">
+        <v>4.76</v>
+      </c>
+      <c r="K1603">
+        <v>0.96</v>
+      </c>
+      <c r="L1603">
+        <v>0.33</v>
+      </c>
+      <c r="M1603">
+        <v>0.11</v>
+      </c>
+      <c r="N1603">
+        <v>0.04</v>
+      </c>
+      <c r="O1603">
+        <v>8</v>
+      </c>
+      <c r="P1603">
+        <v>7.14</v>
+      </c>
+      <c r="Q1603">
+        <v>31.54</v>
+      </c>
+      <c r="R1603">
+        <v>4.12</v>
+      </c>
+      <c r="S1603">
+        <v>32</v>
+      </c>
+      <c r="T1603">
+        <v>1</v>
+      </c>
+      <c r="U1603">
+        <v>26</v>
+      </c>
+      <c r="V1603">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1604" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1604" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1604" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1604" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1604" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1604" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1604" t="s">
+        <v>1310</v>
+      </c>
+      <c r="H1604">
+        <v>5.59</v>
+      </c>
+      <c r="I1604">
+        <v>1.24</v>
+      </c>
+      <c r="J1604">
+        <v>4.34</v>
+      </c>
+      <c r="K1604">
+        <v>0.77</v>
+      </c>
+      <c r="L1604">
+        <v>0.31</v>
+      </c>
+      <c r="M1604">
+        <v>0.17</v>
+      </c>
+      <c r="N1604">
+        <v>0.01</v>
+      </c>
+      <c r="O1604">
+        <v>12</v>
+      </c>
+      <c r="P1604">
+        <v>6.61</v>
+      </c>
+      <c r="Q1604">
+        <v>30.83</v>
+      </c>
+      <c r="R1604">
+        <v>4.55</v>
+      </c>
+      <c r="S1604">
+        <v>25</v>
+      </c>
+      <c r="T1604">
+        <v>6</v>
+      </c>
+      <c r="U1604">
+        <v>16</v>
+      </c>
+      <c r="V1604">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1605" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1605" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1605" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1605" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1605" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1605" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1605" t="s">
+        <v>315</v>
+      </c>
+      <c r="H1605">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I1605">
+        <v>1.43</v>
+      </c>
+      <c r="J1605">
+        <v>8.35</v>
+      </c>
+      <c r="K1605">
+        <v>0.93</v>
+      </c>
+      <c r="L1605">
+        <v>0.42</v>
+      </c>
+      <c r="M1605">
+        <v>0.09</v>
+      </c>
+      <c r="N1605">
+        <v>0</v>
+      </c>
+      <c r="O1605">
+        <v>7</v>
+      </c>
+      <c r="P1605">
+        <v>5.81</v>
+      </c>
+      <c r="Q1605">
+        <v>29.09</v>
+      </c>
+      <c r="R1605">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="S1605">
+        <v>28</v>
+      </c>
+      <c r="T1605">
+        <v>2</v>
+      </c>
+      <c r="U1605">
+        <v>22</v>
+      </c>
+      <c r="V1605">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1606" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1606" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1606" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1606" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1606" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1606" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1606" t="s">
+        <v>1311</v>
+      </c>
+      <c r="H1606">
+        <v>5.05</v>
+      </c>
+      <c r="I1606">
+        <v>0.73</v>
+      </c>
+      <c r="J1606">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="K1606">
+        <v>0.49</v>
+      </c>
+      <c r="L1606">
+        <v>0.23</v>
+      </c>
+      <c r="M1606">
+        <v>0.02</v>
+      </c>
+      <c r="N1606">
+        <v>0</v>
+      </c>
+      <c r="O1606">
+        <v>1</v>
+      </c>
+      <c r="P1606">
+        <v>5.59</v>
+      </c>
+      <c r="Q1606">
+        <v>28.34</v>
+      </c>
+      <c r="R1606">
+        <v>4.57</v>
+      </c>
+      <c r="S1606">
+        <v>19</v>
+      </c>
+      <c r="T1606">
+        <v>3</v>
+      </c>
+      <c r="U1606">
+        <v>13</v>
+      </c>
+      <c r="V1606">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1607" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1607" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1607" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1607" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1607" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1607" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1607" t="s">
+        <v>1312</v>
+      </c>
+      <c r="H1607">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="I1607">
+        <v>0.94</v>
+      </c>
+      <c r="J1607">
+        <v>3.4</v>
+      </c>
+      <c r="K1607">
+        <v>0.7</v>
+      </c>
+      <c r="L1607">
+        <v>0.21</v>
+      </c>
+      <c r="M1607">
+        <v>0.04</v>
+      </c>
+      <c r="N1607">
+        <v>0</v>
+      </c>
+      <c r="O1607">
+        <v>3</v>
+      </c>
+      <c r="P1607">
+        <v>7.21</v>
+      </c>
+      <c r="Q1607">
+        <v>26.64</v>
+      </c>
+      <c r="R1607">
+        <v>4.45</v>
+      </c>
+      <c r="S1607">
+        <v>12</v>
+      </c>
+      <c r="T1607">
+        <v>2</v>
+      </c>
+      <c r="U1607">
+        <v>14</v>
+      </c>
+      <c r="V1607">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1608" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1608" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1608" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1608" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1608" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1608" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1608" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H1608">
+        <v>6.53</v>
+      </c>
+      <c r="I1608">
+        <v>1.67</v>
+      </c>
+      <c r="J1608">
+        <v>4.84</v>
+      </c>
+      <c r="K1608">
+        <v>1.19</v>
+      </c>
+      <c r="L1608">
+        <v>0.45</v>
+      </c>
+      <c r="M1608">
+        <v>0.05</v>
+      </c>
+      <c r="N1608">
+        <v>0</v>
+      </c>
+      <c r="O1608">
+        <v>5</v>
+      </c>
+      <c r="P1608">
+        <v>7.62</v>
+      </c>
+      <c r="Q1608">
+        <v>28.32</v>
+      </c>
+      <c r="R1608">
+        <v>4.99</v>
+      </c>
+      <c r="S1608">
+        <v>35</v>
+      </c>
+      <c r="T1608">
+        <v>10</v>
+      </c>
+      <c r="U1608">
+        <v>30</v>
+      </c>
+      <c r="V1608">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1609" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1609" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C1609" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1609" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1609" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1609" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1609" t="s">
+        <v>1314</v>
+      </c>
+      <c r="H1609">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="I1609">
+        <v>0.61</v>
+      </c>
+      <c r="J1609">
+        <v>3.65</v>
+      </c>
+      <c r="K1609">
+        <v>0.33</v>
+      </c>
+      <c r="L1609">
+        <v>0.21</v>
+      </c>
+      <c r="M1609">
+        <v>0.08</v>
+      </c>
+      <c r="N1609">
+        <v>0</v>
+      </c>
+      <c r="O1609">
+        <v>7</v>
+      </c>
+      <c r="P1609">
+        <v>5.27</v>
+      </c>
+      <c r="Q1609">
+        <v>29.32</v>
+      </c>
+      <c r="R1609">
+        <v>3.39</v>
+      </c>
+      <c r="S1609">
+        <v>6</v>
+      </c>
+      <c r="T1609">
+        <v>0</v>
+      </c>
+      <c r="U1609">
+        <v>12</v>
+      </c>
+      <c r="V1609">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BB122C-B76D-4547-AABC-B4236B38D525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F318DB5-8565-5240-B615-E922DB3C90F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9156" uniqueCount="1316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9204" uniqueCount="1321">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3983,13 +3983,28 @@
   </si>
   <si>
     <t>N3 J17 VS Seyssinet 04/04/2026</t>
+  </si>
+  <si>
+    <t>01:44:31</t>
+  </si>
+  <si>
+    <t>01:42:00</t>
+  </si>
+  <si>
+    <t>01:44:48</t>
+  </si>
+  <si>
+    <t>01:42:18</t>
+  </si>
+  <si>
+    <t>01:43:25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4032,6 +4047,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4053,7 +4075,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4079,6 +4101,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4393,7 +4416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1609"/>
+  <dimension ref="A1:V1617"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -112275,6 +112298,550 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1610" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1610" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1610" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C1610" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1610" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1610" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1610" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1610" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1610">
+        <v>7.75</v>
+      </c>
+      <c r="I1610">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J1610">
+        <v>7.61</v>
+      </c>
+      <c r="K1610">
+        <v>0.12</v>
+      </c>
+      <c r="L1610">
+        <v>0.02</v>
+      </c>
+      <c r="M1610">
+        <v>0</v>
+      </c>
+      <c r="N1610">
+        <v>0</v>
+      </c>
+      <c r="O1610">
+        <v>0</v>
+      </c>
+      <c r="P1610">
+        <v>3.76</v>
+      </c>
+      <c r="Q1610">
+        <v>23.42</v>
+      </c>
+      <c r="R1610">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="S1610">
+        <v>14</v>
+      </c>
+      <c r="T1610">
+        <v>1</v>
+      </c>
+      <c r="U1610">
+        <v>14</v>
+      </c>
+      <c r="V1610">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1611" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1611" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C1611" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1611" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1611" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1611" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1611" t="s">
+        <v>381</v>
+      </c>
+      <c r="H1611">
+        <v>7.12</v>
+      </c>
+      <c r="I1611">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J1611">
+        <v>6.83</v>
+      </c>
+      <c r="K1611">
+        <v>0.26</v>
+      </c>
+      <c r="L1611">
+        <v>0.03</v>
+      </c>
+      <c r="M1611">
+        <v>0</v>
+      </c>
+      <c r="N1611">
+        <v>0</v>
+      </c>
+      <c r="O1611">
+        <v>0</v>
+      </c>
+      <c r="P1611">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="Q1611">
+        <v>23.93</v>
+      </c>
+      <c r="R1611">
+        <v>4.62</v>
+      </c>
+      <c r="S1611">
+        <v>48</v>
+      </c>
+      <c r="T1611">
+        <v>6</v>
+      </c>
+      <c r="U1611">
+        <v>34</v>
+      </c>
+      <c r="V1611">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1612" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1612" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C1612" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1612" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1612" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1612" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1612" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H1612">
+        <v>6.28</v>
+      </c>
+      <c r="I1612">
+        <v>0.1</v>
+      </c>
+      <c r="J1612">
+        <v>6.17</v>
+      </c>
+      <c r="K1612">
+        <v>0.1</v>
+      </c>
+      <c r="L1612">
+        <v>0</v>
+      </c>
+      <c r="M1612">
+        <v>0</v>
+      </c>
+      <c r="N1612">
+        <v>0</v>
+      </c>
+      <c r="O1612">
+        <v>0</v>
+      </c>
+      <c r="P1612">
+        <v>3.47</v>
+      </c>
+      <c r="Q1612">
+        <v>20.03</v>
+      </c>
+      <c r="R1612">
+        <v>3.61</v>
+      </c>
+      <c r="S1612">
+        <v>20</v>
+      </c>
+      <c r="T1612">
+        <v>0</v>
+      </c>
+      <c r="U1612">
+        <v>16</v>
+      </c>
+      <c r="V1612">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1613" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1613" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C1613" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1613" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1613" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1613" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1613" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H1613">
+        <v>7.78</v>
+      </c>
+      <c r="I1613">
+        <v>0.34</v>
+      </c>
+      <c r="J1613">
+        <v>7.43</v>
+      </c>
+      <c r="K1613">
+        <v>0.3</v>
+      </c>
+      <c r="L1613">
+        <v>0.05</v>
+      </c>
+      <c r="M1613">
+        <v>0</v>
+      </c>
+      <c r="N1613">
+        <v>0</v>
+      </c>
+      <c r="O1613">
+        <v>1</v>
+      </c>
+      <c r="P1613">
+        <v>3.89</v>
+      </c>
+      <c r="Q1613">
+        <v>25.93</v>
+      </c>
+      <c r="R1613">
+        <v>5.49</v>
+      </c>
+      <c r="S1613">
+        <v>57</v>
+      </c>
+      <c r="T1613">
+        <v>11</v>
+      </c>
+      <c r="U1613">
+        <v>52</v>
+      </c>
+      <c r="V1613">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1614" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1614" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C1614" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1614" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1614" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1614" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1614" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H1614">
+        <v>7.77</v>
+      </c>
+      <c r="I1614">
+        <v>0.18</v>
+      </c>
+      <c r="J1614">
+        <v>7.58</v>
+      </c>
+      <c r="K1614">
+        <v>0.17</v>
+      </c>
+      <c r="L1614">
+        <v>0.02</v>
+      </c>
+      <c r="M1614">
+        <v>0</v>
+      </c>
+      <c r="N1614">
+        <v>0</v>
+      </c>
+      <c r="O1614">
+        <v>1</v>
+      </c>
+      <c r="P1614">
+        <v>3.99</v>
+      </c>
+      <c r="Q1614">
+        <v>25.53</v>
+      </c>
+      <c r="R1614">
+        <v>5.17</v>
+      </c>
+      <c r="S1614">
+        <v>77</v>
+      </c>
+      <c r="T1614">
+        <v>13</v>
+      </c>
+      <c r="U1614">
+        <v>59</v>
+      </c>
+      <c r="V1614">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1615" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1615" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C1615" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1615" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1615" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1615" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1615" t="s">
+        <v>1318</v>
+      </c>
+      <c r="H1615">
+        <v>7.56</v>
+      </c>
+      <c r="I1615">
+        <v>0.32</v>
+      </c>
+      <c r="J1615">
+        <v>7.23</v>
+      </c>
+      <c r="K1615">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L1615">
+        <v>0.04</v>
+      </c>
+      <c r="M1615">
+        <v>0</v>
+      </c>
+      <c r="N1615">
+        <v>0</v>
+      </c>
+      <c r="O1615">
+        <v>0</v>
+      </c>
+      <c r="P1615">
+        <v>4.25</v>
+      </c>
+      <c r="Q1615">
+        <v>22.34</v>
+      </c>
+      <c r="R1615">
+        <v>4.55</v>
+      </c>
+      <c r="S1615">
+        <v>44</v>
+      </c>
+      <c r="T1615">
+        <v>5</v>
+      </c>
+      <c r="U1615">
+        <v>31</v>
+      </c>
+      <c r="V1615">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1616" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1616" s="13">
+        <v>46119</v>
+      </c>
+      <c r="C1616" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1616" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1616" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1616" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1616" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H1616">
+        <v>8.51</v>
+      </c>
+      <c r="I1616">
+        <v>0.3</v>
+      </c>
+      <c r="J1616">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="K1616">
+        <v>0.3</v>
+      </c>
+      <c r="L1616">
+        <v>0.02</v>
+      </c>
+      <c r="M1616">
+        <v>0</v>
+      </c>
+      <c r="N1616">
+        <v>0</v>
+      </c>
+      <c r="O1616">
+        <v>0</v>
+      </c>
+      <c r="P1616">
+        <v>4.91</v>
+      </c>
+      <c r="Q1616">
+        <v>22.97</v>
+      </c>
+      <c r="R1616">
+        <v>5.01</v>
+      </c>
+      <c r="S1616">
+        <v>50</v>
+      </c>
+      <c r="T1616">
+        <v>8</v>
+      </c>
+      <c r="U1616">
+        <v>22</v>
+      </c>
+      <c r="V1616">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1617" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1617" s="13">
+        <v>46119</v>
+      </c>
+      <c r="C1617" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1617" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1617" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1617" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1617" t="s">
+        <v>1320</v>
+      </c>
+      <c r="H1617">
+        <v>7.96</v>
+      </c>
+      <c r="I1617">
+        <v>0.3</v>
+      </c>
+      <c r="J1617">
+        <v>7.65</v>
+      </c>
+      <c r="K1617">
+        <v>0.3</v>
+      </c>
+      <c r="L1617">
+        <v>0.01</v>
+      </c>
+      <c r="M1617">
+        <v>0</v>
+      </c>
+      <c r="N1617">
+        <v>0</v>
+      </c>
+      <c r="O1617">
+        <v>0</v>
+      </c>
+      <c r="P1617">
+        <v>4.53</v>
+      </c>
+      <c r="Q1617">
+        <v>22.06</v>
+      </c>
+      <c r="R1617">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="S1617">
+        <v>65</v>
+      </c>
+      <c r="T1617">
+        <v>4</v>
+      </c>
+      <c r="U1617">
+        <v>45</v>
+      </c>
+      <c r="V1617">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DonneesGPSPropres.xlsx
+++ b/data/DonneesGPSPropres.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F318DB5-8565-5240-B615-E922DB3C90F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E4A5C9-5122-1A4E-86F1-671DE6CB72FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9204" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9276" uniqueCount="1327">
   <si>
     <t>Temps joué</t>
   </si>
@@ -3998,6 +3998,24 @@
   </si>
   <si>
     <t>01:43:25</t>
+  </si>
+  <si>
+    <t>01:32:27</t>
+  </si>
+  <si>
+    <t>01:31:09</t>
+  </si>
+  <si>
+    <t>01:31:58</t>
+  </si>
+  <si>
+    <t>01:31:43</t>
+  </si>
+  <si>
+    <t>01:31:31</t>
+  </si>
+  <si>
+    <t>01:22:08</t>
   </si>
 </sst>
 </file>
@@ -4416,7 +4434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V1617"/>
+  <dimension ref="A1:V1629"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -112842,6 +112860,822 @@
         <v>6</v>
       </c>
     </row>
+    <row r="1618" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1618" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1618" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C1618" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1618" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1618" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1618" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1618" t="s">
+        <v>692</v>
+      </c>
+      <c r="H1618">
+        <v>5.86</v>
+      </c>
+      <c r="I1618">
+        <v>0.23</v>
+      </c>
+      <c r="J1618">
+        <v>5.62</v>
+      </c>
+      <c r="K1618">
+        <v>0.2</v>
+      </c>
+      <c r="L1618">
+        <v>0.04</v>
+      </c>
+      <c r="M1618">
+        <v>0</v>
+      </c>
+      <c r="N1618">
+        <v>0</v>
+      </c>
+      <c r="O1618">
+        <v>1</v>
+      </c>
+      <c r="P1618">
+        <v>3.14</v>
+      </c>
+      <c r="Q1618">
+        <v>25.01</v>
+      </c>
+      <c r="R1618">
+        <v>4.08</v>
+      </c>
+      <c r="S1618">
+        <v>17</v>
+      </c>
+      <c r="T1618">
+        <v>1</v>
+      </c>
+      <c r="U1618">
+        <v>14</v>
+      </c>
+      <c r="V1618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1619" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1619" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C1619" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1619" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1619" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1619" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1619" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1619">
+        <v>5.83</v>
+      </c>
+      <c r="I1619">
+        <v>0.48</v>
+      </c>
+      <c r="J1619">
+        <v>5.33</v>
+      </c>
+      <c r="K1619">
+        <v>0.37</v>
+      </c>
+      <c r="L1619">
+        <v>0.12</v>
+      </c>
+      <c r="M1619">
+        <v>0</v>
+      </c>
+      <c r="N1619">
+        <v>0</v>
+      </c>
+      <c r="O1619">
+        <v>0</v>
+      </c>
+      <c r="P1619">
+        <v>3.81</v>
+      </c>
+      <c r="Q1619">
+        <v>24.84</v>
+      </c>
+      <c r="R1619">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="S1619">
+        <v>47</v>
+      </c>
+      <c r="T1619">
+        <v>12</v>
+      </c>
+      <c r="U1619">
+        <v>34</v>
+      </c>
+      <c r="V1619">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1620" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1620" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C1620" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1620" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1620" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1620" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1620" t="s">
+        <v>1321</v>
+      </c>
+      <c r="H1620">
+        <v>6.04</v>
+      </c>
+      <c r="I1620">
+        <v>0.32</v>
+      </c>
+      <c r="J1620">
+        <v>5.71</v>
+      </c>
+      <c r="K1620">
+        <v>0.26</v>
+      </c>
+      <c r="L1620">
+        <v>0.06</v>
+      </c>
+      <c r="M1620">
+        <v>0</v>
+      </c>
+      <c r="N1620">
+        <v>0</v>
+      </c>
+      <c r="O1620">
+        <v>0</v>
+      </c>
+      <c r="P1620">
+        <v>3.86</v>
+      </c>
+      <c r="Q1620">
+        <v>24.87</v>
+      </c>
+      <c r="R1620">
+        <v>4.21</v>
+      </c>
+      <c r="S1620">
+        <v>41</v>
+      </c>
+      <c r="T1620">
+        <v>3</v>
+      </c>
+      <c r="U1620">
+        <v>30</v>
+      </c>
+      <c r="V1620">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1621" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1621" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1621" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1621" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1621" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1621" t="s">
+        <v>179</v>
+      </c>
+      <c r="H1621">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="I1621">
+        <v>0.35</v>
+      </c>
+      <c r="J1621">
+        <v>7.75</v>
+      </c>
+      <c r="K1621">
+        <v>0.34</v>
+      </c>
+      <c r="L1621">
+        <v>0.03</v>
+      </c>
+      <c r="M1621">
+        <v>0</v>
+      </c>
+      <c r="N1621">
+        <v>0</v>
+      </c>
+      <c r="O1621">
+        <v>0</v>
+      </c>
+      <c r="P1621">
+        <v>3.99</v>
+      </c>
+      <c r="Q1621">
+        <v>22.23</v>
+      </c>
+      <c r="R1621">
+        <v>5.5</v>
+      </c>
+      <c r="S1621">
+        <v>51</v>
+      </c>
+      <c r="T1621">
+        <v>7</v>
+      </c>
+      <c r="U1621">
+        <v>51</v>
+      </c>
+      <c r="V1621">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1622" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1622" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1622" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1622" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1622" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1622" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H1622">
+        <v>6.02</v>
+      </c>
+      <c r="I1622">
+        <v>0.52</v>
+      </c>
+      <c r="J1622">
+        <v>5.49</v>
+      </c>
+      <c r="K1622">
+        <v>0.37</v>
+      </c>
+      <c r="L1622">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M1622">
+        <v>0.03</v>
+      </c>
+      <c r="N1622">
+        <v>0</v>
+      </c>
+      <c r="O1622">
+        <v>4</v>
+      </c>
+      <c r="P1622">
+        <v>3.56</v>
+      </c>
+      <c r="Q1622">
+        <v>27.71</v>
+      </c>
+      <c r="R1622">
+        <v>5.37</v>
+      </c>
+      <c r="S1622">
+        <v>62</v>
+      </c>
+      <c r="T1622">
+        <v>22</v>
+      </c>
+      <c r="U1622">
+        <v>47</v>
+      </c>
+      <c r="V1622">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1623" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1623" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1623" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1623" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1623" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1623" t="s">
+        <v>1323</v>
+      </c>
+      <c r="H1623">
+        <v>6.98</v>
+      </c>
+      <c r="I1623">
+        <v>0.43</v>
+      </c>
+      <c r="J1623">
+        <v>6.53</v>
+      </c>
+      <c r="K1623">
+        <v>0.38</v>
+      </c>
+      <c r="L1623">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M1623">
+        <v>0</v>
+      </c>
+      <c r="N1623">
+        <v>0</v>
+      </c>
+      <c r="O1623">
+        <v>0</v>
+      </c>
+      <c r="P1623">
+        <v>4.49</v>
+      </c>
+      <c r="Q1623">
+        <v>23.26</v>
+      </c>
+      <c r="R1623">
+        <v>4.57</v>
+      </c>
+      <c r="S1623">
+        <v>44</v>
+      </c>
+      <c r="T1623">
+        <v>5</v>
+      </c>
+      <c r="U1623">
+        <v>33</v>
+      </c>
+      <c r="V1623">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1624" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1624" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1624" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1624" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1624" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1624" t="s">
+        <v>1324</v>
+      </c>
+      <c r="H1624">
+        <v>6.41</v>
+      </c>
+      <c r="I1624">
+        <v>0.31</v>
+      </c>
+      <c r="J1624">
+        <v>6.08</v>
+      </c>
+      <c r="K1624">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L1624">
+        <v>0.04</v>
+      </c>
+      <c r="M1624">
+        <v>0</v>
+      </c>
+      <c r="N1624">
+        <v>0</v>
+      </c>
+      <c r="O1624">
+        <v>0</v>
+      </c>
+      <c r="P1624">
+        <v>3.58</v>
+      </c>
+      <c r="Q1624">
+        <v>24.82</v>
+      </c>
+      <c r="R1624">
+        <v>5.24</v>
+      </c>
+      <c r="S1624">
+        <v>53</v>
+      </c>
+      <c r="T1624">
+        <v>15</v>
+      </c>
+      <c r="U1624">
+        <v>45</v>
+      </c>
+      <c r="V1624">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1625" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1625" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1625" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1625" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="F1625" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1625" t="s">
+        <v>739</v>
+      </c>
+      <c r="H1625">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="I1625">
+        <v>0.19</v>
+      </c>
+      <c r="J1625">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="K1625">
+        <v>0.18</v>
+      </c>
+      <c r="L1625">
+        <v>0.01</v>
+      </c>
+      <c r="M1625">
+        <v>0</v>
+      </c>
+      <c r="N1625">
+        <v>0</v>
+      </c>
+      <c r="O1625">
+        <v>0</v>
+      </c>
+      <c r="P1625">
+        <v>3.13</v>
+      </c>
+      <c r="Q1625">
+        <v>22.21</v>
+      </c>
+      <c r="R1625">
+        <v>4.47</v>
+      </c>
+      <c r="S1625">
+        <v>27</v>
+      </c>
+      <c r="T1625">
+        <v>1</v>
+      </c>
+      <c r="U1625">
+        <v>21</v>
+      </c>
+      <c r="V1625">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1626" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1626" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1626" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1626" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1626" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1626" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H1626">
+        <v>6.42</v>
+      </c>
+      <c r="I1626">
+        <v>0.37</v>
+      </c>
+      <c r="J1626">
+        <v>6.04</v>
+      </c>
+      <c r="K1626">
+        <v>0.31</v>
+      </c>
+      <c r="L1626">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M1626">
+        <v>0</v>
+      </c>
+      <c r="N1626">
+        <v>0</v>
+      </c>
+      <c r="O1626">
+        <v>0</v>
+      </c>
+      <c r="P1626">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="Q1626">
+        <v>23.45</v>
+      </c>
+      <c r="R1626">
+        <v>4.95</v>
+      </c>
+      <c r="S1626">
+        <v>28</v>
+      </c>
+      <c r="T1626">
+        <v>9</v>
+      </c>
+      <c r="U1626">
+        <v>34</v>
+      </c>
+      <c r="V1626">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1627" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1627" s="13">
+        <v>46122</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1627" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1627" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1627" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1627" t="s">
+        <v>460</v>
+      </c>
+      <c r="H1627">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="I1627">
+        <v>0.19</v>
+      </c>
+      <c r="J1627">
+        <v>8.19</v>
+      </c>
+      <c r="K1627">
+        <v>0.18</v>
+      </c>
+      <c r="L1627">
+        <v>0.01</v>
+      </c>
+      <c r="M1627">
+        <v>0</v>
+      </c>
+      <c r="N1627">
+        <v>0</v>
+      </c>
+      <c r="O1627">
+        <v>0</v>
+      </c>
+      <c r="P1627">
+        <v>3.86</v>
+      </c>
+      <c r="Q1627">
+        <v>21.44</v>
+      </c>
+      <c r="R1627">
+        <v>4.2</v>
+      </c>
+      <c r="S1627">
+        <v>12</v>
+      </c>
+      <c r="T1627">
+        <v>1</v>
+      </c>
+      <c r="U1627">
+        <v>8</v>
+      </c>
+      <c r="V1627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1628" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1628" s="13">
+        <v>46122</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1628" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1628" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1628" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1628" t="s">
+        <v>460</v>
+      </c>
+      <c r="H1628">
+        <v>6.08</v>
+      </c>
+      <c r="I1628">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J1628">
+        <v>5.79</v>
+      </c>
+      <c r="K1628">
+        <v>0.25</v>
+      </c>
+      <c r="L1628">
+        <v>0.04</v>
+      </c>
+      <c r="M1628">
+        <v>0</v>
+      </c>
+      <c r="N1628">
+        <v>0</v>
+      </c>
+      <c r="O1628">
+        <v>0</v>
+      </c>
+      <c r="P1628">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q1628">
+        <v>24.96</v>
+      </c>
+      <c r="R1628">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="S1628">
+        <v>33</v>
+      </c>
+      <c r="T1628">
+        <v>3</v>
+      </c>
+      <c r="U1628">
+        <v>11</v>
+      </c>
+      <c r="V1628">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1629" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1629" s="13">
+        <v>46122</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1629" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1629" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1629" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1629" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H1629">
+        <v>6.79</v>
+      </c>
+      <c r="I1629">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J1629">
+        <v>6.2</v>
+      </c>
+      <c r="K1629">
+        <v>0.43</v>
+      </c>
+      <c r="L1629">
+        <v>0.15</v>
+      </c>
+      <c r="M1629">
+        <v>0.01</v>
+      </c>
+      <c r="N1629">
+        <v>0</v>
+      </c>
+      <c r="O1629">
+        <v>3</v>
+      </c>
+      <c r="P1629">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="Q1629">
+        <v>25.87</v>
+      </c>
+      <c r="R1629">
+        <v>4.82</v>
+      </c>
+      <c r="S1629">
+        <v>43</v>
+      </c>
+      <c r="T1629">
+        <v>10</v>
+      </c>
+      <c r="U1629">
+        <v>22</v>
+      </c>
+      <c r="V1629">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
